--- a/results_2026_master.xlsx
+++ b/results_2026_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19247\Documents\codemathbike\codemathbike_bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{962FCAA7-C42B-462D-B51C-C29237F60E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2F84A13-8917-4216-9119-36C70B822CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{E4CCCC36-747C-4C6A-A938-400850181E6F}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="419">
   <si>
     <t>Divisions</t>
   </si>
@@ -1438,7 +1438,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="45">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1804,7 +1811,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B67B0C24-496D-4362-8989-27568D29525A}" name="tbl_points" displayName="tbl_points" ref="E1:F60" totalsRowShown="0" headerRowDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B67B0C24-496D-4362-8989-27568D29525A}" name="tbl_points" displayName="tbl_points" ref="E1:F60" totalsRowShown="0" headerRowDxfId="44">
   <autoFilter ref="E1:F60" xr:uid="{B67B0C24-496D-4362-8989-27568D29525A}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{26FEA31D-C1DD-4A82-A0F0-29F4BFEAA9BF}" name="Place"/>
@@ -1815,7 +1822,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}" name="tbl_individual" displayName="tbl_individual" ref="A1:S353" totalsRowShown="0" headerRowDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}" name="tbl_individual" displayName="tbl_individual" ref="A1:S353" totalsRowShown="0" headerRowDxfId="43">
   <autoFilter ref="A1:S353" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S353">
     <sortCondition ref="S1:S353"/>
@@ -1824,38 +1831,38 @@
     <tableColumn id="1" xr3:uid="{DD0C8BFC-D933-4D84-A252-784AFB91D5D2}" name="Student Name"/>
     <tableColumn id="2" xr3:uid="{50DB066B-1368-4510-AE03-F035E82A9C80}" name="School"/>
     <tableColumn id="3" xr3:uid="{7521EB7C-E51A-4930-A4D2-608C8D120FA9}" name="Division"/>
-    <tableColumn id="4" xr3:uid="{95AF9BEA-E11E-4C3A-98F5-4C1CA2AE9261}" name="Plate #" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{C4BC7103-4C35-4FC3-8F18-8455C41D4783}" name="R1 Place" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{F003CE6A-1709-47C7-A52B-4E78A06B55BC}" name="R1 Pts" dataDxfId="39">
+    <tableColumn id="4" xr3:uid="{95AF9BEA-E11E-4C3A-98F5-4C1CA2AE9261}" name="Plate #" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{C4BC7103-4C35-4FC3-8F18-8455C41D4783}" name="R1 Place" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{F003CE6A-1709-47C7-A52B-4E78A06B55BC}" name="R1 Pts" dataDxfId="40">
       <calculatedColumnFormula>IF(E2="","",IF(E2="DNS",0,IF(E2="DQ",0,IF(E2="DNF",1,IF(AND(ISNUMBER(E2),E2&gt;59),1,_xlfn.XLOOKUP(E2,tbl_points[Place],tbl_points[Points],""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00AA5EEC-F524-4B3A-8D3D-DD590338CBF4}" name="R2 Place" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{D5BD0204-BF0C-4CD7-84CF-355F4C709D84}" name="R2 Pts" dataDxfId="37">
+    <tableColumn id="7" xr3:uid="{00AA5EEC-F524-4B3A-8D3D-DD590338CBF4}" name="R2 Place" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{D5BD0204-BF0C-4CD7-84CF-355F4C709D84}" name="R2 Pts" dataDxfId="38">
       <calculatedColumnFormula>IF(G2="","",IF(G2="DNS",0,IF(G2="DQ",0,IF(G2="DNF",1,IF(AND(ISNUMBER(G2),G2&gt;59),1,_xlfn.XLOOKUP(G2,tbl_points[Place],tbl_points[Points],""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{AAA1602A-3E76-4D80-A749-C082B0EEE022}" name="R3 Place" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{129B956B-A68A-4A58-B03A-5E88F63F4109}" name="R3 Pts" dataDxfId="35">
+    <tableColumn id="9" xr3:uid="{AAA1602A-3E76-4D80-A749-C082B0EEE022}" name="R3 Place" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{129B956B-A68A-4A58-B03A-5E88F63F4109}" name="R3 Pts" dataDxfId="36">
       <calculatedColumnFormula>IF(I2="","",IF(I2="DNS",0,IF(I2="DQ",0,IF(I2="DNF",1,IF(AND(ISNUMBER(I2),I2&gt;59),1,_xlfn.XLOOKUP(I2,tbl_points[Place],tbl_points[Points],""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{58CEE06C-D397-4C16-AFDA-197232873DB1}" name="R4 Place" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{8F6D618C-1190-4F5C-A449-77BB8AFE782C}" name="R4 Pts" dataDxfId="33">
+    <tableColumn id="11" xr3:uid="{58CEE06C-D397-4C16-AFDA-197232873DB1}" name="R4 Place" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{8F6D618C-1190-4F5C-A449-77BB8AFE782C}" name="R4 Pts" dataDxfId="34">
       <calculatedColumnFormula>IF(K2="","",IF(K2="DNS",0,IF(K2="DQ",0,IF(K2="DNF",1,IF(AND(ISNUMBER(K2),K2&gt;59),1,_xlfn.XLOOKUP(K2,tbl_points[Place],tbl_points[Points],""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{09134E3A-40B6-4480-BF56-619415F1546B}" name="R5 Place" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{0630E922-C5AC-4446-B509-709B7EECF31A}" name="R5 Pts" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{09134E3A-40B6-4480-BF56-619415F1546B}" name="R5 Place" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{0630E922-C5AC-4446-B509-709B7EECF31A}" name="R5 Pts" dataDxfId="32">
       <calculatedColumnFormula>IF(M2="","",IF(M2="DNS",0,IF(M2="DQ",0,IF(M2="DNF",1,IF(AND(ISNUMBER(M2),M2&gt;59),1,_xlfn.XLOOKUP(M2,tbl_points[Place],tbl_points[Points],""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{A3A3C6B1-EAC4-4CA1-B9F1-91AD4AED8E96}" name="R6 Place" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{183BA364-7ECF-4FCA-8D96-4CEAFE4D6897}" name="R6 Pts" dataDxfId="29">
+    <tableColumn id="15" xr3:uid="{A3A3C6B1-EAC4-4CA1-B9F1-91AD4AED8E96}" name="R6 Place" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{183BA364-7ECF-4FCA-8D96-4CEAFE4D6897}" name="R6 Pts" dataDxfId="30">
       <calculatedColumnFormula>IF(O2="","",IF(O2="DNS",0,IF(O2="DQ",0,IF(O2="DNF",1,IF(AND(ISNUMBER(O2),O2&gt;59),1,_xlfn.XLOOKUP(O2,tbl_points[Place],tbl_points[Points],""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7E434874-15F0-4158-8350-07E2BFD885BE}" name="Total" dataDxfId="28">
+    <tableColumn id="17" xr3:uid="{7E434874-15F0-4158-8350-07E2BFD885BE}" name="Total" dataDxfId="29">
       <calculatedColumnFormula>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{86859925-B685-41CB-B33D-9607A1626666}" name="Lowest Score" dataDxfId="27">
+    <tableColumn id="18" xr3:uid="{86859925-B685-41CB-B33D-9607A1626666}" name="Lowest Score" dataDxfId="28">
       <calculatedColumnFormula>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{3B09C5B7-0CED-45E4-9DF3-6F0F3B8C89EE}" name="Top 5" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{3B09C5B7-0CED-45E4-9DF3-6F0F3B8C89EE}" name="Top 5" dataDxfId="1">
       <calculatedColumnFormula>tbl_individual[[#This Row],[Total]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1864,13 +1871,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10951E40-9465-4D54-A308-3E2A245DA857}" name="enduro" displayName="enduro" ref="A1:E353" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10951E40-9465-4D54-A308-3E2A245DA857}" name="enduro" displayName="enduro" ref="A1:E353" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:E353" xr:uid="{10951E40-9465-4D54-A308-3E2A245DA857}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F5B760F2-2C17-4991-A9D6-EED4261386D4}" name="Student Name"/>
     <tableColumn id="2" xr3:uid="{7CB5820D-3B26-4DA7-9C21-32B6A5DC2026}" name="School"/>
     <tableColumn id="3" xr3:uid="{9F55042D-35BF-4BB8-9118-1298A4D8E67F}" name="Division"/>
-    <tableColumn id="4" xr3:uid="{5F574A16-C593-44D6-BF33-5771DDE10346}" name="Plate #" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{5F574A16-C593-44D6-BF33-5771DDE10346}" name="Plate #" dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{76D035DA-EC5A-4955-8134-6D150CD5B699}" name="yes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1878,12 +1885,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6FE32177-DBD8-4299-9E12-DE45C01CDFC1}" name="tbl_teampoints" displayName="tbl_teampoints" ref="A1:I47" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6FE32177-DBD8-4299-9E12-DE45C01CDFC1}" name="tbl_teampoints" displayName="tbl_teampoints" ref="A1:I47" totalsRowShown="0" headerRowDxfId="27">
   <autoFilter ref="A1:I47" xr:uid="{6FE32177-DBD8-4299-9E12-DE45C01CDFC1}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{E4DDB9C1-470A-4B63-B391-B74364B13A0B}" name="Division"/>
     <tableColumn id="2" xr3:uid="{C9B23502-0457-486C-96DF-CDE7023AF0B8}" name="School"/>
-    <tableColumn id="3" xr3:uid="{2FDC0DE4-1DEE-4FF2-90E4-1CEBC22D34E1}" name="Race 1" dataDxfId="25">
+    <tableColumn id="3" xr3:uid="{2FDC0DE4-1DEE-4FF2-90E4-1CEBC22D34E1}" name="Race 1" dataDxfId="26">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -1915,7 +1922,7 @@
 )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B1A9F92E-C531-4F9B-9E61-4AF67269E504}" name="Race 2" dataDxfId="24">
+    <tableColumn id="4" xr3:uid="{B1A9F92E-C531-4F9B-9E61-4AF67269E504}" name="Race 2" dataDxfId="25">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -1947,7 +1954,7 @@
 )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{98622B84-034F-49A3-94EB-FE028D7330DC}" name="Race 3" dataDxfId="23">
+    <tableColumn id="5" xr3:uid="{98622B84-034F-49A3-94EB-FE028D7330DC}" name="Race 3" dataDxfId="24">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -1979,7 +1986,7 @@
 )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E251564D-BEF9-4A06-B705-57876A4C364D}" name="Race 4" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{E251564D-BEF9-4A06-B705-57876A4C364D}" name="Race 4" dataDxfId="23">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -2011,7 +2018,7 @@
 )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{E38A2690-1CC8-45F7-9CAB-D28FDE2604B7}" name="Race 5" dataDxfId="21">
+    <tableColumn id="7" xr3:uid="{E38A2690-1CC8-45F7-9CAB-D28FDE2604B7}" name="Race 5" dataDxfId="22">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -2043,7 +2050,7 @@
 )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{51FAA391-8BE1-4ECE-A0AB-B5AB0C9BE2C5}" name="Race 6" dataDxfId="20">
+    <tableColumn id="8" xr3:uid="{51FAA391-8BE1-4ECE-A0AB-B5AB0C9BE2C5}" name="Race 6" dataDxfId="21">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -2075,7 +2082,7 @@
 )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{539A3327-6FEC-4B8A-A923-635DC3180909}" name="Total" dataDxfId="19">
+    <tableColumn id="9" xr3:uid="{539A3327-6FEC-4B8A-A923-635DC3180909}" name="Total" dataDxfId="20">
       <calculatedColumnFormula>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3105,9 +3112,12 @@
         <f>IF(E2="","",IF(E2="DNS",0,IF(E2="DQ",0,IF(E2="DNF",1,IF(AND(ISNUMBER(E2),E2&gt;59),1,_xlfn.XLOOKUP(E2,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>45</v>
       </c>
-      <c r="H2" s="3" t="str">
+      <c r="G2" s="3">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3">
         <f>IF(G2="","",IF(G2="DNS",0,IF(G2="DQ",0,IF(G2="DNF",1,IF(AND(ISNUMBER(G2),G2&gt;59),1,_xlfn.XLOOKUP(G2,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="J2" s="3" t="str">
         <f>IF(I2="","",IF(I2="DNS",0,IF(I2="DQ",0,IF(I2="DNF",1,IF(AND(ISNUMBER(I2),I2&gt;59),1,_xlfn.XLOOKUP(I2,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3127,15 +3137,15 @@
       </c>
       <c r="Q2" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="R2" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="S2" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.4">
@@ -3158,9 +3168,12 @@
         <f>IF(E3="","",IF(E3="DNS",0,IF(E3="DQ",0,IF(E3="DNF",1,IF(AND(ISNUMBER(E3),E3&gt;59),1,_xlfn.XLOOKUP(E3,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
         <f>IF(G3="","",IF(G3="DNS",0,IF(G3="DQ",0,IF(G3="DNF",1,IF(AND(ISNUMBER(G3),G3&gt;59),1,_xlfn.XLOOKUP(G3,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="J3" s="3" t="str">
         <f>IF(I3="","",IF(I3="DNS",0,IF(I3="DQ",0,IF(I3="DNF",1,IF(AND(ISNUMBER(I3),I3&gt;59),1,_xlfn.XLOOKUP(I3,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3180,7 +3193,7 @@
       </c>
       <c r="Q3" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R3" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3188,7 +3201,7 @@
       </c>
       <c r="S3" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.4">
@@ -3211,9 +3224,12 @@
         <f>IF(E4="","",IF(E4="DNS",0,IF(E4="DQ",0,IF(E4="DNF",1,IF(AND(ISNUMBER(E4),E4&gt;59),1,_xlfn.XLOOKUP(E4,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>95</v>
       </c>
-      <c r="H4" s="3" t="str">
+      <c r="G4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H4" s="3">
         <f>IF(G4="","",IF(G4="DNS",0,IF(G4="DQ",0,IF(G4="DNF",1,IF(AND(ISNUMBER(G4),G4&gt;59),1,_xlfn.XLOOKUP(G4,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="str">
         <f>IF(I4="","",IF(I4="DNS",0,IF(I4="DQ",0,IF(I4="DNF",1,IF(AND(ISNUMBER(I4),I4&gt;59),1,_xlfn.XLOOKUP(I4,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3237,7 +3253,7 @@
       </c>
       <c r="R4" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -3264,9 +3280,12 @@
         <f>IF(E5="","",IF(E5="DNS",0,IF(E5="DQ",0,IF(E5="DNF",1,IF(AND(ISNUMBER(E5),E5&gt;59),1,_xlfn.XLOOKUP(E5,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>85</v>
       </c>
-      <c r="H5" s="3" t="str">
+      <c r="G5" s="3">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3">
         <f>IF(G5="","",IF(G5="DNS",0,IF(G5="DQ",0,IF(G5="DNF",1,IF(AND(ISNUMBER(G5),G5&gt;59),1,_xlfn.XLOOKUP(G5,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="J5" s="3" t="str">
         <f>IF(I5="","",IF(I5="DNS",0,IF(I5="DQ",0,IF(I5="DNF",1,IF(AND(ISNUMBER(I5),I5&gt;59),1,_xlfn.XLOOKUP(I5,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3286,15 +3305,15 @@
       </c>
       <c r="Q5" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="R5" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="S5" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>85</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.4">
@@ -3317,9 +3336,12 @@
         <f>IF(E6="","",IF(E6="DNS",0,IF(E6="DQ",0,IF(E6="DNF",1,IF(AND(ISNUMBER(E6),E6&gt;59),1,_xlfn.XLOOKUP(E6,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>42</v>
       </c>
-      <c r="H6" s="3" t="str">
+      <c r="G6" s="3">
+        <v>34</v>
+      </c>
+      <c r="H6" s="3">
         <f>IF(G6="","",IF(G6="DNS",0,IF(G6="DQ",0,IF(G6="DNF",1,IF(AND(ISNUMBER(G6),G6&gt;59),1,_xlfn.XLOOKUP(G6,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="J6" s="3" t="str">
         <f>IF(I6="","",IF(I6="DNS",0,IF(I6="DQ",0,IF(I6="DNF",1,IF(AND(ISNUMBER(I6),I6&gt;59),1,_xlfn.XLOOKUP(I6,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3339,15 +3361,15 @@
       </c>
       <c r="Q6" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="R6" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="S6" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.4">
@@ -3370,9 +3392,12 @@
         <f>IF(E7="","",IF(E7="DNS",0,IF(E7="DQ",0,IF(E7="DNF",1,IF(AND(ISNUMBER(E7),E7&gt;59),1,_xlfn.XLOOKUP(E7,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H7" s="3" t="str">
+      <c r="G7" s="3">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3">
         <f>IF(G7="","",IF(G7="DNS",0,IF(G7="DQ",0,IF(G7="DNF",1,IF(AND(ISNUMBER(G7),G7&gt;59),1,_xlfn.XLOOKUP(G7,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="str">
         <f>IF(I7="","",IF(I7="DNS",0,IF(I7="DQ",0,IF(I7="DNF",1,IF(AND(ISNUMBER(I7),I7&gt;59),1,_xlfn.XLOOKUP(I7,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3392,7 +3417,7 @@
       </c>
       <c r="Q7" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R7" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3400,7 +3425,7 @@
       </c>
       <c r="S7" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.4">
@@ -3423,9 +3448,12 @@
         <f>IF(E8="","",IF(E8="DNS",0,IF(E8="DQ",0,IF(E8="DNF",1,IF(AND(ISNUMBER(E8),E8&gt;59),1,_xlfn.XLOOKUP(E8,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>43</v>
       </c>
-      <c r="H8" s="3" t="str">
+      <c r="G8" s="3">
+        <v>11</v>
+      </c>
+      <c r="H8" s="3">
         <f>IF(G8="","",IF(G8="DNS",0,IF(G8="DQ",0,IF(G8="DNF",1,IF(AND(ISNUMBER(G8),G8&gt;59),1,_xlfn.XLOOKUP(G8,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="J8" s="3" t="str">
         <f>IF(I8="","",IF(I8="DNS",0,IF(I8="DQ",0,IF(I8="DNF",1,IF(AND(ISNUMBER(I8),I8&gt;59),1,_xlfn.XLOOKUP(I8,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3445,7 +3473,7 @@
       </c>
       <c r="Q8" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="R8" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3453,7 +3481,7 @@
       </c>
       <c r="S8" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>43</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.4">
@@ -3476,9 +3504,12 @@
         <f>IF(E9="","",IF(E9="DNS",0,IF(E9="DQ",0,IF(E9="DNF",1,IF(AND(ISNUMBER(E9),E9&gt;59),1,_xlfn.XLOOKUP(E9,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>22</v>
       </c>
-      <c r="H9" s="3" t="str">
+      <c r="G9" s="3">
+        <v>23</v>
+      </c>
+      <c r="H9" s="3">
         <f>IF(G9="","",IF(G9="DNS",0,IF(G9="DQ",0,IF(G9="DNF",1,IF(AND(ISNUMBER(G9),G9&gt;59),1,_xlfn.XLOOKUP(G9,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="J9" s="3" t="str">
         <f>IF(I9="","",IF(I9="DNS",0,IF(I9="DQ",0,IF(I9="DNF",1,IF(AND(ISNUMBER(I9),I9&gt;59),1,_xlfn.XLOOKUP(I9,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3498,7 +3529,7 @@
       </c>
       <c r="Q9" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="R9" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3506,7 +3537,7 @@
       </c>
       <c r="S9" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>22</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">
@@ -3529,9 +3560,12 @@
         <f>IF(E10="","",IF(E10="DNS",0,IF(E10="DQ",0,IF(E10="DNF",1,IF(AND(ISNUMBER(E10),E10&gt;59),1,_xlfn.XLOOKUP(E10,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="3" t="str">
+      <c r="G10" s="3">
+        <v>28</v>
+      </c>
+      <c r="H10" s="3">
         <f>IF(G10="","",IF(G10="DNS",0,IF(G10="DQ",0,IF(G10="DNF",1,IF(AND(ISNUMBER(G10),G10&gt;59),1,_xlfn.XLOOKUP(G10,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="J10" s="3" t="str">
         <f>IF(I10="","",IF(I10="DNS",0,IF(I10="DQ",0,IF(I10="DNF",1,IF(AND(ISNUMBER(I10),I10&gt;59),1,_xlfn.XLOOKUP(I10,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3551,7 +3585,7 @@
       </c>
       <c r="Q10" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R10" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3559,7 +3593,7 @@
       </c>
       <c r="S10" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.4">
@@ -3582,9 +3616,12 @@
         <f>IF(E11="","",IF(E11="DNS",0,IF(E11="DQ",0,IF(E11="DNF",1,IF(AND(ISNUMBER(E11),E11&gt;59),1,_xlfn.XLOOKUP(E11,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>36</v>
       </c>
-      <c r="H11" s="3" t="str">
+      <c r="G11" s="3">
+        <v>21</v>
+      </c>
+      <c r="H11" s="3">
         <f>IF(G11="","",IF(G11="DNS",0,IF(G11="DQ",0,IF(G11="DNF",1,IF(AND(ISNUMBER(G11),G11&gt;59),1,_xlfn.XLOOKUP(G11,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="J11" s="3" t="str">
         <f>IF(I11="","",IF(I11="DNS",0,IF(I11="DQ",0,IF(I11="DNF",1,IF(AND(ISNUMBER(I11),I11&gt;59),1,_xlfn.XLOOKUP(I11,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3604,7 +3641,7 @@
       </c>
       <c r="Q11" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="R11" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3612,7 +3649,7 @@
       </c>
       <c r="S11" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.4">
@@ -3635,9 +3672,12 @@
         <f>IF(E12="","",IF(E12="DNS",0,IF(E12="DQ",0,IF(E12="DNF",1,IF(AND(ISNUMBER(E12),E12&gt;59),1,_xlfn.XLOOKUP(E12,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>29</v>
       </c>
-      <c r="H12" s="3" t="str">
+      <c r="G12" s="3">
+        <v>40</v>
+      </c>
+      <c r="H12" s="3">
         <f>IF(G12="","",IF(G12="DNS",0,IF(G12="DQ",0,IF(G12="DNF",1,IF(AND(ISNUMBER(G12),G12&gt;59),1,_xlfn.XLOOKUP(G12,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="J12" s="3" t="str">
         <f>IF(I12="","",IF(I12="DNS",0,IF(I12="DQ",0,IF(I12="DNF",1,IF(AND(ISNUMBER(I12),I12&gt;59),1,_xlfn.XLOOKUP(I12,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3657,15 +3697,15 @@
       </c>
       <c r="Q12" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="R12" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="S12" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.4">
@@ -3688,9 +3728,12 @@
         <f>IF(E13="","",IF(E13="DNS",0,IF(E13="DQ",0,IF(E13="DNF",1,IF(AND(ISNUMBER(E13),E13&gt;59),1,_xlfn.XLOOKUP(E13,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="3" t="str">
+      <c r="G13" s="3">
+        <v>4</v>
+      </c>
+      <c r="H13" s="3">
         <f>IF(G13="","",IF(G13="DNS",0,IF(G13="DQ",0,IF(G13="DNF",1,IF(AND(ISNUMBER(G13),G13&gt;59),1,_xlfn.XLOOKUP(G13,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>85</v>
       </c>
       <c r="J13" s="3" t="str">
         <f>IF(I13="","",IF(I13="DNS",0,IF(I13="DQ",0,IF(I13="DNF",1,IF(AND(ISNUMBER(I13),I13&gt;59),1,_xlfn.XLOOKUP(I13,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3710,7 +3753,7 @@
       </c>
       <c r="Q13" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R13" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3718,7 +3761,7 @@
       </c>
       <c r="S13" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.4">
@@ -3741,9 +3784,12 @@
         <f>IF(E14="","",IF(E14="DNS",0,IF(E14="DQ",0,IF(E14="DNF",1,IF(AND(ISNUMBER(E14),E14&gt;59),1,_xlfn.XLOOKUP(E14,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="str">
+      <c r="G14" s="3">
+        <v>17</v>
+      </c>
+      <c r="H14" s="3">
         <f>IF(G14="","",IF(G14="DNS",0,IF(G14="DQ",0,IF(G14="DNF",1,IF(AND(ISNUMBER(G14),G14&gt;59),1,_xlfn.XLOOKUP(G14,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="J14" s="3" t="str">
         <f>IF(I14="","",IF(I14="DNS",0,IF(I14="DQ",0,IF(I14="DNF",1,IF(AND(ISNUMBER(I14),I14&gt;59),1,_xlfn.XLOOKUP(I14,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3763,7 +3809,7 @@
       </c>
       <c r="Q14" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R14" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3771,7 +3817,7 @@
       </c>
       <c r="S14" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.4">
@@ -3794,9 +3840,12 @@
         <f>IF(E15="","",IF(E15="DNS",0,IF(E15="DQ",0,IF(E15="DNF",1,IF(AND(ISNUMBER(E15),E15&gt;59),1,_xlfn.XLOOKUP(E15,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="str">
+      <c r="G15" s="3">
+        <v>41</v>
+      </c>
+      <c r="H15" s="3">
         <f>IF(G15="","",IF(G15="DNS",0,IF(G15="DQ",0,IF(G15="DNF",1,IF(AND(ISNUMBER(G15),G15&gt;59),1,_xlfn.XLOOKUP(G15,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="J15" s="3" t="str">
         <f>IF(I15="","",IF(I15="DNS",0,IF(I15="DQ",0,IF(I15="DNF",1,IF(AND(ISNUMBER(I15),I15&gt;59),1,_xlfn.XLOOKUP(I15,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3816,7 +3865,7 @@
       </c>
       <c r="Q15" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R15" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -3824,7 +3873,7 @@
       </c>
       <c r="S15" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.4">
@@ -3847,9 +3896,12 @@
         <f>IF(E16="","",IF(E16="DNS",0,IF(E16="DQ",0,IF(E16="DNF",1,IF(AND(ISNUMBER(E16),E16&gt;59),1,_xlfn.XLOOKUP(E16,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="3" t="str">
+      <c r="G16" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H16" s="3">
         <f>IF(G16="","",IF(G16="DNS",0,IF(G16="DQ",0,IF(G16="DNF",1,IF(AND(ISNUMBER(G16),G16&gt;59),1,_xlfn.XLOOKUP(G16,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="str">
         <f>IF(I16="","",IF(I16="DNS",0,IF(I16="DQ",0,IF(I16="DNF",1,IF(AND(ISNUMBER(I16),I16&gt;59),1,_xlfn.XLOOKUP(I16,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3900,9 +3952,12 @@
         <f>IF(E17="","",IF(E17="DNS",0,IF(E17="DQ",0,IF(E17="DNF",1,IF(AND(ISNUMBER(E17),E17&gt;59),1,_xlfn.XLOOKUP(E17,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>70</v>
       </c>
-      <c r="H17" s="3" t="str">
+      <c r="G17" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H17" s="3">
         <f>IF(G17="","",IF(G17="DNS",0,IF(G17="DQ",0,IF(G17="DNF",1,IF(AND(ISNUMBER(G17),G17&gt;59),1,_xlfn.XLOOKUP(G17,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="str">
         <f>IF(I17="","",IF(I17="DNS",0,IF(I17="DQ",0,IF(I17="DNF",1,IF(AND(ISNUMBER(I17),I17&gt;59),1,_xlfn.XLOOKUP(I17,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3926,7 +3981,7 @@
       </c>
       <c r="R17" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -3953,9 +4008,12 @@
         <f>IF(E18="","",IF(E18="DNS",0,IF(E18="DQ",0,IF(E18="DNF",1,IF(AND(ISNUMBER(E18),E18&gt;59),1,_xlfn.XLOOKUP(E18,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="3" t="str">
+      <c r="G18" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H18" s="3">
         <f>IF(G18="","",IF(G18="DNS",0,IF(G18="DQ",0,IF(G18="DNF",1,IF(AND(ISNUMBER(G18),G18&gt;59),1,_xlfn.XLOOKUP(G18,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="str">
         <f>IF(I18="","",IF(I18="DNS",0,IF(I18="DQ",0,IF(I18="DNF",1,IF(AND(ISNUMBER(I18),I18&gt;59),1,_xlfn.XLOOKUP(I18,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4006,9 +4064,12 @@
         <f>IF(E19="","",IF(E19="DNS",0,IF(E19="DQ",0,IF(E19="DNF",1,IF(AND(ISNUMBER(E19),E19&gt;59),1,_xlfn.XLOOKUP(E19,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="3" t="str">
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3">
         <f>IF(G19="","",IF(G19="DNS",0,IF(G19="DQ",0,IF(G19="DNF",1,IF(AND(ISNUMBER(G19),G19&gt;59),1,_xlfn.XLOOKUP(G19,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="J19" s="3" t="str">
         <f>IF(I19="","",IF(I19="DNS",0,IF(I19="DQ",0,IF(I19="DNF",1,IF(AND(ISNUMBER(I19),I19&gt;59),1,_xlfn.XLOOKUP(I19,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4028,7 +4089,7 @@
       </c>
       <c r="Q19" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R19" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4036,7 +4097,7 @@
       </c>
       <c r="S19" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.4">
@@ -4059,9 +4120,12 @@
         <f>IF(E20="","",IF(E20="DNS",0,IF(E20="DQ",0,IF(E20="DNF",1,IF(AND(ISNUMBER(E20),E20&gt;59),1,_xlfn.XLOOKUP(E20,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>90</v>
       </c>
-      <c r="H20" s="3" t="str">
+      <c r="G20" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H20" s="3">
         <f>IF(G20="","",IF(G20="DNS",0,IF(G20="DQ",0,IF(G20="DNF",1,IF(AND(ISNUMBER(G20),G20&gt;59),1,_xlfn.XLOOKUP(G20,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="str">
         <f>IF(I20="","",IF(I20="DNS",0,IF(I20="DQ",0,IF(I20="DNF",1,IF(AND(ISNUMBER(I20),I20&gt;59),1,_xlfn.XLOOKUP(I20,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4085,7 +4149,7 @@
       </c>
       <c r="R20" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -4112,9 +4176,12 @@
         <f>IF(E21="","",IF(E21="DNS",0,IF(E21="DQ",0,IF(E21="DNF",1,IF(AND(ISNUMBER(E21),E21&gt;59),1,_xlfn.XLOOKUP(E21,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>19</v>
       </c>
-      <c r="H21" s="3" t="str">
+      <c r="G21" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H21" s="3">
         <f>IF(G21="","",IF(G21="DNS",0,IF(G21="DQ",0,IF(G21="DNF",1,IF(AND(ISNUMBER(G21),G21&gt;59),1,_xlfn.XLOOKUP(G21,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="str">
         <f>IF(I21="","",IF(I21="DNS",0,IF(I21="DQ",0,IF(I21="DNF",1,IF(AND(ISNUMBER(I21),I21&gt;59),1,_xlfn.XLOOKUP(I21,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4138,7 +4205,7 @@
       </c>
       <c r="R21" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -4165,9 +4232,12 @@
         <f>IF(E22="","",IF(E22="DNS",0,IF(E22="DQ",0,IF(E22="DNF",1,IF(AND(ISNUMBER(E22),E22&gt;59),1,_xlfn.XLOOKUP(E22,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>44</v>
       </c>
-      <c r="H22" s="3" t="str">
+      <c r="G22" s="3">
+        <v>12</v>
+      </c>
+      <c r="H22" s="3">
         <f>IF(G22="","",IF(G22="DNS",0,IF(G22="DQ",0,IF(G22="DNF",1,IF(AND(ISNUMBER(G22),G22&gt;59),1,_xlfn.XLOOKUP(G22,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>51</v>
       </c>
       <c r="J22" s="3" t="str">
         <f>IF(I22="","",IF(I22="DNS",0,IF(I22="DQ",0,IF(I22="DNF",1,IF(AND(ISNUMBER(I22),I22&gt;59),1,_xlfn.XLOOKUP(I22,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4187,7 +4257,7 @@
       </c>
       <c r="Q22" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="R22" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4195,7 +4265,7 @@
       </c>
       <c r="S22" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>44</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.4">
@@ -4218,9 +4288,12 @@
         <f>IF(E23="","",IF(E23="DNS",0,IF(E23="DQ",0,IF(E23="DNF",1,IF(AND(ISNUMBER(E23),E23&gt;59),1,_xlfn.XLOOKUP(E23,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>27</v>
       </c>
-      <c r="H23" s="3" t="str">
+      <c r="G23" s="3">
+        <v>6</v>
+      </c>
+      <c r="H23" s="3">
         <f>IF(G23="","",IF(G23="DNS",0,IF(G23="DQ",0,IF(G23="DNF",1,IF(AND(ISNUMBER(G23),G23&gt;59),1,_xlfn.XLOOKUP(G23,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="J23" s="3" t="str">
         <f>IF(I23="","",IF(I23="DNS",0,IF(I23="DQ",0,IF(I23="DNF",1,IF(AND(ISNUMBER(I23),I23&gt;59),1,_xlfn.XLOOKUP(I23,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4240,7 +4313,7 @@
       </c>
       <c r="Q23" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="R23" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4248,7 +4321,7 @@
       </c>
       <c r="S23" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>27</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.4">
@@ -4271,9 +4344,12 @@
         <f>IF(E24="","",IF(E24="DNS",0,IF(E24="DQ",0,IF(E24="DNF",1,IF(AND(ISNUMBER(E24),E24&gt;59),1,_xlfn.XLOOKUP(E24,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>51</v>
       </c>
-      <c r="H24" s="3" t="str">
+      <c r="G24" s="3">
+        <v>39</v>
+      </c>
+      <c r="H24" s="3">
         <f>IF(G24="","",IF(G24="DNS",0,IF(G24="DQ",0,IF(G24="DNF",1,IF(AND(ISNUMBER(G24),G24&gt;59),1,_xlfn.XLOOKUP(G24,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="J24" s="3" t="str">
         <f>IF(I24="","",IF(I24="DNS",0,IF(I24="DQ",0,IF(I24="DNF",1,IF(AND(ISNUMBER(I24),I24&gt;59),1,_xlfn.XLOOKUP(I24,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4293,15 +4369,15 @@
       </c>
       <c r="Q24" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="R24" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="S24" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.4">
@@ -4324,9 +4400,12 @@
         <f>IF(E25="","",IF(E25="DNS",0,IF(E25="DQ",0,IF(E25="DNF",1,IF(AND(ISNUMBER(E25),E25&gt;59),1,_xlfn.XLOOKUP(E25,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>1</v>
       </c>
-      <c r="H25" s="3" t="str">
+      <c r="G25" s="3">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3">
         <f>IF(G25="","",IF(G25="DNS",0,IF(G25="DQ",0,IF(G25="DNF",1,IF(AND(ISNUMBER(G25),G25&gt;59),1,_xlfn.XLOOKUP(G25,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="J25" s="3" t="str">
         <f>IF(I25="","",IF(I25="DNS",0,IF(I25="DQ",0,IF(I25="DNF",1,IF(AND(ISNUMBER(I25),I25&gt;59),1,_xlfn.XLOOKUP(I25,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4346,7 +4425,7 @@
       </c>
       <c r="Q25" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="R25" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4354,7 +4433,7 @@
       </c>
       <c r="S25" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.4">
@@ -4377,9 +4456,12 @@
         <f>IF(E26="","",IF(E26="DNS",0,IF(E26="DQ",0,IF(E26="DNF",1,IF(AND(ISNUMBER(E26),E26&gt;59),1,_xlfn.XLOOKUP(E26,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>60</v>
       </c>
-      <c r="H26" s="3" t="str">
+      <c r="G26" s="3">
+        <v>42</v>
+      </c>
+      <c r="H26" s="3">
         <f>IF(G26="","",IF(G26="DNS",0,IF(G26="DQ",0,IF(G26="DNF",1,IF(AND(ISNUMBER(G26),G26&gt;59),1,_xlfn.XLOOKUP(G26,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="J26" s="3" t="str">
         <f>IF(I26="","",IF(I26="DNS",0,IF(I26="DQ",0,IF(I26="DNF",1,IF(AND(ISNUMBER(I26),I26&gt;59),1,_xlfn.XLOOKUP(I26,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4399,15 +4481,15 @@
       </c>
       <c r="Q26" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="R26" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="S26" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.4">
@@ -4430,9 +4512,12 @@
         <f>IF(E27="","",IF(E27="DNS",0,IF(E27="DQ",0,IF(E27="DNF",1,IF(AND(ISNUMBER(E27),E27&gt;59),1,_xlfn.XLOOKUP(E27,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>26</v>
       </c>
-      <c r="H27" s="3" t="str">
+      <c r="G27" s="3">
+        <v>36</v>
+      </c>
+      <c r="H27" s="3">
         <f>IF(G27="","",IF(G27="DNS",0,IF(G27="DQ",0,IF(G27="DNF",1,IF(AND(ISNUMBER(G27),G27&gt;59),1,_xlfn.XLOOKUP(G27,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="J27" s="3" t="str">
         <f>IF(I27="","",IF(I27="DNS",0,IF(I27="DQ",0,IF(I27="DNF",1,IF(AND(ISNUMBER(I27),I27&gt;59),1,_xlfn.XLOOKUP(I27,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4452,15 +4537,15 @@
       </c>
       <c r="Q27" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="R27" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="S27" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.4">
@@ -4483,9 +4568,12 @@
         <f>IF(E28="","",IF(E28="DNS",0,IF(E28="DQ",0,IF(E28="DNF",1,IF(AND(ISNUMBER(E28),E28&gt;59),1,_xlfn.XLOOKUP(E28,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="3" t="str">
+      <c r="G28" s="3">
+        <v>19</v>
+      </c>
+      <c r="H28" s="3">
         <f>IF(G28="","",IF(G28="DNS",0,IF(G28="DQ",0,IF(G28="DNF",1,IF(AND(ISNUMBER(G28),G28&gt;59),1,_xlfn.XLOOKUP(G28,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="J28" s="3" t="str">
         <f>IF(I28="","",IF(I28="DNS",0,IF(I28="DQ",0,IF(I28="DNF",1,IF(AND(ISNUMBER(I28),I28&gt;59),1,_xlfn.XLOOKUP(I28,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4505,7 +4593,7 @@
       </c>
       <c r="Q28" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R28" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4513,7 +4601,7 @@
       </c>
       <c r="S28" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.4">
@@ -4536,9 +4624,12 @@
         <f>IF(E29="","",IF(E29="DNS",0,IF(E29="DQ",0,IF(E29="DNF",1,IF(AND(ISNUMBER(E29),E29&gt;59),1,_xlfn.XLOOKUP(E29,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="str">
+      <c r="G29" s="3">
+        <v>14</v>
+      </c>
+      <c r="H29" s="3">
         <f>IF(G29="","",IF(G29="DNS",0,IF(G29="DQ",0,IF(G29="DNF",1,IF(AND(ISNUMBER(G29),G29&gt;59),1,_xlfn.XLOOKUP(G29,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="J29" s="3" t="str">
         <f>IF(I29="","",IF(I29="DNS",0,IF(I29="DQ",0,IF(I29="DNF",1,IF(AND(ISNUMBER(I29),I29&gt;59),1,_xlfn.XLOOKUP(I29,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4558,7 +4649,7 @@
       </c>
       <c r="Q29" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="R29" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4566,7 +4657,7 @@
       </c>
       <c r="S29" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.4">
@@ -4589,9 +4680,12 @@
         <f>IF(E30="","",IF(E30="DNS",0,IF(E30="DQ",0,IF(E30="DNF",1,IF(AND(ISNUMBER(E30),E30&gt;59),1,_xlfn.XLOOKUP(E30,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>100</v>
       </c>
-      <c r="H30" s="3" t="str">
+      <c r="G30" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H30" s="3">
         <f>IF(G30="","",IF(G30="DNS",0,IF(G30="DQ",0,IF(G30="DNF",1,IF(AND(ISNUMBER(G30),G30&gt;59),1,_xlfn.XLOOKUP(G30,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="str">
         <f>IF(I30="","",IF(I30="DNS",0,IF(I30="DQ",0,IF(I30="DNF",1,IF(AND(ISNUMBER(I30),I30&gt;59),1,_xlfn.XLOOKUP(I30,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4615,7 +4709,7 @@
       </c>
       <c r="R30" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -4642,9 +4736,12 @@
         <f>IF(E31="","",IF(E31="DNS",0,IF(E31="DQ",0,IF(E31="DNF",1,IF(AND(ISNUMBER(E31),E31&gt;59),1,_xlfn.XLOOKUP(E31,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>18</v>
       </c>
-      <c r="H31" s="3" t="str">
+      <c r="G31" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H31" s="3">
         <f>IF(G31="","",IF(G31="DNS",0,IF(G31="DQ",0,IF(G31="DNF",1,IF(AND(ISNUMBER(G31),G31&gt;59),1,_xlfn.XLOOKUP(G31,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="str">
         <f>IF(I31="","",IF(I31="DNS",0,IF(I31="DQ",0,IF(I31="DNF",1,IF(AND(ISNUMBER(I31),I31&gt;59),1,_xlfn.XLOOKUP(I31,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4668,7 +4765,7 @@
       </c>
       <c r="R31" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S31" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -4695,9 +4792,12 @@
         <f>IF(E32="","",IF(E32="DNS",0,IF(E32="DQ",0,IF(E32="DNF",1,IF(AND(ISNUMBER(E32),E32&gt;59),1,_xlfn.XLOOKUP(E32,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>28</v>
       </c>
-      <c r="H32" s="3" t="str">
+      <c r="G32" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H32" s="3">
         <f>IF(G32="","",IF(G32="DNS",0,IF(G32="DQ",0,IF(G32="DNF",1,IF(AND(ISNUMBER(G32),G32&gt;59),1,_xlfn.XLOOKUP(G32,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="str">
         <f>IF(I32="","",IF(I32="DNS",0,IF(I32="DQ",0,IF(I32="DNF",1,IF(AND(ISNUMBER(I32),I32&gt;59),1,_xlfn.XLOOKUP(I32,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4721,7 +4821,7 @@
       </c>
       <c r="R32" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -4748,9 +4848,12 @@
         <f>IF(E33="","",IF(E33="DNS",0,IF(E33="DQ",0,IF(E33="DNF",1,IF(AND(ISNUMBER(E33),E33&gt;59),1,_xlfn.XLOOKUP(E33,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>25</v>
       </c>
-      <c r="H33" s="3" t="str">
+      <c r="G33" s="3">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3">
         <f>IF(G33="","",IF(G33="DNS",0,IF(G33="DQ",0,IF(G33="DNF",1,IF(AND(ISNUMBER(G33),G33&gt;59),1,_xlfn.XLOOKUP(G33,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="J33" s="3" t="str">
         <f>IF(I33="","",IF(I33="DNS",0,IF(I33="DQ",0,IF(I33="DNF",1,IF(AND(ISNUMBER(I33),I33&gt;59),1,_xlfn.XLOOKUP(I33,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4770,7 +4873,7 @@
       </c>
       <c r="Q33" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="R33" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4778,7 +4881,7 @@
       </c>
       <c r="S33" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.4">
@@ -4801,9 +4904,12 @@
         <f>IF(E34="","",IF(E34="DNS",0,IF(E34="DQ",0,IF(E34="DNF",1,IF(AND(ISNUMBER(E34),E34&gt;59),1,_xlfn.XLOOKUP(E34,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>47</v>
       </c>
-      <c r="H34" s="3" t="str">
+      <c r="G34" s="3">
+        <v>38</v>
+      </c>
+      <c r="H34" s="3">
         <f>IF(G34="","",IF(G34="DNS",0,IF(G34="DQ",0,IF(G34="DNF",1,IF(AND(ISNUMBER(G34),G34&gt;59),1,_xlfn.XLOOKUP(G34,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="J34" s="3" t="str">
         <f>IF(I34="","",IF(I34="DNS",0,IF(I34="DQ",0,IF(I34="DNF",1,IF(AND(ISNUMBER(I34),I34&gt;59),1,_xlfn.XLOOKUP(I34,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4823,15 +4929,15 @@
       </c>
       <c r="Q34" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="R34" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="S34" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.4">
@@ -4854,9 +4960,12 @@
         <f>IF(E35="","",IF(E35="DNS",0,IF(E35="DQ",0,IF(E35="DNF",1,IF(AND(ISNUMBER(E35),E35&gt;59),1,_xlfn.XLOOKUP(E35,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>38</v>
       </c>
-      <c r="H35" s="3" t="str">
+      <c r="G35" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H35" s="3">
         <f>IF(G35="","",IF(G35="DNS",0,IF(G35="DQ",0,IF(G35="DNF",1,IF(AND(ISNUMBER(G35),G35&gt;59),1,_xlfn.XLOOKUP(G35,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="str">
         <f>IF(I35="","",IF(I35="DNS",0,IF(I35="DQ",0,IF(I35="DNF",1,IF(AND(ISNUMBER(I35),I35&gt;59),1,_xlfn.XLOOKUP(I35,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4880,7 +4989,7 @@
       </c>
       <c r="R35" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -4907,9 +5016,12 @@
         <f>IF(E36="","",IF(E36="DNS",0,IF(E36="DQ",0,IF(E36="DNF",1,IF(AND(ISNUMBER(E36),E36&gt;59),1,_xlfn.XLOOKUP(E36,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>53</v>
       </c>
-      <c r="H36" s="3" t="str">
+      <c r="G36" s="3">
+        <v>29</v>
+      </c>
+      <c r="H36" s="3">
         <f>IF(G36="","",IF(G36="DNS",0,IF(G36="DQ",0,IF(G36="DNF",1,IF(AND(ISNUMBER(G36),G36&gt;59),1,_xlfn.XLOOKUP(G36,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="J36" s="3" t="str">
         <f>IF(I36="","",IF(I36="DNS",0,IF(I36="DQ",0,IF(I36="DNF",1,IF(AND(ISNUMBER(I36),I36&gt;59),1,_xlfn.XLOOKUP(I36,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4929,15 +5041,15 @@
       </c>
       <c r="Q36" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="R36" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="S36" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>53</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.4">
@@ -4960,9 +5072,12 @@
         <f>IF(E37="","",IF(E37="DNS",0,IF(E37="DQ",0,IF(E37="DNF",1,IF(AND(ISNUMBER(E37),E37&gt;59),1,_xlfn.XLOOKUP(E37,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>30</v>
       </c>
-      <c r="H37" s="3" t="str">
+      <c r="G37" s="3">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3">
         <f>IF(G37="","",IF(G37="DNS",0,IF(G37="DQ",0,IF(G37="DNF",1,IF(AND(ISNUMBER(G37),G37&gt;59),1,_xlfn.XLOOKUP(G37,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="J37" s="3" t="str">
         <f>IF(I37="","",IF(I37="DNS",0,IF(I37="DQ",0,IF(I37="DNF",1,IF(AND(ISNUMBER(I37),I37&gt;59),1,_xlfn.XLOOKUP(I37,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4982,7 +5097,7 @@
       </c>
       <c r="Q37" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="R37" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -4990,7 +5105,7 @@
       </c>
       <c r="S37" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>30</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.4">
@@ -5013,9 +5128,12 @@
         <f>IF(E38="","",IF(E38="DNS",0,IF(E38="DQ",0,IF(E38="DNF",1,IF(AND(ISNUMBER(E38),E38&gt;59),1,_xlfn.XLOOKUP(E38,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H38" s="3" t="str">
+      <c r="G38" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H38" s="3">
         <f>IF(G38="","",IF(G38="DNS",0,IF(G38="DQ",0,IF(G38="DNF",1,IF(AND(ISNUMBER(G38),G38&gt;59),1,_xlfn.XLOOKUP(G38,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="str">
         <f>IF(I38="","",IF(I38="DNS",0,IF(I38="DQ",0,IF(I38="DNF",1,IF(AND(ISNUMBER(I38),I38&gt;59),1,_xlfn.XLOOKUP(I38,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5066,9 +5184,12 @@
         <f>IF(E39="","",IF(E39="DNS",0,IF(E39="DQ",0,IF(E39="DNF",1,IF(AND(ISNUMBER(E39),E39&gt;59),1,_xlfn.XLOOKUP(E39,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>65</v>
       </c>
-      <c r="H39" s="3" t="str">
+      <c r="G39" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H39" s="3">
         <f>IF(G39="","",IF(G39="DNS",0,IF(G39="DQ",0,IF(G39="DNF",1,IF(AND(ISNUMBER(G39),G39&gt;59),1,_xlfn.XLOOKUP(G39,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="str">
         <f>IF(I39="","",IF(I39="DNS",0,IF(I39="DQ",0,IF(I39="DNF",1,IF(AND(ISNUMBER(I39),I39&gt;59),1,_xlfn.XLOOKUP(I39,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5092,7 +5213,7 @@
       </c>
       <c r="R39" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="S39" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -5119,9 +5240,12 @@
         <f>IF(E40="","",IF(E40="DNS",0,IF(E40="DQ",0,IF(E40="DNF",1,IF(AND(ISNUMBER(E40),E40&gt;59),1,_xlfn.XLOOKUP(E40,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>37</v>
       </c>
-      <c r="H40" s="3" t="str">
+      <c r="G40" s="3">
+        <v>31</v>
+      </c>
+      <c r="H40" s="3">
         <f>IF(G40="","",IF(G40="DNS",0,IF(G40="DQ",0,IF(G40="DNF",1,IF(AND(ISNUMBER(G40),G40&gt;59),1,_xlfn.XLOOKUP(G40,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="J40" s="3" t="str">
         <f>IF(I40="","",IF(I40="DNS",0,IF(I40="DQ",0,IF(I40="DNF",1,IF(AND(ISNUMBER(I40),I40&gt;59),1,_xlfn.XLOOKUP(I40,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5141,15 +5265,15 @@
       </c>
       <c r="Q40" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="R40" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S40" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.4">
@@ -5172,9 +5296,12 @@
         <f>IF(E41="","",IF(E41="DNS",0,IF(E41="DQ",0,IF(E41="DNF",1,IF(AND(ISNUMBER(E41),E41&gt;59),1,_xlfn.XLOOKUP(E41,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>55</v>
       </c>
-      <c r="H41" s="3" t="str">
+      <c r="G41" s="3">
+        <v>30</v>
+      </c>
+      <c r="H41" s="3">
         <f>IF(G41="","",IF(G41="DNS",0,IF(G41="DQ",0,IF(G41="DNF",1,IF(AND(ISNUMBER(G41),G41&gt;59),1,_xlfn.XLOOKUP(G41,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="J41" s="3" t="str">
         <f>IF(I41="","",IF(I41="DNS",0,IF(I41="DQ",0,IF(I41="DNF",1,IF(AND(ISNUMBER(I41),I41&gt;59),1,_xlfn.XLOOKUP(I41,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5194,15 +5321,15 @@
       </c>
       <c r="Q41" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="R41" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="S41" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>55</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.4">
@@ -5225,9 +5352,12 @@
         <f>IF(E42="","",IF(E42="DNS",0,IF(E42="DQ",0,IF(E42="DNF",1,IF(AND(ISNUMBER(E42),E42&gt;59),1,_xlfn.XLOOKUP(E42,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>32</v>
       </c>
-      <c r="H42" s="3" t="str">
+      <c r="G42" s="3">
+        <v>27</v>
+      </c>
+      <c r="H42" s="3">
         <f>IF(G42="","",IF(G42="DNS",0,IF(G42="DQ",0,IF(G42="DNF",1,IF(AND(ISNUMBER(G42),G42&gt;59),1,_xlfn.XLOOKUP(G42,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="J42" s="3" t="str">
         <f>IF(I42="","",IF(I42="DNS",0,IF(I42="DQ",0,IF(I42="DNF",1,IF(AND(ISNUMBER(I42),I42&gt;59),1,_xlfn.XLOOKUP(I42,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5247,7 +5377,7 @@
       </c>
       <c r="Q42" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="R42" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -5255,7 +5385,7 @@
       </c>
       <c r="S42" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.4">
@@ -5278,9 +5408,12 @@
         <f>IF(E43="","",IF(E43="DNS",0,IF(E43="DQ",0,IF(E43="DNF",1,IF(AND(ISNUMBER(E43),E43&gt;59),1,_xlfn.XLOOKUP(E43,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>80</v>
       </c>
-      <c r="H43" s="3" t="str">
+      <c r="G43" s="3">
+        <v>35</v>
+      </c>
+      <c r="H43" s="3">
         <f>IF(G43="","",IF(G43="DNS",0,IF(G43="DQ",0,IF(G43="DNF",1,IF(AND(ISNUMBER(G43),G43&gt;59),1,_xlfn.XLOOKUP(G43,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="J43" s="3" t="str">
         <f>IF(I43="","",IF(I43="DNS",0,IF(I43="DQ",0,IF(I43="DNF",1,IF(AND(ISNUMBER(I43),I43&gt;59),1,_xlfn.XLOOKUP(I43,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5300,15 +5433,15 @@
       </c>
       <c r="Q43" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="R43" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="S43" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>80</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.4">
@@ -5331,9 +5464,12 @@
         <f>IF(E44="","",IF(E44="DNS",0,IF(E44="DQ",0,IF(E44="DNF",1,IF(AND(ISNUMBER(E44),E44&gt;59),1,_xlfn.XLOOKUP(E44,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>31</v>
       </c>
-      <c r="H44" s="3" t="str">
+      <c r="G44" s="3">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3">
         <f>IF(G44="","",IF(G44="DNS",0,IF(G44="DQ",0,IF(G44="DNF",1,IF(AND(ISNUMBER(G44),G44&gt;59),1,_xlfn.XLOOKUP(G44,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="J44" s="3" t="str">
         <f>IF(I44="","",IF(I44="DNS",0,IF(I44="DQ",0,IF(I44="DNF",1,IF(AND(ISNUMBER(I44),I44&gt;59),1,_xlfn.XLOOKUP(I44,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5353,7 +5489,7 @@
       </c>
       <c r="Q44" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="R44" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -5361,7 +5497,7 @@
       </c>
       <c r="S44" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>31</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.4">
@@ -5384,9 +5520,12 @@
         <f>IF(E45="","",IF(E45="DNS",0,IF(E45="DQ",0,IF(E45="DNF",1,IF(AND(ISNUMBER(E45),E45&gt;59),1,_xlfn.XLOOKUP(E45,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>75</v>
       </c>
-      <c r="H45" s="3" t="str">
+      <c r="G45" s="3">
+        <v>46</v>
+      </c>
+      <c r="H45" s="3">
         <f>IF(G45="","",IF(G45="DNS",0,IF(G45="DQ",0,IF(G45="DNF",1,IF(AND(ISNUMBER(G45),G45&gt;59),1,_xlfn.XLOOKUP(G45,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="J45" s="3" t="str">
         <f>IF(I45="","",IF(I45="DNS",0,IF(I45="DQ",0,IF(I45="DNF",1,IF(AND(ISNUMBER(I45),I45&gt;59),1,_xlfn.XLOOKUP(I45,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5406,15 +5545,15 @@
       </c>
       <c r="Q45" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="R45" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="S45" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>75</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.4">
@@ -5437,9 +5576,12 @@
         <f>IF(E46="","",IF(E46="DNS",0,IF(E46="DQ",0,IF(E46="DNF",1,IF(AND(ISNUMBER(E46),E46&gt;59),1,_xlfn.XLOOKUP(E46,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>20</v>
       </c>
-      <c r="H46" s="3" t="str">
+      <c r="G46" s="3">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
         <f>IF(G46="","",IF(G46="DNS",0,IF(G46="DQ",0,IF(G46="DNF",1,IF(AND(ISNUMBER(G46),G46&gt;59),1,_xlfn.XLOOKUP(G46,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="J46" s="3" t="str">
         <f>IF(I46="","",IF(I46="DNS",0,IF(I46="DQ",0,IF(I46="DNF",1,IF(AND(ISNUMBER(I46),I46&gt;59),1,_xlfn.XLOOKUP(I46,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5459,7 +5601,7 @@
       </c>
       <c r="Q46" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="R46" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -5467,7 +5609,7 @@
       </c>
       <c r="S46" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.4">
@@ -5490,9 +5632,12 @@
         <f>IF(E47="","",IF(E47="DNS",0,IF(E47="DQ",0,IF(E47="DNF",1,IF(AND(ISNUMBER(E47),E47&gt;59),1,_xlfn.XLOOKUP(E47,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>33</v>
       </c>
-      <c r="H47" s="3" t="str">
+      <c r="G47" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H47" s="3">
         <f>IF(G47="","",IF(G47="DNS",0,IF(G47="DQ",0,IF(G47="DNF",1,IF(AND(ISNUMBER(G47),G47&gt;59),1,_xlfn.XLOOKUP(G47,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="str">
         <f>IF(I47="","",IF(I47="DNS",0,IF(I47="DQ",0,IF(I47="DNF",1,IF(AND(ISNUMBER(I47),I47&gt;59),1,_xlfn.XLOOKUP(I47,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5516,7 +5661,7 @@
       </c>
       <c r="R47" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -5543,9 +5688,12 @@
         <f>IF(E48="","",IF(E48="DNS",0,IF(E48="DQ",0,IF(E48="DNF",1,IF(AND(ISNUMBER(E48),E48&gt;59),1,_xlfn.XLOOKUP(E48,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>40</v>
       </c>
-      <c r="H48" s="3" t="str">
+      <c r="G48" s="3">
+        <v>7</v>
+      </c>
+      <c r="H48" s="3">
         <f>IF(G48="","",IF(G48="DNS",0,IF(G48="DQ",0,IF(G48="DNF",1,IF(AND(ISNUMBER(G48),G48&gt;59),1,_xlfn.XLOOKUP(G48,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="J48" s="3" t="str">
         <f>IF(I48="","",IF(I48="DNS",0,IF(I48="DQ",0,IF(I48="DNF",1,IF(AND(ISNUMBER(I48),I48&gt;59),1,_xlfn.XLOOKUP(I48,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5565,7 +5713,7 @@
       </c>
       <c r="Q48" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="R48" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -5573,7 +5721,7 @@
       </c>
       <c r="S48" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>40</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.4">
@@ -5596,9 +5744,12 @@
         <f>IF(E49="","",IF(E49="DNS",0,IF(E49="DQ",0,IF(E49="DNF",1,IF(AND(ISNUMBER(E49),E49&gt;59),1,_xlfn.XLOOKUP(E49,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>23</v>
       </c>
-      <c r="H49" s="3" t="str">
+      <c r="G49" s="3">
+        <v>43</v>
+      </c>
+      <c r="H49" s="3">
         <f>IF(G49="","",IF(G49="DNS",0,IF(G49="DQ",0,IF(G49="DNF",1,IF(AND(ISNUMBER(G49),G49&gt;59),1,_xlfn.XLOOKUP(G49,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="J49" s="3" t="str">
         <f>IF(I49="","",IF(I49="DNS",0,IF(I49="DQ",0,IF(I49="DNF",1,IF(AND(ISNUMBER(I49),I49&gt;59),1,_xlfn.XLOOKUP(I49,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5618,15 +5769,15 @@
       </c>
       <c r="Q49" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R49" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="S49" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.4">
@@ -5649,9 +5800,12 @@
         <f>IF(E50="","",IF(E50="DNS",0,IF(E50="DQ",0,IF(E50="DNF",1,IF(AND(ISNUMBER(E50),E50&gt;59),1,_xlfn.XLOOKUP(E50,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>41</v>
       </c>
-      <c r="H50" s="3" t="str">
+      <c r="G50" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H50" s="3">
         <f>IF(G50="","",IF(G50="DNS",0,IF(G50="DQ",0,IF(G50="DNF",1,IF(AND(ISNUMBER(G50),G50&gt;59),1,_xlfn.XLOOKUP(G50,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="str">
         <f>IF(I50="","",IF(I50="DNS",0,IF(I50="DQ",0,IF(I50="DNF",1,IF(AND(ISNUMBER(I50),I50&gt;59),1,_xlfn.XLOOKUP(I50,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5675,7 +5829,7 @@
       </c>
       <c r="R50" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S50" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -5702,9 +5856,12 @@
         <f>IF(E51="","",IF(E51="DNS",0,IF(E51="DQ",0,IF(E51="DNF",1,IF(AND(ISNUMBER(E51),E51&gt;59),1,_xlfn.XLOOKUP(E51,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>35</v>
       </c>
-      <c r="H51" s="3" t="str">
+      <c r="G51" s="3">
+        <v>24</v>
+      </c>
+      <c r="H51" s="3">
         <f>IF(G51="","",IF(G51="DNS",0,IF(G51="DQ",0,IF(G51="DNF",1,IF(AND(ISNUMBER(G51),G51&gt;59),1,_xlfn.XLOOKUP(G51,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>36</v>
       </c>
       <c r="J51" s="3" t="str">
         <f>IF(I51="","",IF(I51="DNS",0,IF(I51="DQ",0,IF(I51="DNF",1,IF(AND(ISNUMBER(I51),I51&gt;59),1,_xlfn.XLOOKUP(I51,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5724,7 +5881,7 @@
       </c>
       <c r="Q51" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="R51" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -5732,7 +5889,7 @@
       </c>
       <c r="S51" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.4">
@@ -5755,9 +5912,12 @@
         <f>IF(E52="","",IF(E52="DNS",0,IF(E52="DQ",0,IF(E52="DNF",1,IF(AND(ISNUMBER(E52),E52&gt;59),1,_xlfn.XLOOKUP(E52,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>34</v>
       </c>
-      <c r="H52" s="3" t="str">
+      <c r="G52" s="3">
+        <v>32</v>
+      </c>
+      <c r="H52" s="3">
         <f>IF(G52="","",IF(G52="DNS",0,IF(G52="DQ",0,IF(G52="DNF",1,IF(AND(ISNUMBER(G52),G52&gt;59),1,_xlfn.XLOOKUP(G52,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="J52" s="3" t="str">
         <f>IF(I52="","",IF(I52="DNS",0,IF(I52="DQ",0,IF(I52="DNF",1,IF(AND(ISNUMBER(I52),I52&gt;59),1,_xlfn.XLOOKUP(I52,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5777,15 +5937,15 @@
       </c>
       <c r="Q52" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="R52" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S52" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.4">
@@ -5808,9 +5968,12 @@
         <f>IF(E53="","",IF(E53="DNS",0,IF(E53="DQ",0,IF(E53="DNF",1,IF(AND(ISNUMBER(E53),E53&gt;59),1,_xlfn.XLOOKUP(E53,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H53" s="3" t="str">
+      <c r="G53" s="3">
+        <v>26</v>
+      </c>
+      <c r="H53" s="3">
         <f>IF(G53="","",IF(G53="DNS",0,IF(G53="DQ",0,IF(G53="DNF",1,IF(AND(ISNUMBER(G53),G53&gt;59),1,_xlfn.XLOOKUP(G53,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="J53" s="3" t="str">
         <f>IF(I53="","",IF(I53="DNS",0,IF(I53="DQ",0,IF(I53="DNF",1,IF(AND(ISNUMBER(I53),I53&gt;59),1,_xlfn.XLOOKUP(I53,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5830,7 +5993,7 @@
       </c>
       <c r="Q53" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R53" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -5838,7 +6001,7 @@
       </c>
       <c r="S53" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.4">
@@ -5861,9 +6024,12 @@
         <f>IF(E54="","",IF(E54="DNS",0,IF(E54="DQ",0,IF(E54="DNF",1,IF(AND(ISNUMBER(E54),E54&gt;59),1,_xlfn.XLOOKUP(E54,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H54" s="3" t="str">
+      <c r="G54" s="3">
+        <v>47</v>
+      </c>
+      <c r="H54" s="3">
         <f>IF(G54="","",IF(G54="DNS",0,IF(G54="DQ",0,IF(G54="DNF",1,IF(AND(ISNUMBER(G54),G54&gt;59),1,_xlfn.XLOOKUP(G54,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="J54" s="3" t="str">
         <f>IF(I54="","",IF(I54="DNS",0,IF(I54="DQ",0,IF(I54="DNF",1,IF(AND(ISNUMBER(I54),I54&gt;59),1,_xlfn.XLOOKUP(I54,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5883,7 +6049,7 @@
       </c>
       <c r="Q54" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R54" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -5891,7 +6057,7 @@
       </c>
       <c r="S54" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.4">
@@ -5914,9 +6080,12 @@
         <f>IF(E55="","",IF(E55="DNS",0,IF(E55="DQ",0,IF(E55="DNF",1,IF(AND(ISNUMBER(E55),E55&gt;59),1,_xlfn.XLOOKUP(E55,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>21</v>
       </c>
-      <c r="H55" s="3" t="str">
+      <c r="G55" s="3">
+        <v>45</v>
+      </c>
+      <c r="H55" s="3">
         <f>IF(G55="","",IF(G55="DNS",0,IF(G55="DQ",0,IF(G55="DNF",1,IF(AND(ISNUMBER(G55),G55&gt;59),1,_xlfn.XLOOKUP(G55,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="J55" s="3" t="str">
         <f>IF(I55="","",IF(I55="DNS",0,IF(I55="DQ",0,IF(I55="DNF",1,IF(AND(ISNUMBER(I55),I55&gt;59),1,_xlfn.XLOOKUP(I55,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5936,15 +6105,15 @@
       </c>
       <c r="Q55" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="R55" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="S55" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.4">
@@ -5967,9 +6136,12 @@
         <f>IF(E56="","",IF(E56="DNS",0,IF(E56="DQ",0,IF(E56="DNF",1,IF(AND(ISNUMBER(E56),E56&gt;59),1,_xlfn.XLOOKUP(E56,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H56" s="3" t="str">
+      <c r="G56" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H56" s="3">
         <f>IF(G56="","",IF(G56="DNS",0,IF(G56="DQ",0,IF(G56="DNF",1,IF(AND(ISNUMBER(G56),G56&gt;59),1,_xlfn.XLOOKUP(G56,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="str">
         <f>IF(I56="","",IF(I56="DNS",0,IF(I56="DQ",0,IF(I56="DNF",1,IF(AND(ISNUMBER(I56),I56&gt;59),1,_xlfn.XLOOKUP(I56,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6020,9 +6192,12 @@
         <f>IF(E57="","",IF(E57="DNS",0,IF(E57="DQ",0,IF(E57="DNF",1,IF(AND(ISNUMBER(E57),E57&gt;59),1,_xlfn.XLOOKUP(E57,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>49</v>
       </c>
-      <c r="H57" s="3" t="str">
+      <c r="G57" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H57" s="3">
         <f>IF(G57="","",IF(G57="DNS",0,IF(G57="DQ",0,IF(G57="DNF",1,IF(AND(ISNUMBER(G57),G57&gt;59),1,_xlfn.XLOOKUP(G57,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J57" s="3" t="str">
         <f>IF(I57="","",IF(I57="DNS",0,IF(I57="DQ",0,IF(I57="DNF",1,IF(AND(ISNUMBER(I57),I57&gt;59),1,_xlfn.XLOOKUP(I57,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6046,7 +6221,7 @@
       </c>
       <c r="R57" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
@@ -6073,9 +6248,12 @@
         <f>IF(E58="","",IF(E58="DNS",0,IF(E58="DQ",0,IF(E58="DNF",1,IF(AND(ISNUMBER(E58),E58&gt;59),1,_xlfn.XLOOKUP(E58,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>17</v>
       </c>
-      <c r="H58" s="3" t="str">
+      <c r="G58" s="3">
+        <v>33</v>
+      </c>
+      <c r="H58" s="3">
         <f>IF(G58="","",IF(G58="DNS",0,IF(G58="DQ",0,IF(G58="DNF",1,IF(AND(ISNUMBER(G58),G58&gt;59),1,_xlfn.XLOOKUP(G58,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="J58" s="3" t="str">
         <f>IF(I58="","",IF(I58="DNS",0,IF(I58="DQ",0,IF(I58="DNF",1,IF(AND(ISNUMBER(I58),I58&gt;59),1,_xlfn.XLOOKUP(I58,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6095,7 +6273,7 @@
       </c>
       <c r="Q58" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="R58" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -6103,7 +6281,7 @@
       </c>
       <c r="S58" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.4">
@@ -6126,9 +6304,12 @@
         <f>IF(E59="","",IF(E59="DNS",0,IF(E59="DQ",0,IF(E59="DNF",1,IF(AND(ISNUMBER(E59),E59&gt;59),1,_xlfn.XLOOKUP(E59,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="str">
+      <c r="G59" s="3">
+        <v>44</v>
+      </c>
+      <c r="H59" s="3">
         <f>IF(G59="","",IF(G59="DNS",0,IF(G59="DQ",0,IF(G59="DNF",1,IF(AND(ISNUMBER(G59),G59&gt;59),1,_xlfn.XLOOKUP(G59,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="J59" s="3" t="str">
         <f>IF(I59="","",IF(I59="DNS",0,IF(I59="DQ",0,IF(I59="DNF",1,IF(AND(ISNUMBER(I59),I59&gt;59),1,_xlfn.XLOOKUP(I59,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6148,7 +6329,7 @@
       </c>
       <c r="Q59" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R59" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -6156,7 +6337,7 @@
       </c>
       <c r="S59" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.4">
@@ -6179,9 +6360,12 @@
         <f>IF(E60="","",IF(E60="DNS",0,IF(E60="DQ",0,IF(E60="DNF",1,IF(AND(ISNUMBER(E60),E60&gt;59),1,_xlfn.XLOOKUP(E60,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H60" s="3" t="str">
+      <c r="G60" s="3">
+        <v>15</v>
+      </c>
+      <c r="H60" s="3">
         <f>IF(G60="","",IF(G60="DNS",0,IF(G60="DQ",0,IF(G60="DNF",1,IF(AND(ISNUMBER(G60),G60&gt;59),1,_xlfn.XLOOKUP(G60,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="J60" s="3" t="str">
         <f>IF(I60="","",IF(I60="DNS",0,IF(I60="DQ",0,IF(I60="DNF",1,IF(AND(ISNUMBER(I60),I60&gt;59),1,_xlfn.XLOOKUP(I60,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6201,7 +6385,7 @@
       </c>
       <c r="Q60" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R60" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -6209,7 +6393,7 @@
       </c>
       <c r="S60" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.4">
@@ -6232,9 +6416,12 @@
         <f>IF(E61="","",IF(E61="DNS",0,IF(E61="DQ",0,IF(E61="DNF",1,IF(AND(ISNUMBER(E61),E61&gt;59),1,_xlfn.XLOOKUP(E61,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="3" t="str">
+      <c r="G61" s="3">
+        <v>48</v>
+      </c>
+      <c r="H61" s="3">
         <f>IF(G61="","",IF(G61="DNS",0,IF(G61="DQ",0,IF(G61="DNF",1,IF(AND(ISNUMBER(G61),G61&gt;59),1,_xlfn.XLOOKUP(G61,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="J61" s="3" t="str">
         <f>IF(I61="","",IF(I61="DNS",0,IF(I61="DQ",0,IF(I61="DNF",1,IF(AND(ISNUMBER(I61),I61&gt;59),1,_xlfn.XLOOKUP(I61,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6254,7 +6441,7 @@
       </c>
       <c r="Q61" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R61" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -6262,7 +6449,7 @@
       </c>
       <c r="S61" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.4">
@@ -6285,9 +6472,12 @@
         <f>IF(E62="","",IF(E62="DNS",0,IF(E62="DQ",0,IF(E62="DNF",1,IF(AND(ISNUMBER(E62),E62&gt;59),1,_xlfn.XLOOKUP(E62,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H62" s="3" t="str">
+      <c r="G62" s="3">
+        <v>37</v>
+      </c>
+      <c r="H62" s="3">
         <f>IF(G62="","",IF(G62="DNS",0,IF(G62="DQ",0,IF(G62="DNF",1,IF(AND(ISNUMBER(G62),G62&gt;59),1,_xlfn.XLOOKUP(G62,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="J62" s="3" t="str">
         <f>IF(I62="","",IF(I62="DNS",0,IF(I62="DQ",0,IF(I62="DNF",1,IF(AND(ISNUMBER(I62),I62&gt;59),1,_xlfn.XLOOKUP(I62,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6307,7 +6497,7 @@
       </c>
       <c r="Q62" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R62" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -6315,7 +6505,7 @@
       </c>
       <c r="S62" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.4">
@@ -6338,9 +6528,12 @@
         <f>IF(E63="","",IF(E63="DNS",0,IF(E63="DQ",0,IF(E63="DNF",1,IF(AND(ISNUMBER(E63),E63&gt;59),1,_xlfn.XLOOKUP(E63,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H63" s="3" t="str">
+      <c r="G63" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H63" s="3">
         <f>IF(G63="","",IF(G63="DNS",0,IF(G63="DQ",0,IF(G63="DNF",1,IF(AND(ISNUMBER(G63),G63&gt;59),1,_xlfn.XLOOKUP(G63,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="str">
         <f>IF(I63="","",IF(I63="DNS",0,IF(I63="DQ",0,IF(I63="DNF",1,IF(AND(ISNUMBER(I63),I63&gt;59),1,_xlfn.XLOOKUP(I63,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6391,9 +6584,12 @@
         <f>IF(E64="","",IF(E64="DNS",0,IF(E64="DQ",0,IF(E64="DNF",1,IF(AND(ISNUMBER(E64),E64&gt;59),1,_xlfn.XLOOKUP(E64,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v>0</v>
       </c>
-      <c r="H64" s="3" t="str">
+      <c r="G64" s="3">
+        <v>5</v>
+      </c>
+      <c r="H64" s="3">
         <f>IF(G64="","",IF(G64="DNS",0,IF(G64="DQ",0,IF(G64="DNF",1,IF(AND(ISNUMBER(G64),G64&gt;59),1,_xlfn.XLOOKUP(G64,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="J64" s="3" t="str">
         <f>IF(I64="","",IF(I64="DNS",0,IF(I64="DQ",0,IF(I64="DNF",1,IF(AND(ISNUMBER(I64),I64&gt;59),1,_xlfn.XLOOKUP(I64,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6413,7 +6609,7 @@
       </c>
       <c r="Q64" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R64" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
@@ -6421,7 +6617,7 @@
       </c>
       <c r="S64" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.4">
@@ -6441,9 +6637,12 @@
         <f>IF(E65="","",IF(E65="DNS",0,IF(E65="DQ",0,IF(E65="DNF",1,IF(AND(ISNUMBER(E65),E65&gt;59),1,_xlfn.XLOOKUP(E65,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="H65" s="3" t="str">
+      <c r="G65" s="3">
+        <v>18</v>
+      </c>
+      <c r="H65" s="3">
         <f>IF(G65="","",IF(G65="DNS",0,IF(G65="DQ",0,IF(G65="DNF",1,IF(AND(ISNUMBER(G65),G65&gt;59),1,_xlfn.XLOOKUP(G65,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="J65" s="3" t="str">
         <f>IF(I65="","",IF(I65="DNS",0,IF(I65="DQ",0,IF(I65="DNF",1,IF(AND(ISNUMBER(I65),I65&gt;59),1,_xlfn.XLOOKUP(I65,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6463,15 +6662,15 @@
       </c>
       <c r="Q65" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R65" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S65" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.4">
@@ -6491,9 +6690,12 @@
         <f>IF(E66="","",IF(E66="DNS",0,IF(E66="DQ",0,IF(E66="DNF",1,IF(AND(ISNUMBER(E66),E66&gt;59),1,_xlfn.XLOOKUP(E66,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="H66" s="3" t="str">
+      <c r="G66" s="3">
+        <v>22</v>
+      </c>
+      <c r="H66" s="3">
         <f>IF(G66="","",IF(G66="DNS",0,IF(G66="DQ",0,IF(G66="DNF",1,IF(AND(ISNUMBER(G66),G66&gt;59),1,_xlfn.XLOOKUP(G66,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="J66" s="3" t="str">
         <f>IF(I66="","",IF(I66="DNS",0,IF(I66="DQ",0,IF(I66="DNF",1,IF(AND(ISNUMBER(I66),I66&gt;59),1,_xlfn.XLOOKUP(I66,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6513,15 +6715,15 @@
       </c>
       <c r="Q66" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R66" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S66" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.4">
@@ -6541,9 +6743,12 @@
         <f>IF(E67="","",IF(E67="DNS",0,IF(E67="DQ",0,IF(E67="DNF",1,IF(AND(ISNUMBER(E67),E67&gt;59),1,_xlfn.XLOOKUP(E67,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="H67" s="3" t="str">
+      <c r="G67" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H67" s="3">
         <f>IF(G67="","",IF(G67="DNS",0,IF(G67="DQ",0,IF(G67="DNF",1,IF(AND(ISNUMBER(G67),G67&gt;59),1,_xlfn.XLOOKUP(G67,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="str">
         <f>IF(I67="","",IF(I67="DNS",0,IF(I67="DQ",0,IF(I67="DNF",1,IF(AND(ISNUMBER(I67),I67&gt;59),1,_xlfn.XLOOKUP(I67,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6591,9 +6796,12 @@
         <f>IF(E68="","",IF(E68="DNS",0,IF(E68="DQ",0,IF(E68="DNF",1,IF(AND(ISNUMBER(E68),E68&gt;59),1,_xlfn.XLOOKUP(E68,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="H68" s="3" t="str">
+      <c r="G68" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H68" s="3">
         <f>IF(G68="","",IF(G68="DNS",0,IF(G68="DQ",0,IF(G68="DNF",1,IF(AND(ISNUMBER(G68),G68&gt;59),1,_xlfn.XLOOKUP(G68,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="str">
         <f>IF(I68="","",IF(I68="DNS",0,IF(I68="DQ",0,IF(I68="DNF",1,IF(AND(ISNUMBER(I68),I68&gt;59),1,_xlfn.XLOOKUP(I68,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20901,28 +21109,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D384">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$C2="Bant Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$C2="Bant Girls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$C2="Juv Girls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="4">
+    <cfRule type="expression" dxfId="16" priority="4">
       <formula>$C2="Juv Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="5">
+    <cfRule type="expression" dxfId="15" priority="5">
       <formula>$C2="Jr Girls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="6">
+    <cfRule type="expression" dxfId="14" priority="6">
       <formula>$C2="Jr Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>$C2="Sr Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>$C2="Sr Girls"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25901,28 +26109,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D384">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$C2="Bant Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$C2="Bant Girls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>$C2="Juv Girls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>$C2="Juv Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$C2="Jr Girls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>$C2="Jr Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>$C2="Sr Boys"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="8">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>$C2="Sr Girls"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26030,7 +26238,7 @@
 )</f>
         <v>265</v>
       </c>
-      <c r="D2" s="3" t="str" cm="1">
+      <c r="D2" s="3" cm="1">
         <f t="array" ref="D2">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -26061,7 +26269,7 @@
     ""
 )
 )</f>
-        <v/>
+        <v>237</v>
       </c>
       <c r="E2" s="3" t="str" cm="1">
         <f t="array" ref="E2">_xlfn.LET(
@@ -26197,7 +26405,7 @@
       </c>
       <c r="I2" s="3">
         <f>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</f>
-        <v>265</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -28130,7 +28338,7 @@
 )</f>
         <v>182</v>
       </c>
-      <c r="D12" s="3" t="str" cm="1">
+      <c r="D12" s="3" cm="1">
         <f t="array" ref="D12">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -28161,7 +28369,7 @@
     ""
 )
 )</f>
-        <v/>
+        <v>207</v>
       </c>
       <c r="E12" s="3" t="str" cm="1">
         <f t="array" ref="E12">_xlfn.LET(
@@ -28297,7 +28505,7 @@
       </c>
       <c r="I12" s="3">
         <f>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</f>
-        <v>182</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -28371,7 +28579,7 @@
     ""
 )
 )</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E13" s="3" cm="1">
         <f t="array" ref="E13">_xlfn.LET(
@@ -28507,7 +28715,7 @@
       </c>
       <c r="I13" s="3">
         <f>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -28970,7 +29178,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D16" s="3" cm="1">
+      <c r="D16" s="3" t="str" cm="1">
         <f t="array" ref="D16">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -29001,7 +29209,7 @@
     ""
 )
 )</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E16" s="3" cm="1">
         <f t="array" ref="E16">_xlfn.LET(
@@ -29390,7 +29598,7 @@
 )</f>
         <v>110</v>
       </c>
-      <c r="D18" s="3" cm="1">
+      <c r="D18" s="3" t="str" cm="1">
         <f t="array" ref="D18">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -29421,7 +29629,7 @@
     ""
 )
 )</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E18" s="3" cm="1">
         <f t="array" ref="E18">_xlfn.LET(
@@ -31311,7 +31519,7 @@
     ""
 )
 )</f>
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="E27" s="3" cm="1">
         <f t="array" ref="E27">_xlfn.LET(
@@ -31447,7 +31655,7 @@
       </c>
       <c r="I27" s="3">
         <f>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</f>
-        <v>143</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
@@ -33800,7 +34008,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D39" s="3" t="str" cm="1">
+      <c r="D39" s="3" cm="1">
         <f t="array" ref="D39">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -33831,7 +34039,7 @@
     ""
 )
 )</f>
-        <v/>
+        <v>62</v>
       </c>
       <c r="E39" s="3" t="str" cm="1">
         <f t="array" ref="E39">_xlfn.LET(
@@ -33967,7 +34175,7 @@
       </c>
       <c r="I39" s="3">
         <f>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</f>
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
@@ -34430,7 +34638,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D42" s="3" t="str" cm="1">
+      <c r="D42" s="3" cm="1">
         <f t="array" ref="D42">_xlfn.LET(
 _xlpm.teamDiv,tbl_teampoints[[#This Row],[Division]],
 _xlpm.teamSchool,tbl_teampoints[[#This Row],[School]],
@@ -34461,7 +34669,7 @@
     ""
 )
 )</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="E42" s="3" t="str" cm="1">
         <f t="array" ref="E42">_xlfn.LET(
@@ -34597,7 +34805,7 @@
       </c>
       <c r="I42" s="3">
         <f>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">

--- a/results_2026_master.xlsx
+++ b/results_2026_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19247\Documents\codemathbike\codemathbike_bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F2DF82-3A50-4295-9169-F3A778280E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27B22D56-4196-4C1E-9A4B-611B8AB50BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1690" yWindow="-20600" windowWidth="26000" windowHeight="18080" activeTab="1" xr2:uid="{E4CCCC36-747C-4C6A-A938-400850181E6F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{E4CCCC36-747C-4C6A-A938-400850181E6F}"/>
   </bookViews>
   <sheets>
     <sheet name="helper" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="418">
   <si>
     <t>Divisions</t>
   </si>
@@ -1389,7 +1389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1431,6 +1431,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1796,10 +1797,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B67B0C24-496D-4362-8989-27568D29525A}" name="tbl_points" displayName="tbl_points" ref="E1:F60" totalsRowShown="0" headerRowDxfId="43">
   <autoFilter ref="E1:F60" xr:uid="{B67B0C24-496D-4362-8989-27568D29525A}"/>
@@ -1812,10 +1809,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}" name="tbl_individual" displayName="tbl_individual" ref="A1:S351" totalsRowShown="0" headerRowDxfId="42">
-  <autoFilter ref="A1:S351" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S351">
-    <sortCondition ref="C1:C351"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}" name="tbl_individual" displayName="tbl_individual" ref="A1:S348" totalsRowShown="0" headerRowDxfId="42">
+  <autoFilter ref="A1:S348" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S348">
+    <sortCondition ref="B1:B348"/>
   </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{DD0C8BFC-D933-4D84-A252-784AFB91D5D2}" name="Student Name"/>
@@ -3000,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD5F9FD-2710-473F-9F71-EF9C438166F2}">
-  <dimension ref="A1:S351"/>
+  <dimension ref="A1:S348"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.8984375" bestFit="1" customWidth="1"/>
@@ -3584,16 +3581,16 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3">
-        <v>8190</v>
+        <v>10119</v>
       </c>
       <c r="F12" s="3" t="str">
         <f>IF(E12="","",IF(E12="DNS",0,IF(E12="DQ",0,IF(E12="DNF",1,IF(AND(ISNUMBER(E12),E12&gt;59),1,_xlfn.XLOOKUP(E12,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3634,16 +3631,16 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3">
-        <v>8189</v>
+        <v>10150</v>
       </c>
       <c r="F13" s="3" t="str">
         <f>IF(E13="","",IF(E13="DNS",0,IF(E13="DQ",0,IF(E13="DNF",1,IF(AND(ISNUMBER(E13),E13&gt;59),1,_xlfn.XLOOKUP(E13,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3684,16 +3681,16 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3">
-        <v>8191</v>
+        <v>10110</v>
       </c>
       <c r="F14" s="3" t="str">
         <f>IF(E14="","",IF(E14="DNS",0,IF(E14="DQ",0,IF(E14="DNF",1,IF(AND(ISNUMBER(E14),E14&gt;59),1,_xlfn.XLOOKUP(E14,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3734,16 +3731,16 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3">
-        <v>8192</v>
+        <v>10117</v>
       </c>
       <c r="F15" s="3" t="str">
         <f>IF(E15="","",IF(E15="DNS",0,IF(E15="DQ",0,IF(E15="DNF",1,IF(AND(ISNUMBER(E15),E15&gt;59),1,_xlfn.XLOOKUP(E15,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3784,16 +3781,16 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3">
-        <v>8194</v>
+        <v>10111</v>
       </c>
       <c r="F16" s="3" t="str">
         <f>IF(E16="","",IF(E16="DNS",0,IF(E16="DQ",0,IF(E16="DNF",1,IF(AND(ISNUMBER(E16),E16&gt;59),1,_xlfn.XLOOKUP(E16,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3834,16 +3831,16 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3">
-        <v>8193</v>
+        <v>10114</v>
       </c>
       <c r="F17" s="3" t="str">
         <f>IF(E17="","",IF(E17="DNS",0,IF(E17="DQ",0,IF(E17="DNF",1,IF(AND(ISNUMBER(E17),E17&gt;59),1,_xlfn.XLOOKUP(E17,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3884,16 +3881,16 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="3">
-        <v>8196</v>
+        <v>10115</v>
       </c>
       <c r="F18" s="3" t="str">
         <f>IF(E18="","",IF(E18="DNS",0,IF(E18="DQ",0,IF(E18="DNF",1,IF(AND(ISNUMBER(E18),E18&gt;59),1,_xlfn.XLOOKUP(E18,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3934,16 +3931,16 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3">
-        <v>8195</v>
+        <v>10151</v>
       </c>
       <c r="F19" s="3" t="str">
         <f>IF(E19="","",IF(E19="DNS",0,IF(E19="DQ",0,IF(E19="DNF",1,IF(AND(ISNUMBER(E19),E19&gt;59),1,_xlfn.XLOOKUP(E19,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -3984,16 +3981,16 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3">
-        <v>802</v>
+        <v>10126</v>
       </c>
       <c r="F20" s="3" t="str">
         <f>IF(E20="","",IF(E20="DNS",0,IF(E20="DQ",0,IF(E20="DNF",1,IF(AND(ISNUMBER(E20),E20&gt;59),1,_xlfn.XLOOKUP(E20,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4033,17 +4030,17 @@
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
+      <c r="A21" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>3</v>
       </c>
       <c r="D21" s="3">
-        <v>8197</v>
+        <v>10065</v>
       </c>
       <c r="F21" s="3" t="str">
         <f>IF(E21="","",IF(E21="DNS",0,IF(E21="DQ",0,IF(E21="DNF",1,IF(AND(ISNUMBER(E21),E21&gt;59),1,_xlfn.XLOOKUP(E21,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4083,17 +4080,17 @@
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>148</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>7</v>
+      <c r="A22" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>3</v>
       </c>
       <c r="D22" s="3">
-        <v>8198</v>
+        <v>10198</v>
       </c>
       <c r="F22" s="3" t="str">
         <f>IF(E22="","",IF(E22="DNS",0,IF(E22="DQ",0,IF(E22="DNF",1,IF(AND(ISNUMBER(E22),E22&gt;59),1,_xlfn.XLOOKUP(E22,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4133,17 +4130,17 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
+      <c r="A23" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>3</v>
       </c>
       <c r="D23" s="3">
-        <v>800</v>
+        <v>10158</v>
       </c>
       <c r="F23" s="3" t="str">
         <f>IF(E23="","",IF(E23="DNS",0,IF(E23="DQ",0,IF(E23="DNF",1,IF(AND(ISNUMBER(E23),E23&gt;59),1,_xlfn.XLOOKUP(E23,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4184,16 +4181,16 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3">
-        <v>801</v>
+        <v>1027</v>
       </c>
       <c r="F24" s="3" t="str">
         <f>IF(E24="","",IF(E24="DNS",0,IF(E24="DQ",0,IF(E24="DNF",1,IF(AND(ISNUMBER(E24),E24&gt;59),1,_xlfn.XLOOKUP(E24,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4234,16 +4231,16 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="3">
-        <v>8199</v>
+        <v>1029</v>
       </c>
       <c r="F25" s="3" t="str">
         <f>IF(E25="","",IF(E25="DNS",0,IF(E25="DQ",0,IF(E25="DNF",1,IF(AND(ISNUMBER(E25),E25&gt;59),1,_xlfn.XLOOKUP(E25,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4283,17 +4280,17 @@
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A26" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>7</v>
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
       </c>
       <c r="D26" s="3">
-        <v>8009</v>
+        <v>1028</v>
       </c>
       <c r="F26" s="3" t="str">
         <f>IF(E26="","",IF(E26="DNS",0,IF(E26="DQ",0,IF(E26="DNF",1,IF(AND(ISNUMBER(E26),E26&gt;59),1,_xlfn.XLOOKUP(E26,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4334,16 +4331,16 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D27" s="3">
-        <v>804</v>
+        <v>1019</v>
       </c>
       <c r="F27" s="3" t="str">
         <f>IF(E27="","",IF(E27="DNS",0,IF(E27="DQ",0,IF(E27="DNF",1,IF(AND(ISNUMBER(E27),E27&gt;59),1,_xlfn.XLOOKUP(E27,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4384,16 +4381,16 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D28" s="3">
-        <v>803</v>
+        <v>1030</v>
       </c>
       <c r="F28" s="3" t="str">
         <f>IF(E28="","",IF(E28="DNS",0,IF(E28="DQ",0,IF(E28="DNF",1,IF(AND(ISNUMBER(E28),E28&gt;59),1,_xlfn.XLOOKUP(E28,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4434,16 +4431,16 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D29" s="3">
-        <v>840</v>
+        <v>1020</v>
       </c>
       <c r="F29" s="3" t="str">
         <f>IF(E29="","",IF(E29="DNS",0,IF(E29="DQ",0,IF(E29="DNF",1,IF(AND(ISNUMBER(E29),E29&gt;59),1,_xlfn.XLOOKUP(E29,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4484,16 +4481,16 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" s="3">
-        <v>839</v>
+        <v>900</v>
       </c>
       <c r="F30" s="3" t="str">
         <f>IF(E30="","",IF(E30="DNS",0,IF(E30="DQ",0,IF(E30="DNF",1,IF(AND(ISNUMBER(E30),E30&gt;59),1,_xlfn.XLOOKUP(E30,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4534,16 +4531,16 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D31" s="3">
-        <v>837</v>
+        <v>907</v>
       </c>
       <c r="F31" s="3" t="str">
         <f>IF(E31="","",IF(E31="DNS",0,IF(E31="DQ",0,IF(E31="DNF",1,IF(AND(ISNUMBER(E31),E31&gt;59),1,_xlfn.XLOOKUP(E31,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4584,16 +4581,16 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D32" s="3">
-        <v>838</v>
+        <v>909</v>
       </c>
       <c r="F32" s="3" t="str">
         <f>IF(E32="","",IF(E32="DNS",0,IF(E32="DQ",0,IF(E32="DNF",1,IF(AND(ISNUMBER(E32),E32&gt;59),1,_xlfn.XLOOKUP(E32,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4634,16 +4631,16 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D33" s="3">
-        <v>808</v>
+        <v>908</v>
       </c>
       <c r="F33" s="3" t="str">
         <f>IF(E33="","",IF(E33="DNS",0,IF(E33="DQ",0,IF(E33="DNF",1,IF(AND(ISNUMBER(E33),E33&gt;59),1,_xlfn.XLOOKUP(E33,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4684,16 +4681,16 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D34" s="3">
-        <v>807</v>
+        <v>903</v>
       </c>
       <c r="F34" s="3" t="str">
         <f>IF(E34="","",IF(E34="DNS",0,IF(E34="DQ",0,IF(E34="DNF",1,IF(AND(ISNUMBER(E34),E34&gt;59),1,_xlfn.XLOOKUP(E34,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4734,16 +4731,16 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D35" s="3">
-        <v>806</v>
+        <v>904</v>
       </c>
       <c r="F35" s="3" t="str">
         <f>IF(E35="","",IF(E35="DNS",0,IF(E35="DQ",0,IF(E35="DNF",1,IF(AND(ISNUMBER(E35),E35&gt;59),1,_xlfn.XLOOKUP(E35,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4784,16 +4781,16 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>191</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D36" s="3">
-        <v>810</v>
+        <v>901</v>
       </c>
       <c r="F36" s="3" t="str">
         <f>IF(E36="","",IF(E36="DNS",0,IF(E36="DQ",0,IF(E36="DNF",1,IF(AND(ISNUMBER(E36),E36&gt;59),1,_xlfn.XLOOKUP(E36,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4834,16 +4831,16 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D37" s="3">
-        <v>811</v>
+        <v>905</v>
       </c>
       <c r="F37" s="3" t="str">
         <f>IF(E37="","",IF(E37="DNS",0,IF(E37="DQ",0,IF(E37="DNF",1,IF(AND(ISNUMBER(E37),E37&gt;59),1,_xlfn.XLOOKUP(E37,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4884,16 +4881,16 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>812</v>
+        <v>910</v>
       </c>
       <c r="F38" s="3" t="str">
         <f>IF(E38="","",IF(E38="DNS",0,IF(E38="DQ",0,IF(E38="DNF",1,IF(AND(ISNUMBER(E38),E38&gt;59),1,_xlfn.XLOOKUP(E38,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4934,16 +4931,16 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>809</v>
+        <v>902</v>
       </c>
       <c r="F39" s="3" t="str">
         <f>IF(E39="","",IF(E39="DNS",0,IF(E39="DQ",0,IF(E39="DNF",1,IF(AND(ISNUMBER(E39),E39&gt;59),1,_xlfn.XLOOKUP(E39,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -4984,16 +4981,16 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D40" s="3">
-        <v>813</v>
+        <v>906</v>
       </c>
       <c r="F40" s="3" t="str">
         <f>IF(E40="","",IF(E40="DNS",0,IF(E40="DQ",0,IF(E40="DNF",1,IF(AND(ISNUMBER(E40),E40&gt;59),1,_xlfn.XLOOKUP(E40,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5034,16 +5031,16 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>244</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41" s="3">
-        <v>814</v>
+        <v>9471</v>
       </c>
       <c r="F41" s="3" t="str">
         <f>IF(E41="","",IF(E41="DNS",0,IF(E41="DQ",0,IF(E41="DNF",1,IF(AND(ISNUMBER(E41),E41&gt;59),1,_xlfn.XLOOKUP(E41,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5084,16 +5081,16 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>252</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D42" s="3">
-        <v>816</v>
+        <v>918</v>
       </c>
       <c r="F42" s="3" t="str">
         <f>IF(E42="","",IF(E42="DNS",0,IF(E42="DQ",0,IF(E42="DNF",1,IF(AND(ISNUMBER(E42),E42&gt;59),1,_xlfn.XLOOKUP(E42,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5134,16 +5131,16 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>251</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43" s="3">
-        <v>815</v>
+        <v>9421</v>
       </c>
       <c r="F43" s="3" t="str">
         <f>IF(E43="","",IF(E43="DNS",0,IF(E43="DQ",0,IF(E43="DNF",1,IF(AND(ISNUMBER(E43),E43&gt;59),1,_xlfn.XLOOKUP(E43,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5184,16 +5181,16 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>253</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" s="3">
-        <v>817</v>
+        <v>9451</v>
       </c>
       <c r="F44" s="3" t="str">
         <f>IF(E44="","",IF(E44="DNS",0,IF(E44="DQ",0,IF(E44="DNF",1,IF(AND(ISNUMBER(E44),E44&gt;59),1,_xlfn.XLOOKUP(E44,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5234,16 +5231,16 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>288</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" s="3">
-        <v>819</v>
+        <v>9481</v>
       </c>
       <c r="F45" s="3" t="str">
         <f>IF(E45="","",IF(E45="DNS",0,IF(E45="DQ",0,IF(E45="DNF",1,IF(AND(ISNUMBER(E45),E45&gt;59),1,_xlfn.XLOOKUP(E45,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5284,16 +5281,16 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>287</v>
+        <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D46" s="3">
-        <v>818</v>
+        <v>12017</v>
       </c>
       <c r="F46" s="3" t="str">
         <f>IF(E46="","",IF(E46="DNS",0,IF(E46="DQ",0,IF(E46="DNF",1,IF(AND(ISNUMBER(E46),E46&gt;59),1,_xlfn.XLOOKUP(E46,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5334,16 +5331,16 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>311</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D47" s="3">
-        <v>822</v>
+        <v>12013</v>
       </c>
       <c r="F47" s="3" t="str">
         <f>IF(E47="","",IF(E47="DNS",0,IF(E47="DQ",0,IF(E47="DNF",1,IF(AND(ISNUMBER(E47),E47&gt;59),1,_xlfn.XLOOKUP(E47,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5384,16 +5381,16 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>310</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D48" s="3">
-        <v>821</v>
+        <v>12016</v>
       </c>
       <c r="F48" s="3" t="str">
         <f>IF(E48="","",IF(E48="DNS",0,IF(E48="DQ",0,IF(E48="DNF",1,IF(AND(ISNUMBER(E48),E48&gt;59),1,_xlfn.XLOOKUP(E48,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5434,16 +5431,16 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>312</v>
+        <v>100</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49" s="3">
-        <v>823</v>
+        <v>12005</v>
       </c>
       <c r="F49" s="3" t="str">
         <f>IF(E49="","",IF(E49="DNS",0,IF(E49="DQ",0,IF(E49="DNF",1,IF(AND(ISNUMBER(E49),E49&gt;59),1,_xlfn.XLOOKUP(E49,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5484,16 +5481,16 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D50" s="3">
-        <v>820</v>
+        <v>12001</v>
       </c>
       <c r="F50" s="3" t="str">
         <f>IF(E50="","",IF(E50="DNS",0,IF(E50="DQ",0,IF(E50="DNF",1,IF(AND(ISNUMBER(E50),E50&gt;59),1,_xlfn.XLOOKUP(E50,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5534,16 +5531,16 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D51" s="3">
-        <v>824</v>
+        <v>12009</v>
       </c>
       <c r="F51" s="3" t="str">
         <f>IF(E51="","",IF(E51="DNS",0,IF(E51="DQ",0,IF(E51="DNF",1,IF(AND(ISNUMBER(E51),E51&gt;59),1,_xlfn.XLOOKUP(E51,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5584,16 +5581,16 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>321</v>
+        <v>105</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D52" s="3">
-        <v>825</v>
+        <v>12015</v>
       </c>
       <c r="F52" s="3" t="str">
         <f>IF(E52="","",IF(E52="DNS",0,IF(E52="DQ",0,IF(E52="DNF",1,IF(AND(ISNUMBER(E52),E52&gt;59),1,_xlfn.XLOOKUP(E52,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5634,16 +5631,16 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>338</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D53" s="3">
-        <v>826</v>
+        <v>12014</v>
       </c>
       <c r="F53" s="3" t="str">
         <f>IF(E53="","",IF(E53="DNS",0,IF(E53="DQ",0,IF(E53="DNF",1,IF(AND(ISNUMBER(E53),E53&gt;59),1,_xlfn.XLOOKUP(E53,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5684,16 +5681,16 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>342</v>
+        <v>102</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D54" s="3">
-        <v>830</v>
+        <v>12012</v>
       </c>
       <c r="F54" s="3" t="str">
         <f>IF(E54="","",IF(E54="DNS",0,IF(E54="DQ",0,IF(E54="DNF",1,IF(AND(ISNUMBER(E54),E54&gt;59),1,_xlfn.XLOOKUP(E54,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5734,16 +5731,16 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>339</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="3">
-        <v>827</v>
+        <v>8190</v>
       </c>
       <c r="F55" s="3" t="str">
         <f>IF(E55="","",IF(E55="DNS",0,IF(E55="DQ",0,IF(E55="DNF",1,IF(AND(ISNUMBER(E55),E55&gt;59),1,_xlfn.XLOOKUP(E55,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5784,16 +5781,16 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>341</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
       </c>
       <c r="D56" s="3">
-        <v>829</v>
+        <v>8189</v>
       </c>
       <c r="F56" s="3" t="str">
         <f>IF(E56="","",IF(E56="DNS",0,IF(E56="DQ",0,IF(E56="DNF",1,IF(AND(ISNUMBER(E56),E56&gt;59),1,_xlfn.XLOOKUP(E56,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5834,16 +5831,16 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>340</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D57" s="3">
-        <v>828</v>
+        <v>10153</v>
       </c>
       <c r="F57" s="3" t="str">
         <f>IF(E57="","",IF(E57="DNS",0,IF(E57="DQ",0,IF(E57="DNF",1,IF(AND(ISNUMBER(E57),E57&gt;59),1,_xlfn.XLOOKUP(E57,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5884,16 +5881,16 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>359</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D58" s="3">
-        <v>832</v>
+        <v>10154</v>
       </c>
       <c r="F58" s="3" t="str">
         <f>IF(E58="","",IF(E58="DNS",0,IF(E58="DQ",0,IF(E58="DNF",1,IF(AND(ISNUMBER(E58),E58&gt;59),1,_xlfn.XLOOKUP(E58,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5934,16 +5931,16 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>358</v>
+        <v>112</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D59" s="3">
-        <v>831</v>
+        <v>10152</v>
       </c>
       <c r="F59" s="3" t="str">
         <f>IF(E59="","",IF(E59="DNS",0,IF(E59="DQ",0,IF(E59="DNF",1,IF(AND(ISNUMBER(E59),E59&gt;59),1,_xlfn.XLOOKUP(E59,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -5984,16 +5981,16 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>365</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D60" s="3">
-        <v>834</v>
+        <v>10155</v>
       </c>
       <c r="F60" s="3" t="str">
         <f>IF(E60="","",IF(E60="DNS",0,IF(E60="DQ",0,IF(E60="DNF",1,IF(AND(ISNUMBER(E60),E60&gt;59),1,_xlfn.XLOOKUP(E60,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6034,16 +6031,16 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>367</v>
+        <v>110</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D61" s="3">
-        <v>836</v>
+        <v>911</v>
       </c>
       <c r="F61" s="3" t="str">
         <f>IF(E61="","",IF(E61="DNS",0,IF(E61="DQ",0,IF(E61="DNF",1,IF(AND(ISNUMBER(E61),E61&gt;59),1,_xlfn.XLOOKUP(E61,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6084,16 +6081,16 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62" s="3">
-        <v>835</v>
+        <v>929</v>
       </c>
       <c r="F62" s="3" t="str">
         <f>IF(E62="","",IF(E62="DNS",0,IF(E62="DQ",0,IF(E62="DNF",1,IF(AND(ISNUMBER(E62),E62&gt;59),1,_xlfn.XLOOKUP(E62,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6134,16 +6131,16 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>364</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D63" s="3">
-        <v>833</v>
+        <v>12018</v>
       </c>
       <c r="F63" s="3" t="str">
         <f>IF(E63="","",IF(E63="DNS",0,IF(E63="DQ",0,IF(E63="DNF",1,IF(AND(ISNUMBER(E63),E63&gt;59),1,_xlfn.XLOOKUP(E63,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6184,16 +6181,16 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>392</v>
+        <v>117</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D64" s="3">
-        <v>8084</v>
+        <v>12019</v>
       </c>
       <c r="F64" s="3" t="str">
         <f>IF(E64="","",IF(E64="DNS",0,IF(E64="DQ",0,IF(E64="DNF",1,IF(AND(ISNUMBER(E64),E64&gt;59),1,_xlfn.XLOOKUP(E64,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6234,16 +6231,16 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="B65" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" s="3">
-        <v>854</v>
+        <v>8191</v>
       </c>
       <c r="F65" s="3" t="str">
         <f>IF(E65="","",IF(E65="DNS",0,IF(E65="DQ",0,IF(E65="DNF",1,IF(AND(ISNUMBER(E65),E65&gt;59),1,_xlfn.XLOOKUP(E65,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6284,16 +6281,16 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" s="3">
-        <v>825</v>
+        <v>8192</v>
       </c>
       <c r="F66" s="3" t="str">
         <f>IF(E66="","",IF(E66="DNS",0,IF(E66="DQ",0,IF(E66="DNF",1,IF(AND(ISNUMBER(E66),E66&gt;59),1,_xlfn.XLOOKUP(E66,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6334,16 +6331,16 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D67" s="3">
-        <v>859</v>
+        <v>10157</v>
       </c>
       <c r="F67" s="3" t="str">
         <f>IF(E67="","",IF(E67="DNS",0,IF(E67="DQ",0,IF(E67="DNF",1,IF(AND(ISNUMBER(E67),E67&gt;59),1,_xlfn.XLOOKUP(E67,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6384,16 +6381,16 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D68" s="3">
-        <v>860</v>
+        <v>10156</v>
       </c>
       <c r="F68" s="3" t="str">
         <f>IF(E68="","",IF(E68="DNS",0,IF(E68="DQ",0,IF(E68="DNF",1,IF(AND(ISNUMBER(E68),E68&gt;59),1,_xlfn.XLOOKUP(E68,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6434,16 +6431,16 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D69" s="3">
-        <v>861</v>
+        <v>12020</v>
       </c>
       <c r="F69" s="3" t="str">
         <f>IF(E69="","",IF(E69="DNS",0,IF(E69="DQ",0,IF(E69="DNF",1,IF(AND(ISNUMBER(E69),E69&gt;59),1,_xlfn.XLOOKUP(E69,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6484,16 +6481,16 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D70" s="3">
-        <v>868</v>
+        <v>12021</v>
       </c>
       <c r="F70" s="3" t="str">
         <f>IF(E70="","",IF(E70="DNS",0,IF(E70="DQ",0,IF(E70="DNF",1,IF(AND(ISNUMBER(E70),E70&gt;59),1,_xlfn.XLOOKUP(E70,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6534,16 +6531,16 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>250</v>
+        <v>124</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D71" s="3">
-        <v>864</v>
+        <v>12022</v>
       </c>
       <c r="F71" s="3" t="str">
         <f>IF(E71="","",IF(E71="DNS",0,IF(E71="DQ",0,IF(E71="DNF",1,IF(AND(ISNUMBER(E71),E71&gt;59),1,_xlfn.XLOOKUP(E71,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6584,16 +6581,16 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>125</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D72" s="3">
-        <v>862</v>
+        <v>12023</v>
       </c>
       <c r="F72" s="3" t="str">
         <f>IF(E72="","",IF(E72="DNS",0,IF(E72="DQ",0,IF(E72="DNF",1,IF(AND(ISNUMBER(E72),E72&gt;59),1,_xlfn.XLOOKUP(E72,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6634,16 +6631,16 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>249</v>
+        <v>126</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D73" s="3">
-        <v>863</v>
+        <v>1227</v>
       </c>
       <c r="F73" s="3" t="str">
         <f>IF(E73="","",IF(E73="DNS",0,IF(E73="DQ",0,IF(E73="DNF",1,IF(AND(ISNUMBER(E73),E73&gt;59),1,_xlfn.XLOOKUP(E73,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6684,16 +6681,16 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="3">
-        <v>865</v>
+        <v>8194</v>
       </c>
       <c r="F74" s="3" t="str">
         <f>IF(E74="","",IF(E74="DNS",0,IF(E74="DQ",0,IF(E74="DNF",1,IF(AND(ISNUMBER(E74),E74&gt;59),1,_xlfn.XLOOKUP(E74,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6734,16 +6731,16 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>323</v>
+        <v>127</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" s="3">
-        <v>867</v>
+        <v>8193</v>
       </c>
       <c r="F75" s="3" t="str">
         <f>IF(E75="","",IF(E75="DNS",0,IF(E75="DQ",0,IF(E75="DNF",1,IF(AND(ISNUMBER(E75),E75&gt;59),1,_xlfn.XLOOKUP(E75,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6784,16 +6781,16 @@
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>322</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D76" s="3">
-        <v>866</v>
+        <v>10159</v>
       </c>
       <c r="F76" s="3" t="str">
         <f>IF(E76="","",IF(E76="DNS",0,IF(E76="DQ",0,IF(E76="DNF",1,IF(AND(ISNUMBER(E76),E76&gt;59),1,_xlfn.XLOOKUP(E76,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6834,16 +6831,16 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C77" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D77" s="3">
-        <v>10119</v>
+        <v>913</v>
       </c>
       <c r="F77" s="3" t="str">
         <f>IF(E77="","",IF(E77="DNS",0,IF(E77="DQ",0,IF(E77="DNF",1,IF(AND(ISNUMBER(E77),E77&gt;59),1,_xlfn.XLOOKUP(E77,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6884,16 +6881,16 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C78" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D78" s="3">
-        <v>10150</v>
+        <v>912</v>
       </c>
       <c r="F78" s="3" t="str">
         <f>IF(E78="","",IF(E78="DNS",0,IF(E78="DQ",0,IF(E78="DNF",1,IF(AND(ISNUMBER(E78),E78&gt;59),1,_xlfn.XLOOKUP(E78,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6933,17 +6930,17 @@
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A79" t="s">
-        <v>89</v>
-      </c>
-      <c r="B79" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" t="s">
-        <v>3</v>
+      <c r="A79" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>1</v>
       </c>
       <c r="D79" s="3">
-        <v>10110</v>
+        <v>12103</v>
       </c>
       <c r="F79" s="3" t="str">
         <f>IF(E79="","",IF(E79="DNS",0,IF(E79="DQ",0,IF(E79="DNF",1,IF(AND(ISNUMBER(E79),E79&gt;59),1,_xlfn.XLOOKUP(E79,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -6984,16 +6981,16 @@
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C80" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" s="3">
-        <v>10117</v>
+        <v>12026</v>
       </c>
       <c r="F80" s="3" t="str">
         <f>IF(E80="","",IF(E80="DNS",0,IF(E80="DQ",0,IF(E80="DNF",1,IF(AND(ISNUMBER(E80),E80&gt;59),1,_xlfn.XLOOKUP(E80,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7034,16 +7031,16 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C81" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" s="3">
-        <v>10111</v>
+        <v>12025</v>
       </c>
       <c r="F81" s="3" t="str">
         <f>IF(E81="","",IF(E81="DNS",0,IF(E81="DQ",0,IF(E81="DNF",1,IF(AND(ISNUMBER(E81),E81&gt;59),1,_xlfn.XLOOKUP(E81,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7084,16 +7081,16 @@
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C82" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" s="3">
-        <v>10114</v>
+        <v>12028</v>
       </c>
       <c r="F82" s="3" t="str">
         <f>IF(E82="","",IF(E82="DNS",0,IF(E82="DQ",0,IF(E82="DNF",1,IF(AND(ISNUMBER(E82),E82&gt;59),1,_xlfn.XLOOKUP(E82,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7134,16 +7131,16 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C83" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" s="3">
-        <v>10115</v>
+        <v>12027</v>
       </c>
       <c r="F83" s="3" t="str">
         <f>IF(E83="","",IF(E83="DNS",0,IF(E83="DQ",0,IF(E83="DNF",1,IF(AND(ISNUMBER(E83),E83&gt;59),1,_xlfn.XLOOKUP(E83,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7184,16 +7181,16 @@
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C84" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" s="3">
-        <v>10151</v>
+        <v>12029</v>
       </c>
       <c r="F84" s="3" t="str">
         <f>IF(E84="","",IF(E84="DNS",0,IF(E84="DQ",0,IF(E84="DNF",1,IF(AND(ISNUMBER(E84),E84&gt;59),1,_xlfn.XLOOKUP(E84,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7234,16 +7231,16 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C85" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" s="3">
-        <v>10126</v>
+        <v>12024</v>
       </c>
       <c r="F85" s="3" t="str">
         <f>IF(E85="","",IF(E85="DNS",0,IF(E85="DQ",0,IF(E85="DNF",1,IF(AND(ISNUMBER(E85),E85&gt;59),1,_xlfn.XLOOKUP(E85,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7283,17 +7280,17 @@
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A86" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>3</v>
+      <c r="A86" t="s">
+        <v>139</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1</v>
       </c>
       <c r="D86" s="3">
-        <v>10065</v>
+        <v>12030</v>
       </c>
       <c r="F86" s="3" t="str">
         <f>IF(E86="","",IF(E86="DNS",0,IF(E86="DQ",0,IF(E86="DNF",1,IF(AND(ISNUMBER(E86),E86&gt;59),1,_xlfn.XLOOKUP(E86,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7333,17 +7330,17 @@
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A87" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>3</v>
+      <c r="A87" t="s">
+        <v>143</v>
+      </c>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2</v>
       </c>
       <c r="D87" s="3">
-        <v>10198</v>
+        <v>1233</v>
       </c>
       <c r="F87" s="3" t="str">
         <f>IF(E87="","",IF(E87="DNS",0,IF(E87="DQ",0,IF(E87="DNF",1,IF(AND(ISNUMBER(E87),E87&gt;59),1,_xlfn.XLOOKUP(E87,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7383,17 +7380,17 @@
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A88" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>3</v>
+      <c r="A88" t="s">
+        <v>141</v>
+      </c>
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2</v>
       </c>
       <c r="D88" s="3">
-        <v>10158</v>
+        <v>1231</v>
       </c>
       <c r="F88" s="3" t="str">
         <f>IF(E88="","",IF(E88="DNS",0,IF(E88="DQ",0,IF(E88="DNF",1,IF(AND(ISNUMBER(E88),E88&gt;59),1,_xlfn.XLOOKUP(E88,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7434,16 +7431,16 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" s="3">
-        <v>10153</v>
+        <v>1230</v>
       </c>
       <c r="F89" s="3" t="str">
         <f>IF(E89="","",IF(E89="DNS",0,IF(E89="DQ",0,IF(E89="DNF",1,IF(AND(ISNUMBER(E89),E89&gt;59),1,_xlfn.XLOOKUP(E89,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7484,16 +7481,16 @@
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>10154</v>
+        <v>1232</v>
       </c>
       <c r="F90" s="3" t="str">
         <f>IF(E90="","",IF(E90="DNS",0,IF(E90="DQ",0,IF(E90="DNF",1,IF(AND(ISNUMBER(E90),E90&gt;59),1,_xlfn.XLOOKUP(E90,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7534,16 +7531,16 @@
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D91" s="3">
-        <v>10152</v>
+        <v>8196</v>
       </c>
       <c r="F91" s="3" t="str">
         <f>IF(E91="","",IF(E91="DNS",0,IF(E91="DQ",0,IF(E91="DNF",1,IF(AND(ISNUMBER(E91),E91&gt;59),1,_xlfn.XLOOKUP(E91,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7584,16 +7581,16 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C92" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D92" s="3">
-        <v>10155</v>
+        <v>8195</v>
       </c>
       <c r="F92" s="3" t="str">
         <f>IF(E92="","",IF(E92="DNS",0,IF(E92="DQ",0,IF(E92="DNF",1,IF(AND(ISNUMBER(E92),E92&gt;59),1,_xlfn.XLOOKUP(E92,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7634,16 +7631,16 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C93" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93" s="3">
-        <v>10157</v>
+        <v>12031</v>
       </c>
       <c r="F93" s="3" t="str">
         <f>IF(E93="","",IF(E93="DNS",0,IF(E93="DQ",0,IF(E93="DNF",1,IF(AND(ISNUMBER(E93),E93&gt;59),1,_xlfn.XLOOKUP(E93,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7684,16 +7681,16 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C94" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D94" s="3">
-        <v>10156</v>
+        <v>802</v>
       </c>
       <c r="F94" s="3" t="str">
         <f>IF(E94="","",IF(E94="DNS",0,IF(E94="DQ",0,IF(E94="DNF",1,IF(AND(ISNUMBER(E94),E94&gt;59),1,_xlfn.XLOOKUP(E94,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7734,16 +7731,16 @@
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D95" s="3">
-        <v>10159</v>
+        <v>8197</v>
       </c>
       <c r="F95" s="3" t="str">
         <f>IF(E95="","",IF(E95="DNS",0,IF(E95="DQ",0,IF(E95="DNF",1,IF(AND(ISNUMBER(E95),E95&gt;59),1,_xlfn.XLOOKUP(E95,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7784,16 +7781,16 @@
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B96" t="s">
         <v>16</v>
       </c>
       <c r="C96" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D96" s="3">
-        <v>10160</v>
+        <v>8198</v>
       </c>
       <c r="F96" s="3" t="str">
         <f>IF(E96="","",IF(E96="DNS",0,IF(E96="DQ",0,IF(E96="DNF",1,IF(AND(ISNUMBER(E96),E96&gt;59),1,_xlfn.XLOOKUP(E96,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7834,16 +7831,16 @@
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D97" s="3">
-        <v>10161</v>
+        <v>800</v>
       </c>
       <c r="F97" s="3" t="str">
         <f>IF(E97="","",IF(E97="DNS",0,IF(E97="DQ",0,IF(E97="DNF",1,IF(AND(ISNUMBER(E97),E97&gt;59),1,_xlfn.XLOOKUP(E97,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7884,16 +7881,16 @@
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C98" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D98" s="3">
-        <v>10164</v>
+        <v>801</v>
       </c>
       <c r="F98" s="3" t="str">
         <f>IF(E98="","",IF(E98="DNS",0,IF(E98="DQ",0,IF(E98="DNF",1,IF(AND(ISNUMBER(E98),E98&gt;59),1,_xlfn.XLOOKUP(E98,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7934,16 +7931,16 @@
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D99" s="3">
-        <v>10162</v>
+        <v>8199</v>
       </c>
       <c r="F99" s="3" t="str">
         <f>IF(E99="","",IF(E99="DNS",0,IF(E99="DQ",0,IF(E99="DNF",1,IF(AND(ISNUMBER(E99),E99&gt;59),1,_xlfn.XLOOKUP(E99,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -7983,17 +7980,17 @@
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>186</v>
-      </c>
-      <c r="B100" t="s">
-        <v>20</v>
-      </c>
-      <c r="C100" t="s">
-        <v>3</v>
+      <c r="A100" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="D100" s="3">
-        <v>10163</v>
+        <v>8009</v>
       </c>
       <c r="F100" s="3" t="str">
         <f>IF(E100="","",IF(E100="DNS",0,IF(E100="DQ",0,IF(E100="DNF",1,IF(AND(ISNUMBER(E100),E100&gt;59),1,_xlfn.XLOOKUP(E100,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8034,16 +8031,16 @@
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D101" s="3">
-        <v>10171</v>
+        <v>854</v>
       </c>
       <c r="F101" s="3" t="str">
         <f>IF(E101="","",IF(E101="DNS",0,IF(E101="DQ",0,IF(E101="DNF",1,IF(AND(ISNUMBER(E101),E101&gt;59),1,_xlfn.XLOOKUP(E101,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8084,16 +8081,16 @@
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C102" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D102" s="3">
-        <v>10170</v>
+        <v>825</v>
       </c>
       <c r="F102" s="3" t="str">
         <f>IF(E102="","",IF(E102="DNS",0,IF(E102="DQ",0,IF(E102="DNF",1,IF(AND(ISNUMBER(E102),E102&gt;59),1,_xlfn.XLOOKUP(E102,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8134,16 +8131,16 @@
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C103" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="3">
-        <v>10166</v>
+        <v>10160</v>
       </c>
       <c r="F103" s="3" t="str">
         <f>IF(E103="","",IF(E103="DNS",0,IF(E103="DQ",0,IF(E103="DNF",1,IF(AND(ISNUMBER(E103),E103&gt;59),1,_xlfn.XLOOKUP(E103,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8184,16 +8181,16 @@
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="B104" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C104" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D104" s="3">
-        <v>10167</v>
+        <v>9491</v>
       </c>
       <c r="F104" s="3" t="str">
         <f>IF(E104="","",IF(E104="DNS",0,IF(E104="DQ",0,IF(E104="DNF",1,IF(AND(ISNUMBER(E104),E104&gt;59),1,_xlfn.XLOOKUP(E104,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8234,16 +8231,16 @@
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="B105" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D105" s="3">
-        <v>10165</v>
+        <v>12032</v>
       </c>
       <c r="F105" s="3" t="str">
         <f>IF(E105="","",IF(E105="DNS",0,IF(E105="DQ",0,IF(E105="DNF",1,IF(AND(ISNUMBER(E105),E105&gt;59),1,_xlfn.XLOOKUP(E105,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8284,16 +8281,16 @@
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" s="3">
-        <v>10169</v>
+        <v>12033</v>
       </c>
       <c r="F106" s="3" t="str">
         <f>IF(E106="","",IF(E106="DNS",0,IF(E106="DQ",0,IF(E106="DNF",1,IF(AND(ISNUMBER(E106),E106&gt;59),1,_xlfn.XLOOKUP(E106,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8334,16 +8331,16 @@
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="B107" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D107" s="3">
-        <v>10168</v>
+        <v>804</v>
       </c>
       <c r="F107" s="3" t="str">
         <f>IF(E107="","",IF(E107="DNS",0,IF(E107="DQ",0,IF(E107="DNF",1,IF(AND(ISNUMBER(E107),E107&gt;59),1,_xlfn.XLOOKUP(E107,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8384,16 +8381,16 @@
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="B108" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D108" s="3">
-        <v>10177</v>
+        <v>803</v>
       </c>
       <c r="F108" s="3" t="str">
         <f>IF(E108="","",IF(E108="DNS",0,IF(E108="DQ",0,IF(E108="DNF",1,IF(AND(ISNUMBER(E108),E108&gt;59),1,_xlfn.XLOOKUP(E108,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8434,16 +8431,16 @@
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="B109" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C109" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="3">
-        <v>10174</v>
+        <v>10161</v>
       </c>
       <c r="F109" s="3" t="str">
         <f>IF(E109="","",IF(E109="DNS",0,IF(E109="DQ",0,IF(E109="DNF",1,IF(AND(ISNUMBER(E109),E109&gt;59),1,_xlfn.XLOOKUP(E109,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8484,16 +8481,16 @@
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>225</v>
+        <v>162</v>
       </c>
       <c r="B110" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D110" s="3">
-        <v>10175</v>
+        <v>915</v>
       </c>
       <c r="F110" s="3" t="str">
         <f>IF(E110="","",IF(E110="DNS",0,IF(E110="DQ",0,IF(E110="DNF",1,IF(AND(ISNUMBER(E110),E110&gt;59),1,_xlfn.XLOOKUP(E110,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8534,16 +8531,16 @@
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="B111" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D111" s="3">
-        <v>10172</v>
+        <v>916</v>
       </c>
       <c r="F111" s="3" t="str">
         <f>IF(E111="","",IF(E111="DNS",0,IF(E111="DQ",0,IF(E111="DNF",1,IF(AND(ISNUMBER(E111),E111&gt;59),1,_xlfn.XLOOKUP(E111,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8584,16 +8581,16 @@
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="B112" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D112" s="3">
-        <v>10176</v>
+        <v>917</v>
       </c>
       <c r="F112" s="3" t="str">
         <f>IF(E112="","",IF(E112="DNS",0,IF(E112="DQ",0,IF(E112="DNF",1,IF(AND(ISNUMBER(E112),E112&gt;59),1,_xlfn.XLOOKUP(E112,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8634,16 +8631,16 @@
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="B113" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D113" s="3">
-        <v>10173</v>
+        <v>914</v>
       </c>
       <c r="F113" s="3" t="str">
         <f>IF(E113="","",IF(E113="DNS",0,IF(E113="DQ",0,IF(E113="DNF",1,IF(AND(ISNUMBER(E113),E113&gt;59),1,_xlfn.XLOOKUP(E113,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8684,16 +8681,16 @@
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="B114" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D114" s="3">
-        <v>10178</v>
+        <v>925</v>
       </c>
       <c r="F114" s="3" t="str">
         <f>IF(E114="","",IF(E114="DNS",0,IF(E114="DQ",0,IF(E114="DNF",1,IF(AND(ISNUMBER(E114),E114&gt;59),1,_xlfn.XLOOKUP(E114,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8734,16 +8731,16 @@
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="B115" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115" s="3">
-        <v>10180</v>
+        <v>12035</v>
       </c>
       <c r="F115" s="3" t="str">
         <f>IF(E115="","",IF(E115="DNS",0,IF(E115="DQ",0,IF(E115="DNF",1,IF(AND(ISNUMBER(E115),E115&gt;59),1,_xlfn.XLOOKUP(E115,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8784,16 +8781,16 @@
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>246</v>
+        <v>167</v>
       </c>
       <c r="B116" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116" s="3">
-        <v>10179</v>
+        <v>12034</v>
       </c>
       <c r="F116" s="3" t="str">
         <f>IF(E116="","",IF(E116="DNS",0,IF(E116="DQ",0,IF(E116="DNF",1,IF(AND(ISNUMBER(E116),E116&gt;59),1,_xlfn.XLOOKUP(E116,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8834,16 +8831,16 @@
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>268</v>
+        <v>175</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C117" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D117" s="3">
-        <v>10183</v>
+        <v>840</v>
       </c>
       <c r="F117" s="3" t="str">
         <f>IF(E117="","",IF(E117="DNS",0,IF(E117="DQ",0,IF(E117="DNF",1,IF(AND(ISNUMBER(E117),E117&gt;59),1,_xlfn.XLOOKUP(E117,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8884,16 +8881,16 @@
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>269</v>
+        <v>174</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C118" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D118" s="3">
-        <v>10184</v>
+        <v>839</v>
       </c>
       <c r="F118" s="3" t="str">
         <f>IF(E118="","",IF(E118="DNS",0,IF(E118="DQ",0,IF(E118="DNF",1,IF(AND(ISNUMBER(E118),E118&gt;59),1,_xlfn.XLOOKUP(E118,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8934,16 +8931,16 @@
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>267</v>
+        <v>172</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C119" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D119" s="3">
-        <v>10182</v>
+        <v>837</v>
       </c>
       <c r="F119" s="3" t="str">
         <f>IF(E119="","",IF(E119="DNS",0,IF(E119="DQ",0,IF(E119="DNF",1,IF(AND(ISNUMBER(E119),E119&gt;59),1,_xlfn.XLOOKUP(E119,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -8984,16 +8981,16 @@
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>266</v>
+        <v>173</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C120" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D120" s="3">
-        <v>10181</v>
+        <v>838</v>
       </c>
       <c r="F120" s="3" t="str">
         <f>IF(E120="","",IF(E120="DNS",0,IF(E120="DQ",0,IF(E120="DNF",1,IF(AND(ISNUMBER(E120),E120&gt;59),1,_xlfn.XLOOKUP(E120,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9034,16 +9031,16 @@
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C121" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D121" s="3">
-        <v>10186</v>
+        <v>859</v>
       </c>
       <c r="F121" s="3" t="str">
         <f>IF(E121="","",IF(E121="DNS",0,IF(E121="DQ",0,IF(E121="DNF",1,IF(AND(ISNUMBER(E121),E121&gt;59),1,_xlfn.XLOOKUP(E121,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9084,16 +9081,16 @@
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C122" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D122" s="3">
-        <v>10185</v>
+        <v>860</v>
       </c>
       <c r="F122" s="3" t="str">
         <f>IF(E122="","",IF(E122="DNS",0,IF(E122="DQ",0,IF(E122="DNF",1,IF(AND(ISNUMBER(E122),E122&gt;59),1,_xlfn.XLOOKUP(E122,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9134,16 +9131,16 @@
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C123" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D123" s="3">
-        <v>10187</v>
+        <v>861</v>
       </c>
       <c r="F123" s="3" t="str">
         <f>IF(E123="","",IF(E123="DNS",0,IF(E123="DQ",0,IF(E123="DNF",1,IF(AND(ISNUMBER(E123),E123&gt;59),1,_xlfn.XLOOKUP(E123,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9184,16 +9181,16 @@
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>307</v>
+        <v>178</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C124" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D124" s="3">
-        <v>10189</v>
+        <v>957</v>
       </c>
       <c r="F124" s="3" t="str">
         <f>IF(E124="","",IF(E124="DNS",0,IF(E124="DQ",0,IF(E124="DNF",1,IF(AND(ISNUMBER(E124),E124&gt;59),1,_xlfn.XLOOKUP(E124,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9234,16 +9231,16 @@
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>306</v>
+        <v>176</v>
       </c>
       <c r="B125" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C125" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D125" s="3">
-        <v>10188</v>
+        <v>955</v>
       </c>
       <c r="F125" s="3" t="str">
         <f>IF(E125="","",IF(E125="DNS",0,IF(E125="DQ",0,IF(E125="DNF",1,IF(AND(ISNUMBER(E125),E125&gt;59),1,_xlfn.XLOOKUP(E125,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9284,16 +9281,16 @@
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>315</v>
+        <v>177</v>
       </c>
       <c r="B126" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C126" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D126" s="3">
-        <v>10190</v>
+        <v>956</v>
       </c>
       <c r="F126" s="3" t="str">
         <f>IF(E126="","",IF(E126="DNS",0,IF(E126="DQ",0,IF(E126="DNF",1,IF(AND(ISNUMBER(E126),E126&gt;59),1,_xlfn.XLOOKUP(E126,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9334,16 +9331,16 @@
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>328</v>
+        <v>181</v>
       </c>
       <c r="B127" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C127" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D127" s="3">
-        <v>10191</v>
+        <v>808</v>
       </c>
       <c r="F127" s="3" t="str">
         <f>IF(E127="","",IF(E127="DNS",0,IF(E127="DQ",0,IF(E127="DNF",1,IF(AND(ISNUMBER(E127),E127&gt;59),1,_xlfn.XLOOKUP(E127,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9384,16 +9381,16 @@
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>348</v>
+        <v>180</v>
       </c>
       <c r="B128" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C128" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D128" s="3">
-        <v>10192</v>
+        <v>807</v>
       </c>
       <c r="F128" s="3" t="str">
         <f>IF(E128="","",IF(E128="DNS",0,IF(E128="DQ",0,IF(E128="DNF",1,IF(AND(ISNUMBER(E128),E128&gt;59),1,_xlfn.XLOOKUP(E128,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9433,17 +9430,17 @@
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A129" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="13">
-        <v>10198</v>
+      <c r="A129" t="s">
+        <v>179</v>
+      </c>
+      <c r="B129" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="3">
+        <v>806</v>
       </c>
       <c r="F129" s="3" t="str">
         <f>IF(E129="","",IF(E129="DNS",0,IF(E129="DQ",0,IF(E129="DNF",1,IF(AND(ISNUMBER(E129),E129&gt;59),1,_xlfn.XLOOKUP(E129,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9484,16 +9481,16 @@
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>382</v>
+        <v>182</v>
       </c>
       <c r="B130" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C130" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D130" s="3">
-        <v>10199</v>
+        <v>868</v>
       </c>
       <c r="F130" s="3" t="str">
         <f>IF(E130="","",IF(E130="DNS",0,IF(E130="DQ",0,IF(E130="DNF",1,IF(AND(ISNUMBER(E130),E130&gt;59),1,_xlfn.XLOOKUP(E130,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9534,16 +9531,16 @@
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>383</v>
+        <v>183</v>
       </c>
       <c r="B131" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C131" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131" s="3">
-        <v>10200</v>
+        <v>1032</v>
       </c>
       <c r="F131" s="3" t="str">
         <f>IF(E131="","",IF(E131="DNS",0,IF(E131="DQ",0,IF(E131="DNF",1,IF(AND(ISNUMBER(E131),E131&gt;59),1,_xlfn.XLOOKUP(E131,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9584,16 +9581,16 @@
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>376</v>
+        <v>187</v>
       </c>
       <c r="B132" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C132" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="3">
-        <v>10193</v>
+        <v>10164</v>
       </c>
       <c r="F132" s="3" t="str">
         <f>IF(E132="","",IF(E132="DNS",0,IF(E132="DQ",0,IF(E132="DNF",1,IF(AND(ISNUMBER(E132),E132&gt;59),1,_xlfn.XLOOKUP(E132,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9634,16 +9631,16 @@
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>380</v>
+        <v>185</v>
       </c>
       <c r="B133" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C133" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="3">
-        <v>10197</v>
+        <v>10162</v>
       </c>
       <c r="F133" s="3" t="str">
         <f>IF(E133="","",IF(E133="DNS",0,IF(E133="DQ",0,IF(E133="DNF",1,IF(AND(ISNUMBER(E133),E133&gt;59),1,_xlfn.XLOOKUP(E133,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9684,16 +9681,16 @@
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>384</v>
+        <v>186</v>
       </c>
       <c r="B134" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C134" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="3">
-        <v>10201</v>
+        <v>10163</v>
       </c>
       <c r="F134" s="3" t="str">
         <f>IF(E134="","",IF(E134="DNS",0,IF(E134="DQ",0,IF(E134="DNF",1,IF(AND(ISNUMBER(E134),E134&gt;59),1,_xlfn.XLOOKUP(E134,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9734,16 +9731,16 @@
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>378</v>
+        <v>184</v>
       </c>
       <c r="B135" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C135" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D135" s="3">
-        <v>10195</v>
+        <v>918</v>
       </c>
       <c r="F135" s="3" t="str">
         <f>IF(E135="","",IF(E135="DNS",0,IF(E135="DQ",0,IF(E135="DNF",1,IF(AND(ISNUMBER(E135),E135&gt;59),1,_xlfn.XLOOKUP(E135,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9784,16 +9781,16 @@
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>379</v>
+        <v>188</v>
       </c>
       <c r="B136" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C136" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D136" s="3">
-        <v>10196</v>
+        <v>12036</v>
       </c>
       <c r="F136" s="3" t="str">
         <f>IF(E136="","",IF(E136="DNS",0,IF(E136="DQ",0,IF(E136="DNF",1,IF(AND(ISNUMBER(E136),E136&gt;59),1,_xlfn.XLOOKUP(E136,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9834,16 +9831,16 @@
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>377</v>
+        <v>189</v>
       </c>
       <c r="B137" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C137" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D137" s="3">
-        <v>10194</v>
+        <v>12037</v>
       </c>
       <c r="F137" s="3" t="str">
         <f>IF(E137="","",IF(E137="DNS",0,IF(E137="DQ",0,IF(E137="DNF",1,IF(AND(ISNUMBER(E137),E137&gt;59),1,_xlfn.XLOOKUP(E137,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9884,16 +9881,16 @@
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>396</v>
+        <v>191</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C138" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D138" s="3">
-        <v>10202</v>
+        <v>810</v>
       </c>
       <c r="F138" s="3" t="str">
         <f>IF(E138="","",IF(E138="DNS",0,IF(E138="DQ",0,IF(E138="DNF",1,IF(AND(ISNUMBER(E138),E138&gt;59),1,_xlfn.XLOOKUP(E138,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9934,16 +9931,16 @@
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C139" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D139" s="3">
-        <v>1027</v>
+        <v>811</v>
       </c>
       <c r="F139" s="3" t="str">
         <f>IF(E139="","",IF(E139="DNS",0,IF(E139="DQ",0,IF(E139="DNF",1,IF(AND(ISNUMBER(E139),E139&gt;59),1,_xlfn.XLOOKUP(E139,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9984,16 +9981,16 @@
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C140" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D140" s="3">
-        <v>1029</v>
+        <v>812</v>
       </c>
       <c r="F140" s="3" t="str">
         <f>IF(E140="","",IF(E140="DNS",0,IF(E140="DQ",0,IF(E140="DNF",1,IF(AND(ISNUMBER(E140),E140&gt;59),1,_xlfn.XLOOKUP(E140,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10034,16 +10031,16 @@
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C141" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D141" s="3">
-        <v>1028</v>
+        <v>809</v>
       </c>
       <c r="F141" s="3" t="str">
         <f>IF(E141="","",IF(E141="DNS",0,IF(E141="DQ",0,IF(E141="DNF",1,IF(AND(ISNUMBER(E141),E141&gt;59),1,_xlfn.XLOOKUP(E141,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10084,16 +10081,16 @@
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C142" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D142" s="3">
-        <v>1019</v>
+        <v>10171</v>
       </c>
       <c r="F142" s="3" t="str">
         <f>IF(E142="","",IF(E142="DNS",0,IF(E142="DQ",0,IF(E142="DNF",1,IF(AND(ISNUMBER(E142),E142&gt;59),1,_xlfn.XLOOKUP(E142,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10134,16 +10131,16 @@
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C143" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D143" s="3">
-        <v>1030</v>
+        <v>10170</v>
       </c>
       <c r="F143" s="3" t="str">
         <f>IF(E143="","",IF(E143="DNS",0,IF(E143="DQ",0,IF(E143="DNF",1,IF(AND(ISNUMBER(E143),E143&gt;59),1,_xlfn.XLOOKUP(E143,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10184,16 +10181,16 @@
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C144" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D144" s="3">
-        <v>1020</v>
+        <v>10166</v>
       </c>
       <c r="F144" s="3" t="str">
         <f>IF(E144="","",IF(E144="DNS",0,IF(E144="DQ",0,IF(E144="DNF",1,IF(AND(ISNUMBER(E144),E144&gt;59),1,_xlfn.XLOOKUP(E144,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10234,16 +10231,16 @@
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B145" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C145" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D145" s="3">
-        <v>1032</v>
+        <v>10167</v>
       </c>
       <c r="F145" s="3" t="str">
         <f>IF(E145="","",IF(E145="DNS",0,IF(E145="DQ",0,IF(E145="DNF",1,IF(AND(ISNUMBER(E145),E145&gt;59),1,_xlfn.XLOOKUP(E145,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10284,16 +10281,16 @@
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B146" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C146" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D146" s="3">
-        <v>1034</v>
+        <v>10165</v>
       </c>
       <c r="F146" s="3" t="str">
         <f>IF(E146="","",IF(E146="DNS",0,IF(E146="DQ",0,IF(E146="DNF",1,IF(AND(ISNUMBER(E146),E146&gt;59),1,_xlfn.XLOOKUP(E146,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10334,16 +10331,16 @@
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C147" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D147" s="3">
-        <v>1033</v>
+        <v>10169</v>
       </c>
       <c r="F147" s="3" t="str">
         <f>IF(E147="","",IF(E147="DNS",0,IF(E147="DQ",0,IF(E147="DNF",1,IF(AND(ISNUMBER(E147),E147&gt;59),1,_xlfn.XLOOKUP(E147,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10384,16 +10381,16 @@
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C148" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D148" s="3">
-        <v>1035</v>
+        <v>10168</v>
       </c>
       <c r="F148" s="3" t="str">
         <f>IF(E148="","",IF(E148="DNS",0,IF(E148="DQ",0,IF(E148="DNF",1,IF(AND(ISNUMBER(E148),E148&gt;59),1,_xlfn.XLOOKUP(E148,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10434,16 +10431,16 @@
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C149" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D149" s="3">
-        <v>1038</v>
+        <v>920</v>
       </c>
       <c r="F149" s="3" t="str">
         <f>IF(E149="","",IF(E149="DNS",0,IF(E149="DQ",0,IF(E149="DNF",1,IF(AND(ISNUMBER(E149),E149&gt;59),1,_xlfn.XLOOKUP(E149,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10484,16 +10481,16 @@
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>265</v>
+        <v>197</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C150" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D150" s="3">
-        <v>1039</v>
+        <v>922</v>
       </c>
       <c r="F150" s="3" t="str">
         <f>IF(E150="","",IF(E150="DNS",0,IF(E150="DQ",0,IF(E150="DNF",1,IF(AND(ISNUMBER(E150),E150&gt;59),1,_xlfn.XLOOKUP(E150,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10534,16 +10531,16 @@
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>263</v>
+        <v>196</v>
       </c>
       <c r="B151" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C151" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D151" s="3">
-        <v>1037</v>
+        <v>921</v>
       </c>
       <c r="F151" s="3" t="str">
         <f>IF(E151="","",IF(E151="DNS",0,IF(E151="DQ",0,IF(E151="DNF",1,IF(AND(ISNUMBER(E151),E151&gt;59),1,_xlfn.XLOOKUP(E151,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10584,16 +10581,16 @@
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="B152" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C152" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D152" s="3">
-        <v>1036</v>
+        <v>919</v>
       </c>
       <c r="F152" s="3" t="str">
         <f>IF(E152="","",IF(E152="DNS",0,IF(E152="DQ",0,IF(E152="DNF",1,IF(AND(ISNUMBER(E152),E152&gt;59),1,_xlfn.XLOOKUP(E152,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10634,16 +10631,16 @@
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>214</v>
       </c>
       <c r="B153" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C153" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D153" s="3">
-        <v>1031</v>
+        <v>12047</v>
       </c>
       <c r="F153" s="3" t="str">
         <f>IF(E153="","",IF(E153="DNS",0,IF(E153="DQ",0,IF(E153="DNF",1,IF(AND(ISNUMBER(E153),E153&gt;59),1,_xlfn.XLOOKUP(E153,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10684,16 +10681,16 @@
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="B154" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D154" s="3">
-        <v>1040</v>
+        <v>12042</v>
       </c>
       <c r="F154" s="3" t="str">
         <f>IF(E154="","",IF(E154="DNS",0,IF(E154="DQ",0,IF(E154="DNF",1,IF(AND(ISNUMBER(E154),E154&gt;59),1,_xlfn.XLOOKUP(E154,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10734,16 +10731,16 @@
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>374</v>
+        <v>212</v>
       </c>
       <c r="B155" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C155" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D155" s="3">
-        <v>1042</v>
+        <v>12045</v>
       </c>
       <c r="F155" s="3" t="str">
         <f>IF(E155="","",IF(E155="DNS",0,IF(E155="DQ",0,IF(E155="DNF",1,IF(AND(ISNUMBER(E155),E155&gt;59),1,_xlfn.XLOOKUP(E155,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10784,16 +10781,16 @@
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>375</v>
+        <v>215</v>
       </c>
       <c r="B156" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C156" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D156" s="3">
-        <v>1043</v>
+        <v>12048</v>
       </c>
       <c r="F156" s="3" t="str">
         <f>IF(E156="","",IF(E156="DNS",0,IF(E156="DQ",0,IF(E156="DNF",1,IF(AND(ISNUMBER(E156),E156&gt;59),1,_xlfn.XLOOKUP(E156,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10834,16 +10831,16 @@
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>373</v>
+        <v>206</v>
       </c>
       <c r="B157" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C157" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D157" s="3">
-        <v>1041</v>
+        <v>12039</v>
       </c>
       <c r="F157" s="3" t="str">
         <f>IF(E157="","",IF(E157="DNS",0,IF(E157="DQ",0,IF(E157="DNF",1,IF(AND(ISNUMBER(E157),E157&gt;59),1,_xlfn.XLOOKUP(E157,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10884,16 +10881,16 @@
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>397</v>
+        <v>205</v>
       </c>
       <c r="B158" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C158" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D158" s="3">
-        <v>1044</v>
+        <v>12038</v>
       </c>
       <c r="F158" s="3" t="str">
         <f>IF(E158="","",IF(E158="DNS",0,IF(E158="DQ",0,IF(E158="DNF",1,IF(AND(ISNUMBER(E158),E158&gt;59),1,_xlfn.XLOOKUP(E158,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10934,16 +10931,16 @@
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="B159" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C159" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D159" s="3">
-        <v>900</v>
+        <v>12040</v>
       </c>
       <c r="F159" s="3" t="str">
         <f>IF(E159="","",IF(E159="DNS",0,IF(E159="DQ",0,IF(E159="DNF",1,IF(AND(ISNUMBER(E159),E159&gt;59),1,_xlfn.XLOOKUP(E159,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10984,16 +10981,16 @@
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C160" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D160" s="3">
-        <v>907</v>
+        <v>12044</v>
       </c>
       <c r="F160" s="3" t="str">
         <f>IF(E160="","",IF(E160="DNS",0,IF(E160="DQ",0,IF(E160="DNF",1,IF(AND(ISNUMBER(E160),E160&gt;59),1,_xlfn.XLOOKUP(E160,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11034,16 +11031,16 @@
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C161" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D161" s="3">
-        <v>909</v>
+        <v>12046</v>
       </c>
       <c r="F161" s="3" t="str">
         <f>IF(E161="","",IF(E161="DNS",0,IF(E161="DQ",0,IF(E161="DNF",1,IF(AND(ISNUMBER(E161),E161&gt;59),1,_xlfn.XLOOKUP(E161,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11084,16 +11081,16 @@
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C162" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D162" s="3">
-        <v>908</v>
+        <v>12043</v>
       </c>
       <c r="F162" s="3" t="str">
         <f>IF(E162="","",IF(E162="DNS",0,IF(E162="DQ",0,IF(E162="DNF",1,IF(AND(ISNUMBER(E162),E162&gt;59),1,_xlfn.XLOOKUP(E162,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11134,16 +11131,16 @@
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C163" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3">
-        <v>903</v>
+        <v>12041</v>
       </c>
       <c r="F163" s="3" t="str">
         <f>IF(E163="","",IF(E163="DNS",0,IF(E163="DQ",0,IF(E163="DNF",1,IF(AND(ISNUMBER(E163),E163&gt;59),1,_xlfn.XLOOKUP(E163,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11184,16 +11181,16 @@
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C164" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D164" s="3">
-        <v>904</v>
+        <v>1234</v>
       </c>
       <c r="F164" s="3" t="str">
         <f>IF(E164="","",IF(E164="DNS",0,IF(E164="DQ",0,IF(E164="DNF",1,IF(AND(ISNUMBER(E164),E164&gt;59),1,_xlfn.XLOOKUP(E164,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11234,16 +11231,16 @@
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="B165" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C165" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D165" s="3">
-        <v>901</v>
+        <v>1236</v>
       </c>
       <c r="F165" s="3" t="str">
         <f>IF(E165="","",IF(E165="DNS",0,IF(E165="DQ",0,IF(E165="DNF",1,IF(AND(ISNUMBER(E165),E165&gt;59),1,_xlfn.XLOOKUP(E165,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11284,16 +11281,16 @@
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="B166" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C166" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D166" s="3">
-        <v>905</v>
+        <v>1235</v>
       </c>
       <c r="F166" s="3" t="str">
         <f>IF(E166="","",IF(E166="DNS",0,IF(E166="DQ",0,IF(E166="DNF",1,IF(AND(ISNUMBER(E166),E166&gt;59),1,_xlfn.XLOOKUP(E166,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11334,16 +11331,16 @@
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="B167" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C167" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D167" s="3">
-        <v>910</v>
+        <v>10177</v>
       </c>
       <c r="F167" s="3" t="str">
         <f>IF(E167="","",IF(E167="DNS",0,IF(E167="DQ",0,IF(E167="DNF",1,IF(AND(ISNUMBER(E167),E167&gt;59),1,_xlfn.XLOOKUP(E167,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11384,16 +11381,16 @@
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="B168" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C168" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D168" s="3">
-        <v>902</v>
+        <v>10174</v>
       </c>
       <c r="F168" s="3" t="str">
         <f>IF(E168="","",IF(E168="DNS",0,IF(E168="DQ",0,IF(E168="DNF",1,IF(AND(ISNUMBER(E168),E168&gt;59),1,_xlfn.XLOOKUP(E168,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11434,16 +11431,16 @@
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="B169" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C169" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D169" s="3">
-        <v>906</v>
+        <v>10175</v>
       </c>
       <c r="F169" s="3" t="str">
         <f>IF(E169="","",IF(E169="DNS",0,IF(E169="DQ",0,IF(E169="DNF",1,IF(AND(ISNUMBER(E169),E169&gt;59),1,_xlfn.XLOOKUP(E169,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11484,16 +11481,16 @@
     </row>
     <row r="170" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="B170" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C170" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D170" s="3">
-        <v>911</v>
+        <v>10172</v>
       </c>
       <c r="F170" s="3" t="str">
         <f>IF(E170="","",IF(E170="DNS",0,IF(E170="DQ",0,IF(E170="DNF",1,IF(AND(ISNUMBER(E170),E170&gt;59),1,_xlfn.XLOOKUP(E170,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11534,16 +11531,16 @@
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>130</v>
+        <v>226</v>
       </c>
       <c r="B171" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C171" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D171" s="3">
-        <v>913</v>
+        <v>10176</v>
       </c>
       <c r="F171" s="3" t="str">
         <f>IF(E171="","",IF(E171="DNS",0,IF(E171="DQ",0,IF(E171="DNF",1,IF(AND(ISNUMBER(E171),E171&gt;59),1,_xlfn.XLOOKUP(E171,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11584,16 +11581,16 @@
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="B172" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C172" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D172" s="3">
-        <v>912</v>
+        <v>10173</v>
       </c>
       <c r="F172" s="3" t="str">
         <f>IF(E172="","",IF(E172="DNS",0,IF(E172="DQ",0,IF(E172="DNF",1,IF(AND(ISNUMBER(E172),E172&gt;59),1,_xlfn.XLOOKUP(E172,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11634,16 +11631,16 @@
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>162</v>
+        <v>228</v>
       </c>
       <c r="B173" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C173" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D173" s="3">
-        <v>915</v>
+        <v>10178</v>
       </c>
       <c r="F173" s="3" t="str">
         <f>IF(E173="","",IF(E173="DNS",0,IF(E173="DQ",0,IF(E173="DNF",1,IF(AND(ISNUMBER(E173),E173&gt;59),1,_xlfn.XLOOKUP(E173,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11684,16 +11681,16 @@
     </row>
     <row r="174" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="B174" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D174" s="3">
-        <v>916</v>
+        <v>1034</v>
       </c>
       <c r="F174" s="3" t="str">
         <f>IF(E174="","",IF(E174="DNS",0,IF(E174="DQ",0,IF(E174="DNF",1,IF(AND(ISNUMBER(E174),E174&gt;59),1,_xlfn.XLOOKUP(E174,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11734,16 +11731,16 @@
     </row>
     <row r="175" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="B175" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D175" s="3">
-        <v>917</v>
+        <v>1033</v>
       </c>
       <c r="F175" s="3" t="str">
         <f>IF(E175="","",IF(E175="DNS",0,IF(E175="DQ",0,IF(E175="DNF",1,IF(AND(ISNUMBER(E175),E175&gt;59),1,_xlfn.XLOOKUP(E175,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11784,16 +11781,16 @@
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="B176" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C176" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D176" s="3">
-        <v>914</v>
+        <v>1035</v>
       </c>
       <c r="F176" s="3" t="str">
         <f>IF(E176="","",IF(E176="DNS",0,IF(E176="DQ",0,IF(E176="DNF",1,IF(AND(ISNUMBER(E176),E176&gt;59),1,_xlfn.XLOOKUP(E176,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11834,16 +11831,16 @@
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B177" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C177" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D177" s="3">
-        <v>957</v>
+        <v>12058</v>
       </c>
       <c r="F177" s="3" t="str">
         <f>IF(E177="","",IF(E177="DNS",0,IF(E177="DQ",0,IF(E177="DNF",1,IF(AND(ISNUMBER(E177),E177&gt;59),1,_xlfn.XLOOKUP(E177,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11884,16 +11881,16 @@
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="B178" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C178" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D178" s="3">
-        <v>955</v>
+        <v>12057</v>
       </c>
       <c r="F178" s="3" t="str">
         <f>IF(E178="","",IF(E178="DNS",0,IF(E178="DQ",0,IF(E178="DNF",1,IF(AND(ISNUMBER(E178),E178&gt;59),1,_xlfn.XLOOKUP(E178,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11934,16 +11931,16 @@
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="B179" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C179" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D179" s="3">
-        <v>956</v>
+        <v>12059</v>
       </c>
       <c r="F179" s="3" t="str">
         <f>IF(E179="","",IF(E179="DNS",0,IF(E179="DQ",0,IF(E179="DNF",1,IF(AND(ISNUMBER(E179),E179&gt;59),1,_xlfn.XLOOKUP(E179,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11984,16 +11981,16 @@
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="B180" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C180" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D180" s="3">
-        <v>918</v>
+        <v>12054</v>
       </c>
       <c r="F180" s="3" t="str">
         <f>IF(E180="","",IF(E180="DNS",0,IF(E180="DQ",0,IF(E180="DNF",1,IF(AND(ISNUMBER(E180),E180&gt;59),1,_xlfn.XLOOKUP(E180,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12034,16 +12031,16 @@
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="B181" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C181" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D181" s="3">
-        <v>920</v>
+        <v>12060</v>
       </c>
       <c r="F181" s="3" t="str">
         <f>IF(E181="","",IF(E181="DNS",0,IF(E181="DQ",0,IF(E181="DNF",1,IF(AND(ISNUMBER(E181),E181&gt;59),1,_xlfn.XLOOKUP(E181,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12084,16 +12081,16 @@
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="B182" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C182" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D182" s="3">
-        <v>922</v>
+        <v>12049</v>
       </c>
       <c r="F182" s="3" t="str">
         <f>IF(E182="","",IF(E182="DNS",0,IF(E182="DQ",0,IF(E182="DNF",1,IF(AND(ISNUMBER(E182),E182&gt;59),1,_xlfn.XLOOKUP(E182,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12134,16 +12131,16 @@
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="B183" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C183" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D183" s="3">
-        <v>921</v>
+        <v>12055</v>
       </c>
       <c r="F183" s="3" t="str">
         <f>IF(E183="","",IF(E183="DNS",0,IF(E183="DQ",0,IF(E183="DNF",1,IF(AND(ISNUMBER(E183),E183&gt;59),1,_xlfn.XLOOKUP(E183,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12184,16 +12181,16 @@
     </row>
     <row r="184" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="B184" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C184" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D184" s="3">
-        <v>919</v>
+        <v>12050</v>
       </c>
       <c r="F184" s="3" t="str">
         <f>IF(E184="","",IF(E184="DNS",0,IF(E184="DQ",0,IF(E184="DNF",1,IF(AND(ISNUMBER(E184),E184&gt;59),1,_xlfn.XLOOKUP(E184,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12234,16 +12231,16 @@
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B185" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D185" s="3">
-        <v>923</v>
+        <v>12052</v>
       </c>
       <c r="F185" s="3" t="str">
         <f>IF(E185="","",IF(E185="DNS",0,IF(E185="DQ",0,IF(E185="DNF",1,IF(AND(ISNUMBER(E185),E185&gt;59),1,_xlfn.XLOOKUP(E185,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12284,16 +12281,16 @@
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="B186" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C186" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D186" s="3">
-        <v>924</v>
+        <v>12053</v>
       </c>
       <c r="F186" s="3" t="str">
         <f>IF(E186="","",IF(E186="DNS",0,IF(E186="DQ",0,IF(E186="DNF",1,IF(AND(ISNUMBER(E186),E186&gt;59),1,_xlfn.XLOOKUP(E186,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12334,16 +12331,16 @@
     </row>
     <row r="187" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="B187" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C187" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D187" s="3">
-        <v>925</v>
+        <v>12051</v>
       </c>
       <c r="F187" s="3" t="str">
         <f>IF(E187="","",IF(E187="DNS",0,IF(E187="DQ",0,IF(E187="DNF",1,IF(AND(ISNUMBER(E187),E187&gt;59),1,_xlfn.XLOOKUP(E187,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12384,16 +12381,16 @@
     </row>
     <row r="188" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="B188" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C188" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D188" s="3">
-        <v>926</v>
+        <v>12056</v>
       </c>
       <c r="F188" s="3" t="str">
         <f>IF(E188="","",IF(E188="DNS",0,IF(E188="DQ",0,IF(E188="DNF",1,IF(AND(ISNUMBER(E188),E188&gt;59),1,_xlfn.XLOOKUP(E188,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12434,16 +12431,16 @@
     </row>
     <row r="189" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="B189" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C189" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D189" s="3">
-        <v>927</v>
+        <v>1238</v>
       </c>
       <c r="F189" s="3" t="str">
         <f>IF(E189="","",IF(E189="DNS",0,IF(E189="DQ",0,IF(E189="DNF",1,IF(AND(ISNUMBER(E189),E189&gt;59),1,_xlfn.XLOOKUP(E189,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12484,16 +12481,16 @@
     </row>
     <row r="190" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="B190" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C190" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D190" s="3">
-        <v>928</v>
+        <v>1237</v>
       </c>
       <c r="F190" s="3" t="str">
         <f>IF(E190="","",IF(E190="DNS",0,IF(E190="DQ",0,IF(E190="DNF",1,IF(AND(ISNUMBER(E190),E190&gt;59),1,_xlfn.XLOOKUP(E190,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12534,16 +12531,16 @@
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="B191" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C191" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D191" s="3">
-        <v>934</v>
+        <v>813</v>
       </c>
       <c r="F191" s="3" t="str">
         <f>IF(E191="","",IF(E191="DNS",0,IF(E191="DQ",0,IF(E191="DNF",1,IF(AND(ISNUMBER(E191),E191&gt;59),1,_xlfn.XLOOKUP(E191,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12584,16 +12581,16 @@
     </row>
     <row r="192" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="B192" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C192" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D192" s="3">
-        <v>935</v>
+        <v>814</v>
       </c>
       <c r="F192" s="3" t="str">
         <f>IF(E192="","",IF(E192="DNS",0,IF(E192="DQ",0,IF(E192="DNF",1,IF(AND(ISNUMBER(E192),E192&gt;59),1,_xlfn.XLOOKUP(E192,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12634,16 +12631,16 @@
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="B193" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C193" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D193" s="3">
-        <v>931</v>
+        <v>10180</v>
       </c>
       <c r="F193" s="3" t="str">
         <f>IF(E193="","",IF(E193="DNS",0,IF(E193="DQ",0,IF(E193="DNF",1,IF(AND(ISNUMBER(E193),E193&gt;59),1,_xlfn.XLOOKUP(E193,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12684,16 +12681,16 @@
     </row>
     <row r="194" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>301</v>
+        <v>246</v>
       </c>
       <c r="B194" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C194" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D194" s="3">
-        <v>936</v>
+        <v>10179</v>
       </c>
       <c r="F194" s="3" t="str">
         <f>IF(E194="","",IF(E194="DNS",0,IF(E194="DQ",0,IF(E194="DNF",1,IF(AND(ISNUMBER(E194),E194&gt;59),1,_xlfn.XLOOKUP(E194,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12734,16 +12731,16 @@
     </row>
     <row r="195" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="B195" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
       </c>
       <c r="D195" s="3">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="F195" s="3" t="str">
         <f>IF(E195="","",IF(E195="DNS",0,IF(E195="DQ",0,IF(E195="DNF",1,IF(AND(ISNUMBER(E195),E195&gt;59),1,_xlfn.XLOOKUP(E195,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12784,16 +12781,16 @@
     </row>
     <row r="196" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="B196" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C196" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D196" s="3">
-        <v>929</v>
+        <v>816</v>
       </c>
       <c r="F196" s="3" t="str">
         <f>IF(E196="","",IF(E196="DNS",0,IF(E196="DQ",0,IF(E196="DNF",1,IF(AND(ISNUMBER(E196),E196&gt;59),1,_xlfn.XLOOKUP(E196,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12834,16 +12831,16 @@
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="B197" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C197" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D197" s="3">
-        <v>937</v>
+        <v>815</v>
       </c>
       <c r="F197" s="3" t="str">
         <f>IF(E197="","",IF(E197="DNS",0,IF(E197="DQ",0,IF(E197="DNF",1,IF(AND(ISNUMBER(E197),E197&gt;59),1,_xlfn.XLOOKUP(E197,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12884,16 +12881,16 @@
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="B198" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C198" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D198" s="3">
-        <v>930</v>
+        <v>817</v>
       </c>
       <c r="F198" s="3" t="str">
         <f>IF(E198="","",IF(E198="DNS",0,IF(E198="DQ",0,IF(E198="DNF",1,IF(AND(ISNUMBER(E198),E198&gt;59),1,_xlfn.XLOOKUP(E198,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12934,16 +12931,16 @@
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>303</v>
+        <v>250</v>
       </c>
       <c r="B199" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C199" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D199" s="3">
-        <v>938</v>
+        <v>864</v>
       </c>
       <c r="F199" s="3" t="str">
         <f>IF(E199="","",IF(E199="DNS",0,IF(E199="DQ",0,IF(E199="DNF",1,IF(AND(ISNUMBER(E199),E199&gt;59),1,_xlfn.XLOOKUP(E199,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12984,16 +12981,16 @@
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="B200" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C200" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D200" s="3">
-        <v>933</v>
+        <v>862</v>
       </c>
       <c r="F200" s="3" t="str">
         <f>IF(E200="","",IF(E200="DNS",0,IF(E200="DQ",0,IF(E200="DNF",1,IF(AND(ISNUMBER(E200),E200&gt;59),1,_xlfn.XLOOKUP(E200,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13034,16 +13031,16 @@
     </row>
     <row r="201" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="B201" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C201" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D201" s="3">
-        <v>940</v>
+        <v>863</v>
       </c>
       <c r="F201" s="3" t="str">
         <f>IF(E201="","",IF(E201="DNS",0,IF(E201="DQ",0,IF(E201="DNF",1,IF(AND(ISNUMBER(E201),E201&gt;59),1,_xlfn.XLOOKUP(E201,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13084,16 +13081,16 @@
     </row>
     <row r="202" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="B202" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C202" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D202" s="3">
-        <v>939</v>
+        <v>10183</v>
       </c>
       <c r="F202" s="3" t="str">
         <f>IF(E202="","",IF(E202="DNS",0,IF(E202="DQ",0,IF(E202="DNF",1,IF(AND(ISNUMBER(E202),E202&gt;59),1,_xlfn.XLOOKUP(E202,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13134,16 +13131,16 @@
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>326</v>
+        <v>269</v>
       </c>
       <c r="B203" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C203" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D203" s="3">
-        <v>943</v>
+        <v>10184</v>
       </c>
       <c r="F203" s="3" t="str">
         <f>IF(E203="","",IF(E203="DNS",0,IF(E203="DQ",0,IF(E203="DNF",1,IF(AND(ISNUMBER(E203),E203&gt;59),1,_xlfn.XLOOKUP(E203,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13184,16 +13181,16 @@
     </row>
     <row r="204" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="B204" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D204" s="3">
-        <v>944</v>
+        <v>10182</v>
       </c>
       <c r="F204" s="3" t="str">
         <f>IF(E204="","",IF(E204="DNS",0,IF(E204="DQ",0,IF(E204="DNF",1,IF(AND(ISNUMBER(E204),E204&gt;59),1,_xlfn.XLOOKUP(E204,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13234,16 +13231,16 @@
     </row>
     <row r="205" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>324</v>
+        <v>266</v>
       </c>
       <c r="B205" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C205" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D205" s="3">
-        <v>941</v>
+        <v>10181</v>
       </c>
       <c r="F205" s="3" t="str">
         <f>IF(E205="","",IF(E205="DNS",0,IF(E205="DQ",0,IF(E205="DNF",1,IF(AND(ISNUMBER(E205),E205&gt;59),1,_xlfn.XLOOKUP(E205,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13284,16 +13281,16 @@
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="B206" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C206" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D206" s="3">
-        <v>942</v>
+        <v>10186</v>
       </c>
       <c r="F206" s="3" t="str">
         <f>IF(E206="","",IF(E206="DNS",0,IF(E206="DQ",0,IF(E206="DNF",1,IF(AND(ISNUMBER(E206),E206&gt;59),1,_xlfn.XLOOKUP(E206,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13334,16 +13331,16 @@
     </row>
     <row r="207" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>344</v>
+        <v>270</v>
       </c>
       <c r="B207" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C207" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D207" s="3">
-        <v>946</v>
+        <v>10185</v>
       </c>
       <c r="F207" s="3" t="str">
         <f>IF(E207="","",IF(E207="DNS",0,IF(E207="DQ",0,IF(E207="DNF",1,IF(AND(ISNUMBER(E207),E207&gt;59),1,_xlfn.XLOOKUP(E207,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13384,16 +13381,16 @@
     </row>
     <row r="208" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>345</v>
+        <v>264</v>
       </c>
       <c r="B208" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C208" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D208" s="3">
-        <v>947</v>
+        <v>1038</v>
       </c>
       <c r="F208" s="3" t="str">
         <f>IF(E208="","",IF(E208="DNS",0,IF(E208="DQ",0,IF(E208="DNF",1,IF(AND(ISNUMBER(E208),E208&gt;59),1,_xlfn.XLOOKUP(E208,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13434,16 +13431,16 @@
     </row>
     <row r="209" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>346</v>
+        <v>265</v>
       </c>
       <c r="B209" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C209" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D209" s="3">
-        <v>948</v>
+        <v>1039</v>
       </c>
       <c r="F209" s="3" t="str">
         <f>IF(E209="","",IF(E209="DNS",0,IF(E209="DQ",0,IF(E209="DNF",1,IF(AND(ISNUMBER(E209),E209&gt;59),1,_xlfn.XLOOKUP(E209,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13484,16 +13481,16 @@
     </row>
     <row r="210" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>343</v>
+        <v>263</v>
       </c>
       <c r="B210" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C210" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D210" s="3">
-        <v>945</v>
+        <v>1037</v>
       </c>
       <c r="F210" s="3" t="str">
         <f>IF(E210="","",IF(E210="DNS",0,IF(E210="DQ",0,IF(E210="DNF",1,IF(AND(ISNUMBER(E210),E210&gt;59),1,_xlfn.XLOOKUP(E210,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13534,16 +13531,16 @@
     </row>
     <row r="211" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>347</v>
+        <v>262</v>
       </c>
       <c r="B211" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C211" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D211" s="3">
-        <v>949</v>
+        <v>1036</v>
       </c>
       <c r="F211" s="3" t="str">
         <f>IF(E211="","",IF(E211="DNS",0,IF(E211="DQ",0,IF(E211="DNF",1,IF(AND(ISNUMBER(E211),E211&gt;59),1,_xlfn.XLOOKUP(E211,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13584,16 +13581,16 @@
     </row>
     <row r="212" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="B212" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
       </c>
       <c r="D212" s="3">
-        <v>951</v>
+        <v>924</v>
       </c>
       <c r="F212" s="3" t="str">
         <f>IF(E212="","",IF(E212="DNS",0,IF(E212="DQ",0,IF(E212="DNF",1,IF(AND(ISNUMBER(E212),E212&gt;59),1,_xlfn.XLOOKUP(E212,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13634,16 +13631,16 @@
     </row>
     <row r="213" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>360</v>
+        <v>258</v>
       </c>
       <c r="B213" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="3">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="F213" s="3" t="str">
         <f>IF(E213="","",IF(E213="DNS",0,IF(E213="DQ",0,IF(E213="DNF",1,IF(AND(ISNUMBER(E213),E213&gt;59),1,_xlfn.XLOOKUP(E213,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13684,16 +13681,16 @@
     </row>
     <row r="214" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>394</v>
+        <v>259</v>
       </c>
       <c r="B214" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C214" t="s">
         <v>5</v>
       </c>
       <c r="D214" s="3">
-        <v>953</v>
+        <v>926</v>
       </c>
       <c r="F214" s="3" t="str">
         <f>IF(E214="","",IF(E214="DNS",0,IF(E214="DQ",0,IF(E214="DNF",1,IF(AND(ISNUMBER(E214),E214&gt;59),1,_xlfn.XLOOKUP(E214,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13734,16 +13731,16 @@
     </row>
     <row r="215" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>393</v>
+        <v>260</v>
       </c>
       <c r="B215" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="3">
-        <v>952</v>
+        <v>927</v>
       </c>
       <c r="F215" s="3" t="str">
         <f>IF(E215="","",IF(E215="DNS",0,IF(E215="DQ",0,IF(E215="DNF",1,IF(AND(ISNUMBER(E215),E215&gt;59),1,_xlfn.XLOOKUP(E215,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13784,16 +13781,16 @@
     </row>
     <row r="216" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>395</v>
+        <v>261</v>
       </c>
       <c r="B216" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C216" t="s">
         <v>5</v>
       </c>
       <c r="D216" s="3">
-        <v>954</v>
+        <v>928</v>
       </c>
       <c r="F216" s="3" t="str">
         <f>IF(E216="","",IF(E216="DNS",0,IF(E216="DQ",0,IF(E216="DNF",1,IF(AND(ISNUMBER(E216),E216&gt;59),1,_xlfn.XLOOKUP(E216,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13834,16 +13831,16 @@
     </row>
     <row r="217" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>70</v>
+        <v>255</v>
       </c>
       <c r="B217" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C217" t="s">
         <v>6</v>
       </c>
       <c r="D217" s="3">
-        <v>9471</v>
+        <v>927</v>
       </c>
       <c r="F217" s="3" t="str">
         <f>IF(E217="","",IF(E217="DNS",0,IF(E217="DQ",0,IF(E217="DNF",1,IF(AND(ISNUMBER(E217),E217&gt;59),1,_xlfn.XLOOKUP(E217,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13884,16 +13881,16 @@
     </row>
     <row r="218" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>67</v>
+        <v>254</v>
       </c>
       <c r="B218" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C218" t="s">
         <v>6</v>
       </c>
       <c r="D218" s="3">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="F218" s="3" t="str">
         <f>IF(E218="","",IF(E218="DNS",0,IF(E218="DQ",0,IF(E218="DNF",1,IF(AND(ISNUMBER(E218),E218&gt;59),1,_xlfn.XLOOKUP(E218,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13934,16 +13931,16 @@
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>68</v>
+        <v>256</v>
       </c>
       <c r="B219" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C219" t="s">
         <v>6</v>
       </c>
       <c r="D219" s="3">
-        <v>9421</v>
+        <v>928</v>
       </c>
       <c r="F219" s="3" t="str">
         <f>IF(E219="","",IF(E219="DNS",0,IF(E219="DQ",0,IF(E219="DNF",1,IF(AND(ISNUMBER(E219),E219&gt;59),1,_xlfn.XLOOKUP(E219,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13984,16 +13981,16 @@
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>69</v>
+        <v>284</v>
       </c>
       <c r="B220" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C220" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D220" s="3">
-        <v>9451</v>
+        <v>12069</v>
       </c>
       <c r="F220" s="3" t="str">
         <f>IF(E220="","",IF(E220="DNS",0,IF(E220="DQ",0,IF(E220="DNF",1,IF(AND(ISNUMBER(E220),E220&gt;59),1,_xlfn.XLOOKUP(E220,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14034,16 +14031,16 @@
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>71</v>
+        <v>279</v>
       </c>
       <c r="B221" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C221" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D221" s="3">
-        <v>9481</v>
+        <v>12064</v>
       </c>
       <c r="F221" s="3" t="str">
         <f>IF(E221="","",IF(E221="DNS",0,IF(E221="DQ",0,IF(E221="DNF",1,IF(AND(ISNUMBER(E221),E221&gt;59),1,_xlfn.XLOOKUP(E221,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14084,16 +14081,16 @@
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>111</v>
+        <v>281</v>
       </c>
       <c r="B222" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C222" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D222" s="3">
-        <v>929</v>
+        <v>12066</v>
       </c>
       <c r="F222" s="3" t="str">
         <f>IF(E222="","",IF(E222="DNS",0,IF(E222="DQ",0,IF(E222="DNF",1,IF(AND(ISNUMBER(E222),E222&gt;59),1,_xlfn.XLOOKUP(E222,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14134,16 +14131,16 @@
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>155</v>
+        <v>280</v>
       </c>
       <c r="B223" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C223" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D223" s="3">
-        <v>9491</v>
+        <v>12065</v>
       </c>
       <c r="F223" s="3" t="str">
         <f>IF(E223="","",IF(E223="DNS",0,IF(E223="DQ",0,IF(E223="DNF",1,IF(AND(ISNUMBER(E223),E223&gt;59),1,_xlfn.XLOOKUP(E223,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14184,16 +14181,16 @@
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>165</v>
+        <v>282</v>
       </c>
       <c r="B224" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C224" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D224" s="3">
-        <v>925</v>
+        <v>12067</v>
       </c>
       <c r="F224" s="3" t="str">
         <f>IF(E224="","",IF(E224="DNS",0,IF(E224="DQ",0,IF(E224="DNF",1,IF(AND(ISNUMBER(E224),E224&gt;59),1,_xlfn.XLOOKUP(E224,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14234,16 +14231,16 @@
     </row>
     <row r="225" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B225" t="s">
         <v>24</v>
       </c>
       <c r="C225" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D225" s="3">
-        <v>927</v>
+        <v>12062</v>
       </c>
       <c r="F225" s="3" t="str">
         <f>IF(E225="","",IF(E225="DNS",0,IF(E225="DQ",0,IF(E225="DNF",1,IF(AND(ISNUMBER(E225),E225&gt;59),1,_xlfn.XLOOKUP(E225,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14284,16 +14281,16 @@
     </row>
     <row r="226" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="B226" t="s">
         <v>24</v>
       </c>
       <c r="C226" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D226" s="3">
-        <v>926</v>
+        <v>12071</v>
       </c>
       <c r="F226" s="3" t="str">
         <f>IF(E226="","",IF(E226="DNS",0,IF(E226="DQ",0,IF(E226="DNF",1,IF(AND(ISNUMBER(E226),E226&gt;59),1,_xlfn.XLOOKUP(E226,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14334,16 +14331,16 @@
     </row>
     <row r="227" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="B227" t="s">
         <v>24</v>
       </c>
       <c r="C227" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D227" s="3">
-        <v>928</v>
+        <v>12070</v>
       </c>
       <c r="F227" s="3" t="str">
         <f>IF(E227="","",IF(E227="DNS",0,IF(E227="DQ",0,IF(E227="DNF",1,IF(AND(ISNUMBER(E227),E227&gt;59),1,_xlfn.XLOOKUP(E227,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14384,16 +14381,16 @@
     </row>
     <row r="228" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="B228" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C228" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D228" s="3">
-        <v>920</v>
+        <v>12068</v>
       </c>
       <c r="F228" s="3" t="str">
         <f>IF(E228="","",IF(E228="DNS",0,IF(E228="DQ",0,IF(E228="DNF",1,IF(AND(ISNUMBER(E228),E228&gt;59),1,_xlfn.XLOOKUP(E228,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14434,16 +14431,16 @@
     </row>
     <row r="229" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>372</v>
+        <v>276</v>
       </c>
       <c r="B229" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C229" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D229" s="3">
-        <v>935</v>
+        <v>12061</v>
       </c>
       <c r="F229" s="3" t="str">
         <f>IF(E229="","",IF(E229="DNS",0,IF(E229="DQ",0,IF(E229="DNF",1,IF(AND(ISNUMBER(E229),E229&gt;59),1,_xlfn.XLOOKUP(E229,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14484,16 +14481,16 @@
     </row>
     <row r="230" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>370</v>
+        <v>278</v>
       </c>
       <c r="B230" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C230" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D230" s="3">
-        <v>933</v>
+        <v>12063</v>
       </c>
       <c r="F230" s="3" t="str">
         <f>IF(E230="","",IF(E230="DNS",0,IF(E230="DQ",0,IF(E230="DNF",1,IF(AND(ISNUMBER(E230),E230&gt;59),1,_xlfn.XLOOKUP(E230,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14534,16 +14531,16 @@
     </row>
     <row r="231" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>368</v>
+        <v>272</v>
       </c>
       <c r="B231" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C231" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D231" s="3">
-        <v>931</v>
+        <v>1239</v>
       </c>
       <c r="F231" s="3" t="str">
         <f>IF(E231="","",IF(E231="DNS",0,IF(E231="DQ",0,IF(E231="DNF",1,IF(AND(ISNUMBER(E231),E231&gt;59),1,_xlfn.XLOOKUP(E231,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14584,16 +14581,16 @@
     </row>
     <row r="232" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>369</v>
+        <v>274</v>
       </c>
       <c r="B232" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C232" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D232" s="3">
-        <v>932</v>
+        <v>1241</v>
       </c>
       <c r="F232" s="3" t="str">
         <f>IF(E232="","",IF(E232="DNS",0,IF(E232="DQ",0,IF(E232="DNF",1,IF(AND(ISNUMBER(E232),E232&gt;59),1,_xlfn.XLOOKUP(E232,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14634,16 +14631,16 @@
     </row>
     <row r="233" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>371</v>
+        <v>275</v>
       </c>
       <c r="B233" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C233" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D233" s="3">
-        <v>934</v>
+        <v>1242</v>
       </c>
       <c r="F233" s="3" t="str">
         <f>IF(E233="","",IF(E233="DNS",0,IF(E233="DQ",0,IF(E233="DNF",1,IF(AND(ISNUMBER(E233),E233&gt;59),1,_xlfn.XLOOKUP(E233,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14684,16 +14681,16 @@
     </row>
     <row r="234" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="B234" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C234" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" s="3">
-        <v>12017</v>
+        <v>1240</v>
       </c>
       <c r="F234" s="3" t="str">
         <f>IF(E234="","",IF(E234="DNS",0,IF(E234="DQ",0,IF(E234="DNF",1,IF(AND(ISNUMBER(E234),E234&gt;59),1,_xlfn.XLOOKUP(E234,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14734,16 +14731,16 @@
     </row>
     <row r="235" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="B235" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C235" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D235" s="3">
-        <v>12013</v>
+        <v>819</v>
       </c>
       <c r="F235" s="3" t="str">
         <f>IF(E235="","",IF(E235="DNS",0,IF(E235="DQ",0,IF(E235="DNF",1,IF(AND(ISNUMBER(E235),E235&gt;59),1,_xlfn.XLOOKUP(E235,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14784,16 +14781,16 @@
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="B236" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C236" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D236" s="3">
-        <v>12016</v>
+        <v>818</v>
       </c>
       <c r="F236" s="3" t="str">
         <f>IF(E236="","",IF(E236="DNS",0,IF(E236="DQ",0,IF(E236="DNF",1,IF(AND(ISNUMBER(E236),E236&gt;59),1,_xlfn.XLOOKUP(E236,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14834,16 +14831,16 @@
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="B237" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C237" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D237" s="3">
-        <v>12005</v>
+        <v>10187</v>
       </c>
       <c r="F237" s="3" t="str">
         <f>IF(E237="","",IF(E237="DNS",0,IF(E237="DQ",0,IF(E237="DNF",1,IF(AND(ISNUMBER(E237),E237&gt;59),1,_xlfn.XLOOKUP(E237,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14884,16 +14881,16 @@
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>99</v>
+        <v>290</v>
       </c>
       <c r="B238" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C238" t="s">
         <v>1</v>
       </c>
       <c r="D238" s="3">
-        <v>12001</v>
+        <v>12072</v>
       </c>
       <c r="F238" s="3" t="str">
         <f>IF(E238="","",IF(E238="DNS",0,IF(E238="DQ",0,IF(E238="DNF",1,IF(AND(ISNUMBER(E238),E238&gt;59),1,_xlfn.XLOOKUP(E238,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14934,16 +14931,16 @@
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>101</v>
+        <v>292</v>
       </c>
       <c r="B239" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C239" t="s">
         <v>1</v>
       </c>
       <c r="D239" s="3">
-        <v>12009</v>
+        <v>12074</v>
       </c>
       <c r="F239" s="3" t="str">
         <f>IF(E239="","",IF(E239="DNS",0,IF(E239="DQ",0,IF(E239="DNF",1,IF(AND(ISNUMBER(E239),E239&gt;59),1,_xlfn.XLOOKUP(E239,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14984,16 +14981,16 @@
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="B240" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C240" t="s">
         <v>1</v>
       </c>
       <c r="D240" s="3">
-        <v>12015</v>
+        <v>12073</v>
       </c>
       <c r="F240" s="3" t="str">
         <f>IF(E240="","",IF(E240="DNS",0,IF(E240="DQ",0,IF(E240="DNF",1,IF(AND(ISNUMBER(E240),E240&gt;59),1,_xlfn.XLOOKUP(E240,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15034,16 +15031,16 @@
     </row>
     <row r="241" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>104</v>
+        <v>293</v>
       </c>
       <c r="B241" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C241" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D241" s="3">
-        <v>12014</v>
+        <v>865</v>
       </c>
       <c r="F241" s="3" t="str">
         <f>IF(E241="","",IF(E241="DNS",0,IF(E241="DQ",0,IF(E241="DNF",1,IF(AND(ISNUMBER(E241),E241&gt;59),1,_xlfn.XLOOKUP(E241,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15084,16 +15081,16 @@
     </row>
     <row r="242" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>102</v>
+        <v>307</v>
       </c>
       <c r="B242" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C242" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D242" s="3">
-        <v>12012</v>
+        <v>10189</v>
       </c>
       <c r="F242" s="3" t="str">
         <f>IF(E242="","",IF(E242="DNS",0,IF(E242="DQ",0,IF(E242="DNF",1,IF(AND(ISNUMBER(E242),E242&gt;59),1,_xlfn.XLOOKUP(E242,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15134,16 +15131,16 @@
     </row>
     <row r="243" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>116</v>
+        <v>306</v>
       </c>
       <c r="B243" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C243" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D243" s="3">
-        <v>12018</v>
+        <v>10188</v>
       </c>
       <c r="F243" s="3" t="str">
         <f>IF(E243="","",IF(E243="DNS",0,IF(E243="DQ",0,IF(E243="DNF",1,IF(AND(ISNUMBER(E243),E243&gt;59),1,_xlfn.XLOOKUP(E243,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15184,16 +15181,16 @@
     </row>
     <row r="244" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>117</v>
+        <v>305</v>
       </c>
       <c r="B244" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C244" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D244" s="3">
-        <v>12019</v>
+        <v>1031</v>
       </c>
       <c r="F244" s="3" t="str">
         <f>IF(E244="","",IF(E244="DNS",0,IF(E244="DQ",0,IF(E244="DNF",1,IF(AND(ISNUMBER(E244),E244&gt;59),1,_xlfn.XLOOKUP(E244,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15234,16 +15231,16 @@
     </row>
     <row r="245" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>122</v>
+        <v>299</v>
       </c>
       <c r="B245" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C245" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D245" s="3">
-        <v>12020</v>
+        <v>934</v>
       </c>
       <c r="F245" s="3" t="str">
         <f>IF(E245="","",IF(E245="DNS",0,IF(E245="DQ",0,IF(E245="DNF",1,IF(AND(ISNUMBER(E245),E245&gt;59),1,_xlfn.XLOOKUP(E245,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15284,16 +15281,16 @@
     </row>
     <row r="246" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>123</v>
+        <v>300</v>
       </c>
       <c r="B246" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C246" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D246" s="3">
-        <v>12021</v>
+        <v>935</v>
       </c>
       <c r="F246" s="3" t="str">
         <f>IF(E246="","",IF(E246="DNS",0,IF(E246="DQ",0,IF(E246="DNF",1,IF(AND(ISNUMBER(E246),E246&gt;59),1,_xlfn.XLOOKUP(E246,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15334,16 +15331,16 @@
     </row>
     <row r="247" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>124</v>
+        <v>296</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C247" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D247" s="3">
-        <v>12022</v>
+        <v>931</v>
       </c>
       <c r="F247" s="3" t="str">
         <f>IF(E247="","",IF(E247="DNS",0,IF(E247="DQ",0,IF(E247="DNF",1,IF(AND(ISNUMBER(E247),E247&gt;59),1,_xlfn.XLOOKUP(E247,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15384,16 +15381,16 @@
     </row>
     <row r="248" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>125</v>
+        <v>301</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C248" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D248" s="3">
-        <v>12023</v>
+        <v>936</v>
       </c>
       <c r="F248" s="3" t="str">
         <f>IF(E248="","",IF(E248="DNS",0,IF(E248="DQ",0,IF(E248="DNF",1,IF(AND(ISNUMBER(E248),E248&gt;59),1,_xlfn.XLOOKUP(E248,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15433,14 +15430,17 @@
       </c>
     </row>
     <row r="249" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A249" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B249" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C249" s="11" t="s">
-        <v>1</v>
+      <c r="A249" t="s">
+        <v>297</v>
+      </c>
+      <c r="B249" t="s">
+        <v>26</v>
+      </c>
+      <c r="C249" t="s">
+        <v>5</v>
+      </c>
+      <c r="D249" s="3">
+        <v>932</v>
       </c>
       <c r="F249" s="3" t="str">
         <f>IF(E249="","",IF(E249="DNS",0,IF(E249="DQ",0,IF(E249="DNF",1,IF(AND(ISNUMBER(E249),E249&gt;59),1,_xlfn.XLOOKUP(E249,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15481,16 +15481,16 @@
     </row>
     <row r="250" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>135</v>
+        <v>294</v>
       </c>
       <c r="B250" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C250" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D250" s="3">
-        <v>12026</v>
+        <v>929</v>
       </c>
       <c r="F250" s="3" t="str">
         <f>IF(E250="","",IF(E250="DNS",0,IF(E250="DQ",0,IF(E250="DNF",1,IF(AND(ISNUMBER(E250),E250&gt;59),1,_xlfn.XLOOKUP(E250,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15531,16 +15531,16 @@
     </row>
     <row r="251" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="B251" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C251" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D251" s="3">
-        <v>12025</v>
+        <v>937</v>
       </c>
       <c r="F251" s="3" t="str">
         <f>IF(E251="","",IF(E251="DNS",0,IF(E251="DQ",0,IF(E251="DNF",1,IF(AND(ISNUMBER(E251),E251&gt;59),1,_xlfn.XLOOKUP(E251,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15581,16 +15581,16 @@
     </row>
     <row r="252" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>137</v>
+        <v>295</v>
       </c>
       <c r="B252" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C252" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D252" s="3">
-        <v>12028</v>
+        <v>930</v>
       </c>
       <c r="F252" s="3" t="str">
         <f>IF(E252="","",IF(E252="DNS",0,IF(E252="DQ",0,IF(E252="DNF",1,IF(AND(ISNUMBER(E252),E252&gt;59),1,_xlfn.XLOOKUP(E252,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15631,16 +15631,16 @@
     </row>
     <row r="253" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>136</v>
+        <v>303</v>
       </c>
       <c r="B253" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C253" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D253" s="3">
-        <v>12027</v>
+        <v>938</v>
       </c>
       <c r="F253" s="3" t="str">
         <f>IF(E253="","",IF(E253="DNS",0,IF(E253="DQ",0,IF(E253="DNF",1,IF(AND(ISNUMBER(E253),E253&gt;59),1,_xlfn.XLOOKUP(E253,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15681,16 +15681,16 @@
     </row>
     <row r="254" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>138</v>
+        <v>298</v>
       </c>
       <c r="B254" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C254" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D254" s="3">
-        <v>12029</v>
+        <v>933</v>
       </c>
       <c r="F254" s="3" t="str">
         <f>IF(E254="","",IF(E254="DNS",0,IF(E254="DQ",0,IF(E254="DNF",1,IF(AND(ISNUMBER(E254),E254&gt;59),1,_xlfn.XLOOKUP(E254,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15731,16 +15731,16 @@
     </row>
     <row r="255" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>133</v>
+        <v>304</v>
       </c>
       <c r="B255" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C255" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D255" s="3">
-        <v>12024</v>
+        <v>920</v>
       </c>
       <c r="F255" s="3" t="str">
         <f>IF(E255="","",IF(E255="DNS",0,IF(E255="DQ",0,IF(E255="DNF",1,IF(AND(ISNUMBER(E255),E255&gt;59),1,_xlfn.XLOOKUP(E255,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15781,16 +15781,16 @@
     </row>
     <row r="256" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>139</v>
+        <v>308</v>
       </c>
       <c r="B256" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C256" t="s">
         <v>1</v>
       </c>
       <c r="D256" s="3">
-        <v>12030</v>
+        <v>12075</v>
       </c>
       <c r="F256" s="3" t="str">
         <f>IF(E256="","",IF(E256="DNS",0,IF(E256="DQ",0,IF(E256="DNF",1,IF(AND(ISNUMBER(E256),E256&gt;59),1,_xlfn.XLOOKUP(E256,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15831,16 +15831,16 @@
     </row>
     <row r="257" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>146</v>
+        <v>311</v>
       </c>
       <c r="B257" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C257" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D257" s="3">
-        <v>12031</v>
+        <v>822</v>
       </c>
       <c r="F257" s="3" t="str">
         <f>IF(E257="","",IF(E257="DNS",0,IF(E257="DQ",0,IF(E257="DNF",1,IF(AND(ISNUMBER(E257),E257&gt;59),1,_xlfn.XLOOKUP(E257,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15881,16 +15881,16 @@
     </row>
     <row r="258" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>157</v>
+        <v>310</v>
       </c>
       <c r="B258" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C258" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D258" s="3">
-        <v>12032</v>
+        <v>821</v>
       </c>
       <c r="F258" s="3" t="str">
         <f>IF(E258="","",IF(E258="DNS",0,IF(E258="DQ",0,IF(E258="DNF",1,IF(AND(ISNUMBER(E258),E258&gt;59),1,_xlfn.XLOOKUP(E258,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15931,16 +15931,16 @@
     </row>
     <row r="259" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>158</v>
+        <v>312</v>
       </c>
       <c r="B259" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C259" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D259" s="3">
-        <v>12033</v>
+        <v>823</v>
       </c>
       <c r="F259" s="3" t="str">
         <f>IF(E259="","",IF(E259="DNS",0,IF(E259="DQ",0,IF(E259="DNF",1,IF(AND(ISNUMBER(E259),E259&gt;59),1,_xlfn.XLOOKUP(E259,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15981,16 +15981,16 @@
     </row>
     <row r="260" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>168</v>
+        <v>309</v>
       </c>
       <c r="B260" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C260" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D260" s="3">
-        <v>12035</v>
+        <v>820</v>
       </c>
       <c r="F260" s="3" t="str">
         <f>IF(E260="","",IF(E260="DNS",0,IF(E260="DQ",0,IF(E260="DNF",1,IF(AND(ISNUMBER(E260),E260&gt;59),1,_xlfn.XLOOKUP(E260,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16031,16 +16031,16 @@
     </row>
     <row r="261" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>167</v>
+        <v>315</v>
       </c>
       <c r="B261" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C261" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D261" s="3">
-        <v>12034</v>
+        <v>10190</v>
       </c>
       <c r="F261" s="3" t="str">
         <f>IF(E261="","",IF(E261="DNS",0,IF(E261="DQ",0,IF(E261="DNF",1,IF(AND(ISNUMBER(E261),E261&gt;59),1,_xlfn.XLOOKUP(E261,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16081,16 +16081,16 @@
     </row>
     <row r="262" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>188</v>
+        <v>314</v>
       </c>
       <c r="B262" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C262" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D262" s="3">
-        <v>12036</v>
+        <v>940</v>
       </c>
       <c r="F262" s="3" t="str">
         <f>IF(E262="","",IF(E262="DNS",0,IF(E262="DQ",0,IF(E262="DNF",1,IF(AND(ISNUMBER(E262),E262&gt;59),1,_xlfn.XLOOKUP(E262,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16131,16 +16131,16 @@
     </row>
     <row r="263" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>189</v>
+        <v>313</v>
       </c>
       <c r="B263" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C263" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D263" s="3">
-        <v>12037</v>
+        <v>939</v>
       </c>
       <c r="F263" s="3" t="str">
         <f>IF(E263="","",IF(E263="DNS",0,IF(E263="DQ",0,IF(E263="DNF",1,IF(AND(ISNUMBER(E263),E263&gt;59),1,_xlfn.XLOOKUP(E263,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16181,16 +16181,16 @@
     </row>
     <row r="264" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>214</v>
+        <v>319</v>
       </c>
       <c r="B264" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C264" t="s">
         <v>1</v>
       </c>
       <c r="D264" s="3">
-        <v>12047</v>
+        <v>12079</v>
       </c>
       <c r="F264" s="3" t="str">
         <f>IF(E264="","",IF(E264="DNS",0,IF(E264="DQ",0,IF(E264="DNF",1,IF(AND(ISNUMBER(E264),E264&gt;59),1,_xlfn.XLOOKUP(E264,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16231,16 +16231,16 @@
     </row>
     <row r="265" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>209</v>
+        <v>317</v>
       </c>
       <c r="B265" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C265" t="s">
         <v>1</v>
       </c>
       <c r="D265" s="3">
-        <v>12042</v>
+        <v>12077</v>
       </c>
       <c r="F265" s="3" t="str">
         <f>IF(E265="","",IF(E265="DNS",0,IF(E265="DQ",0,IF(E265="DNF",1,IF(AND(ISNUMBER(E265),E265&gt;59),1,_xlfn.XLOOKUP(E265,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16281,16 +16281,16 @@
     </row>
     <row r="266" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>212</v>
+        <v>316</v>
       </c>
       <c r="B266" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C266" t="s">
         <v>1</v>
       </c>
       <c r="D266" s="3">
-        <v>12045</v>
+        <v>12076</v>
       </c>
       <c r="F266" s="3" t="str">
         <f>IF(E266="","",IF(E266="DNS",0,IF(E266="DQ",0,IF(E266="DNF",1,IF(AND(ISNUMBER(E266),E266&gt;59),1,_xlfn.XLOOKUP(E266,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16331,16 +16331,16 @@
     </row>
     <row r="267" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>215</v>
+        <v>318</v>
       </c>
       <c r="B267" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C267" t="s">
         <v>1</v>
       </c>
       <c r="D267" s="3">
-        <v>12048</v>
+        <v>12078</v>
       </c>
       <c r="F267" s="3" t="str">
         <f>IF(E267="","",IF(E267="DNS",0,IF(E267="DQ",0,IF(E267="DNF",1,IF(AND(ISNUMBER(E267),E267&gt;59),1,_xlfn.XLOOKUP(E267,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16381,16 +16381,16 @@
     </row>
     <row r="268" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="B268" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C268" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D268" s="3">
-        <v>12039</v>
+        <v>824</v>
       </c>
       <c r="F268" s="3" t="str">
         <f>IF(E268="","",IF(E268="DNS",0,IF(E268="DQ",0,IF(E268="DNF",1,IF(AND(ISNUMBER(E268),E268&gt;59),1,_xlfn.XLOOKUP(E268,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16431,16 +16431,16 @@
     </row>
     <row r="269" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
-        <v>205</v>
+        <v>321</v>
       </c>
       <c r="B269" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C269" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D269" s="3">
-        <v>12038</v>
+        <v>825</v>
       </c>
       <c r="F269" s="3" t="str">
         <f>IF(E269="","",IF(E269="DNS",0,IF(E269="DQ",0,IF(E269="DNF",1,IF(AND(ISNUMBER(E269),E269&gt;59),1,_xlfn.XLOOKUP(E269,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16481,16 +16481,16 @@
     </row>
     <row r="270" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
-        <v>207</v>
+        <v>323</v>
       </c>
       <c r="B270" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C270" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D270" s="3">
-        <v>12040</v>
+        <v>867</v>
       </c>
       <c r="F270" s="3" t="str">
         <f>IF(E270="","",IF(E270="DNS",0,IF(E270="DQ",0,IF(E270="DNF",1,IF(AND(ISNUMBER(E270),E270&gt;59),1,_xlfn.XLOOKUP(E270,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16531,16 +16531,16 @@
     </row>
     <row r="271" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
-        <v>211</v>
+        <v>322</v>
       </c>
       <c r="B271" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C271" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D271" s="3">
-        <v>12044</v>
+        <v>866</v>
       </c>
       <c r="F271" s="3" t="str">
         <f>IF(E271="","",IF(E271="DNS",0,IF(E271="DQ",0,IF(E271="DNF",1,IF(AND(ISNUMBER(E271),E271&gt;59),1,_xlfn.XLOOKUP(E271,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16581,16 +16581,16 @@
     </row>
     <row r="272" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
-        <v>213</v>
+        <v>328</v>
       </c>
       <c r="B272" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C272" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D272" s="3">
-        <v>12046</v>
+        <v>10191</v>
       </c>
       <c r="F272" s="3" t="str">
         <f>IF(E272="","",IF(E272="DNS",0,IF(E272="DQ",0,IF(E272="DNF",1,IF(AND(ISNUMBER(E272),E272&gt;59),1,_xlfn.XLOOKUP(E272,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16631,16 +16631,16 @@
     </row>
     <row r="273" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>210</v>
+        <v>329</v>
       </c>
       <c r="B273" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C273" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D273" s="3">
-        <v>12043</v>
+        <v>1040</v>
       </c>
       <c r="F273" s="3" t="str">
         <f>IF(E273="","",IF(E273="DNS",0,IF(E273="DQ",0,IF(E273="DNF",1,IF(AND(ISNUMBER(E273),E273&gt;59),1,_xlfn.XLOOKUP(E273,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16681,16 +16681,16 @@
     </row>
     <row r="274" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>208</v>
+        <v>326</v>
       </c>
       <c r="B274" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C274" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D274" s="3">
-        <v>12041</v>
+        <v>943</v>
       </c>
       <c r="F274" s="3" t="str">
         <f>IF(E274="","",IF(E274="DNS",0,IF(E274="DQ",0,IF(E274="DNF",1,IF(AND(ISNUMBER(E274),E274&gt;59),1,_xlfn.XLOOKUP(E274,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16731,16 +16731,16 @@
     </row>
     <row r="275" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>240</v>
+        <v>327</v>
       </c>
       <c r="B275" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C275" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D275" s="3">
-        <v>12058</v>
+        <v>944</v>
       </c>
       <c r="F275" s="3" t="str">
         <f>IF(E275="","",IF(E275="DNS",0,IF(E275="DQ",0,IF(E275="DNF",1,IF(AND(ISNUMBER(E275),E275&gt;59),1,_xlfn.XLOOKUP(E275,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16781,16 +16781,16 @@
     </row>
     <row r="276" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
-        <v>239</v>
+        <v>324</v>
       </c>
       <c r="B276" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C276" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D276" s="3">
-        <v>12057</v>
+        <v>941</v>
       </c>
       <c r="F276" s="3" t="str">
         <f>IF(E276="","",IF(E276="DNS",0,IF(E276="DQ",0,IF(E276="DNF",1,IF(AND(ISNUMBER(E276),E276&gt;59),1,_xlfn.XLOOKUP(E276,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16831,16 +16831,16 @@
     </row>
     <row r="277" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>241</v>
+        <v>325</v>
       </c>
       <c r="B277" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C277" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D277" s="3">
-        <v>12059</v>
+        <v>942</v>
       </c>
       <c r="F277" s="3" t="str">
         <f>IF(E277="","",IF(E277="DNS",0,IF(E277="DQ",0,IF(E277="DNF",1,IF(AND(ISNUMBER(E277),E277&gt;59),1,_xlfn.XLOOKUP(E277,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16881,16 +16881,16 @@
     </row>
     <row r="278" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
-        <v>236</v>
+        <v>336</v>
       </c>
       <c r="B278" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C278" t="s">
         <v>1</v>
       </c>
       <c r="D278" s="3">
-        <v>12054</v>
+        <v>12086</v>
       </c>
       <c r="F278" s="3" t="str">
         <f>IF(E278="","",IF(E278="DNS",0,IF(E278="DQ",0,IF(E278="DNF",1,IF(AND(ISNUMBER(E278),E278&gt;59),1,_xlfn.XLOOKUP(E278,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16931,16 +16931,16 @@
     </row>
     <row r="279" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>242</v>
+        <v>332</v>
       </c>
       <c r="B279" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C279" t="s">
         <v>1</v>
       </c>
       <c r="D279" s="3">
-        <v>12060</v>
+        <v>12082</v>
       </c>
       <c r="F279" s="3" t="str">
         <f>IF(E279="","",IF(E279="DNS",0,IF(E279="DQ",0,IF(E279="DNF",1,IF(AND(ISNUMBER(E279),E279&gt;59),1,_xlfn.XLOOKUP(E279,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16981,16 +16981,16 @@
     </row>
     <row r="280" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>231</v>
+        <v>331</v>
       </c>
       <c r="B280" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C280" t="s">
         <v>1</v>
       </c>
       <c r="D280" s="3">
-        <v>12049</v>
+        <v>12081</v>
       </c>
       <c r="F280" s="3" t="str">
         <f>IF(E280="","",IF(E280="DNS",0,IF(E280="DQ",0,IF(E280="DNF",1,IF(AND(ISNUMBER(E280),E280&gt;59),1,_xlfn.XLOOKUP(E280,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17031,16 +17031,16 @@
     </row>
     <row r="281" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>237</v>
+        <v>330</v>
       </c>
       <c r="B281" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C281" t="s">
         <v>1</v>
       </c>
       <c r="D281" s="3">
-        <v>12055</v>
+        <v>12080</v>
       </c>
       <c r="F281" s="3" t="str">
         <f>IF(E281="","",IF(E281="DNS",0,IF(E281="DQ",0,IF(E281="DNF",1,IF(AND(ISNUMBER(E281),E281&gt;59),1,_xlfn.XLOOKUP(E281,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17081,16 +17081,16 @@
     </row>
     <row r="282" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
-        <v>232</v>
+        <v>333</v>
       </c>
       <c r="B282" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C282" t="s">
         <v>1</v>
       </c>
       <c r="D282" s="3">
-        <v>12050</v>
+        <v>12083</v>
       </c>
       <c r="F282" s="3" t="str">
         <f>IF(E282="","",IF(E282="DNS",0,IF(E282="DQ",0,IF(E282="DNF",1,IF(AND(ISNUMBER(E282),E282&gt;59),1,_xlfn.XLOOKUP(E282,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17131,16 +17131,16 @@
     </row>
     <row r="283" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>234</v>
+        <v>335</v>
       </c>
       <c r="B283" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C283" t="s">
         <v>1</v>
       </c>
       <c r="D283" s="3">
-        <v>12052</v>
+        <v>12085</v>
       </c>
       <c r="F283" s="3" t="str">
         <f>IF(E283="","",IF(E283="DNS",0,IF(E283="DQ",0,IF(E283="DNF",1,IF(AND(ISNUMBER(E283),E283&gt;59),1,_xlfn.XLOOKUP(E283,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17181,16 +17181,16 @@
     </row>
     <row r="284" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="B284" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C284" t="s">
         <v>1</v>
       </c>
       <c r="D284" s="3">
-        <v>12053</v>
+        <v>12084</v>
       </c>
       <c r="F284" s="3" t="str">
         <f>IF(E284="","",IF(E284="DNS",0,IF(E284="DQ",0,IF(E284="DNF",1,IF(AND(ISNUMBER(E284),E284&gt;59),1,_xlfn.XLOOKUP(E284,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17231,16 +17231,16 @@
     </row>
     <row r="285" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="B285" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C285" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D285" s="3">
-        <v>12051</v>
+        <v>1243</v>
       </c>
       <c r="F285" s="3" t="str">
         <f>IF(E285="","",IF(E285="DNS",0,IF(E285="DQ",0,IF(E285="DNF",1,IF(AND(ISNUMBER(E285),E285&gt;59),1,_xlfn.XLOOKUP(E285,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17281,16 +17281,16 @@
     </row>
     <row r="286" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
-        <v>238</v>
+        <v>338</v>
       </c>
       <c r="B286" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C286" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D286" s="3">
-        <v>12056</v>
+        <v>826</v>
       </c>
       <c r="F286" s="3" t="str">
         <f>IF(E286="","",IF(E286="DNS",0,IF(E286="DQ",0,IF(E286="DNF",1,IF(AND(ISNUMBER(E286),E286&gt;59),1,_xlfn.XLOOKUP(E286,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17331,16 +17331,16 @@
     </row>
     <row r="287" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
-        <v>284</v>
+        <v>342</v>
       </c>
       <c r="B287" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C287" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D287" s="3">
-        <v>12069</v>
+        <v>830</v>
       </c>
       <c r="F287" s="3" t="str">
         <f>IF(E287="","",IF(E287="DNS",0,IF(E287="DQ",0,IF(E287="DNF",1,IF(AND(ISNUMBER(E287),E287&gt;59),1,_xlfn.XLOOKUP(E287,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17381,16 +17381,16 @@
     </row>
     <row r="288" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
       <c r="B288" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C288" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D288" s="3">
-        <v>12064</v>
+        <v>827</v>
       </c>
       <c r="F288" s="3" t="str">
         <f>IF(E288="","",IF(E288="DNS",0,IF(E288="DQ",0,IF(E288="DNF",1,IF(AND(ISNUMBER(E288),E288&gt;59),1,_xlfn.XLOOKUP(E288,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17431,16 +17431,16 @@
     </row>
     <row r="289" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
-        <v>281</v>
+        <v>341</v>
       </c>
       <c r="B289" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C289" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D289" s="3">
-        <v>12066</v>
+        <v>829</v>
       </c>
       <c r="F289" s="3" t="str">
         <f>IF(E289="","",IF(E289="DNS",0,IF(E289="DQ",0,IF(E289="DNF",1,IF(AND(ISNUMBER(E289),E289&gt;59),1,_xlfn.XLOOKUP(E289,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17481,16 +17481,16 @@
     </row>
     <row r="290" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="B290" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C290" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D290" s="3">
-        <v>12065</v>
+        <v>828</v>
       </c>
       <c r="F290" s="3" t="str">
         <f>IF(E290="","",IF(E290="DNS",0,IF(E290="DQ",0,IF(E290="DNF",1,IF(AND(ISNUMBER(E290),E290&gt;59),1,_xlfn.XLOOKUP(E290,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17531,16 +17531,16 @@
     </row>
     <row r="291" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
-        <v>282</v>
+        <v>348</v>
       </c>
       <c r="B291" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C291" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D291" s="3">
-        <v>12067</v>
+        <v>10192</v>
       </c>
       <c r="F291" s="3" t="str">
         <f>IF(E291="","",IF(E291="DNS",0,IF(E291="DQ",0,IF(E291="DNF",1,IF(AND(ISNUMBER(E291),E291&gt;59),1,_xlfn.XLOOKUP(E291,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17581,16 +17581,16 @@
     </row>
     <row r="292" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C292" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D292" s="3">
-        <v>12062</v>
+        <v>946</v>
       </c>
       <c r="F292" s="3" t="str">
         <f>IF(E292="","",IF(E292="DNS",0,IF(E292="DQ",0,IF(E292="DNF",1,IF(AND(ISNUMBER(E292),E292&gt;59),1,_xlfn.XLOOKUP(E292,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17631,16 +17631,16 @@
     </row>
     <row r="293" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="B293" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C293" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D293" s="3">
-        <v>12071</v>
+        <v>947</v>
       </c>
       <c r="F293" s="3" t="str">
         <f>IF(E293="","",IF(E293="DNS",0,IF(E293="DQ",0,IF(E293="DNF",1,IF(AND(ISNUMBER(E293),E293&gt;59),1,_xlfn.XLOOKUP(E293,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17681,16 +17681,16 @@
     </row>
     <row r="294" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="B294" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C294" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D294" s="3">
-        <v>12070</v>
+        <v>948</v>
       </c>
       <c r="F294" s="3" t="str">
         <f>IF(E294="","",IF(E294="DNS",0,IF(E294="DQ",0,IF(E294="DNF",1,IF(AND(ISNUMBER(E294),E294&gt;59),1,_xlfn.XLOOKUP(E294,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17731,16 +17731,16 @@
     </row>
     <row r="295" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="B295" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C295" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D295" s="3">
-        <v>12068</v>
+        <v>945</v>
       </c>
       <c r="F295" s="3" t="str">
         <f>IF(E295="","",IF(E295="DNS",0,IF(E295="DQ",0,IF(E295="DNF",1,IF(AND(ISNUMBER(E295),E295&gt;59),1,_xlfn.XLOOKUP(E295,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17781,16 +17781,16 @@
     </row>
     <row r="296" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>276</v>
+        <v>347</v>
       </c>
       <c r="B296" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C296" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D296" s="3">
-        <v>12061</v>
+        <v>949</v>
       </c>
       <c r="F296" s="3" t="str">
         <f>IF(E296="","",IF(E296="DNS",0,IF(E296="DQ",0,IF(E296="DNF",1,IF(AND(ISNUMBER(E296),E296&gt;59),1,_xlfn.XLOOKUP(E296,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17831,16 +17831,16 @@
     </row>
     <row r="297" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>278</v>
+        <v>350</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C297" t="s">
         <v>1</v>
       </c>
       <c r="D297" s="3">
-        <v>12063</v>
+        <v>12087</v>
       </c>
       <c r="F297" s="3" t="str">
         <f>IF(E297="","",IF(E297="DNS",0,IF(E297="DQ",0,IF(E297="DNF",1,IF(AND(ISNUMBER(E297),E297&gt;59),1,_xlfn.XLOOKUP(E297,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17881,16 +17881,16 @@
     </row>
     <row r="298" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>290</v>
+        <v>356</v>
       </c>
       <c r="B298" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C298" t="s">
         <v>1</v>
       </c>
       <c r="D298" s="3">
-        <v>12072</v>
+        <v>12093</v>
       </c>
       <c r="F298" s="3" t="str">
         <f>IF(E298="","",IF(E298="DNS",0,IF(E298="DQ",0,IF(E298="DNF",1,IF(AND(ISNUMBER(E298),E298&gt;59),1,_xlfn.XLOOKUP(E298,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17931,16 +17931,16 @@
     </row>
     <row r="299" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
       <c r="B299" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C299" t="s">
         <v>1</v>
       </c>
       <c r="D299" s="3">
-        <v>12074</v>
+        <v>12090</v>
       </c>
       <c r="F299" s="3" t="str">
         <f>IF(E299="","",IF(E299="DNS",0,IF(E299="DQ",0,IF(E299="DNF",1,IF(AND(ISNUMBER(E299),E299&gt;59),1,_xlfn.XLOOKUP(E299,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17981,16 +17981,16 @@
     </row>
     <row r="300" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>291</v>
+        <v>357</v>
       </c>
       <c r="B300" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C300" t="s">
         <v>1</v>
       </c>
       <c r="D300" s="3">
-        <v>12073</v>
+        <v>12094</v>
       </c>
       <c r="F300" s="3" t="str">
         <f>IF(E300="","",IF(E300="DNS",0,IF(E300="DQ",0,IF(E300="DNF",1,IF(AND(ISNUMBER(E300),E300&gt;59),1,_xlfn.XLOOKUP(E300,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18031,16 +18031,16 @@
     </row>
     <row r="301" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="B301" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C301" t="s">
         <v>1</v>
       </c>
       <c r="D301" s="3">
-        <v>12075</v>
+        <v>12091</v>
       </c>
       <c r="F301" s="3" t="str">
         <f>IF(E301="","",IF(E301="DNS",0,IF(E301="DQ",0,IF(E301="DNF",1,IF(AND(ISNUMBER(E301),E301&gt;59),1,_xlfn.XLOOKUP(E301,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18081,16 +18081,16 @@
     </row>
     <row r="302" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="B302" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C302" t="s">
         <v>1</v>
       </c>
       <c r="D302" s="3">
-        <v>12079</v>
+        <v>12092</v>
       </c>
       <c r="F302" s="3" t="str">
         <f>IF(E302="","",IF(E302="DNS",0,IF(E302="DQ",0,IF(E302="DNF",1,IF(AND(ISNUMBER(E302),E302&gt;59),1,_xlfn.XLOOKUP(E302,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18131,16 +18131,16 @@
     </row>
     <row r="303" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="B303" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C303" t="s">
         <v>1</v>
       </c>
       <c r="D303" s="3">
-        <v>12077</v>
+        <v>12088</v>
       </c>
       <c r="F303" s="3" t="str">
         <f>IF(E303="","",IF(E303="DNS",0,IF(E303="DQ",0,IF(E303="DNF",1,IF(AND(ISNUMBER(E303),E303&gt;59),1,_xlfn.XLOOKUP(E303,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18181,16 +18181,16 @@
     </row>
     <row r="304" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="B304" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C304" t="s">
         <v>1</v>
       </c>
       <c r="D304" s="3">
-        <v>12076</v>
+        <v>12089</v>
       </c>
       <c r="F304" s="3" t="str">
         <f>IF(E304="","",IF(E304="DNS",0,IF(E304="DQ",0,IF(E304="DNF",1,IF(AND(ISNUMBER(E304),E304&gt;59),1,_xlfn.XLOOKUP(E304,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18231,16 +18231,16 @@
     </row>
     <row r="305" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="B305" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C305" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D305" s="3">
-        <v>12078</v>
+        <v>1244</v>
       </c>
       <c r="F305" s="3" t="str">
         <f>IF(E305="","",IF(E305="DNS",0,IF(E305="DQ",0,IF(E305="DNF",1,IF(AND(ISNUMBER(E305),E305&gt;59),1,_xlfn.XLOOKUP(E305,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18281,16 +18281,16 @@
     </row>
     <row r="306" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="B306" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C306" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D306" s="3">
-        <v>12086</v>
+        <v>832</v>
       </c>
       <c r="F306" s="3" t="str">
         <f>IF(E306="","",IF(E306="DNS",0,IF(E306="DQ",0,IF(E306="DNF",1,IF(AND(ISNUMBER(E306),E306&gt;59),1,_xlfn.XLOOKUP(E306,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18329,39 +18329,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="B307" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C307" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D307" s="3">
-        <v>12082</v>
-      </c>
+        <v>831</v>
+      </c>
+      <c r="E307" s="3"/>
       <c r="F307" s="3" t="str">
         <f>IF(E307="","",IF(E307="DNS",0,IF(E307="DQ",0,IF(E307="DNF",1,IF(AND(ISNUMBER(E307),E307&gt;59),1,_xlfn.XLOOKUP(E307,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
+      <c r="G307" s="3"/>
       <c r="H307" s="3" t="str">
         <f>IF(G307="","",IF(G307="DNS",0,IF(G307="DQ",0,IF(G307="DNF",1,IF(AND(ISNUMBER(G307),G307&gt;59),1,_xlfn.XLOOKUP(G307,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
+      <c r="I307" s="3"/>
       <c r="J307" s="3" t="str">
         <f>IF(I307="","",IF(I307="DNS",0,IF(I307="DQ",0,IF(I307="DNF",1,IF(AND(ISNUMBER(I307),I307&gt;59),1,_xlfn.XLOOKUP(I307,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
+      <c r="K307" s="3"/>
       <c r="L307" s="3" t="str">
         <f>IF(K307="","",IF(K307="DNS",0,IF(K307="DQ",0,IF(K307="DNF",1,IF(AND(ISNUMBER(K307),K307&gt;59),1,_xlfn.XLOOKUP(K307,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
+      <c r="M307" s="3"/>
       <c r="N307" s="3" t="str">
         <f>IF(M307="","",IF(M307="DNS",0,IF(M307="DQ",0,IF(M307="DNF",1,IF(AND(ISNUMBER(M307),M307&gt;59),1,_xlfn.XLOOKUP(M307,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
+      <c r="O307" s="3"/>
       <c r="P307" s="3" t="str">
         <f>IF(O307="","",IF(O307="DNS",0,IF(O307="DQ",0,IF(O307="DNF",1,IF(AND(ISNUMBER(O307),O307&gt;59),1,_xlfn.XLOOKUP(O307,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
@@ -18379,45 +18385,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B308" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C308" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D308" s="3">
-        <v>12081</v>
-      </c>
-      <c r="E308" s="3"/>
+        <v>951</v>
+      </c>
       <c r="F308" s="3" t="str">
         <f>IF(E308="","",IF(E308="DNS",0,IF(E308="DQ",0,IF(E308="DNF",1,IF(AND(ISNUMBER(E308),E308&gt;59),1,_xlfn.XLOOKUP(E308,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="G308" s="3"/>
       <c r="H308" s="3" t="str">
         <f>IF(G308="","",IF(G308="DNS",0,IF(G308="DQ",0,IF(G308="DNF",1,IF(AND(ISNUMBER(G308),G308&gt;59),1,_xlfn.XLOOKUP(G308,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="I308" s="3"/>
       <c r="J308" s="3" t="str">
         <f>IF(I308="","",IF(I308="DNS",0,IF(I308="DQ",0,IF(I308="DNF",1,IF(AND(ISNUMBER(I308),I308&gt;59),1,_xlfn.XLOOKUP(I308,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="K308" s="3"/>
       <c r="L308" s="3" t="str">
         <f>IF(K308="","",IF(K308="DNS",0,IF(K308="DQ",0,IF(K308="DNF",1,IF(AND(ISNUMBER(K308),K308&gt;59),1,_xlfn.XLOOKUP(K308,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="M308" s="3"/>
       <c r="N308" s="3" t="str">
         <f>IF(M308="","",IF(M308="DNS",0,IF(M308="DQ",0,IF(M308="DNF",1,IF(AND(ISNUMBER(M308),M308&gt;59),1,_xlfn.XLOOKUP(M308,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="O308" s="3"/>
       <c r="P308" s="3" t="str">
         <f>IF(O308="","",IF(O308="DNS",0,IF(O308="DQ",0,IF(O308="DNF",1,IF(AND(ISNUMBER(O308),O308&gt;59),1,_xlfn.XLOOKUP(O308,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
@@ -18437,16 +18437,16 @@
     </row>
     <row r="309" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="B309" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C309" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D309" s="3">
-        <v>12080</v>
+        <v>950</v>
       </c>
       <c r="F309" s="3" t="str">
         <f>IF(E309="","",IF(E309="DNS",0,IF(E309="DQ",0,IF(E309="DNF",1,IF(AND(ISNUMBER(E309),E309&gt;59),1,_xlfn.XLOOKUP(E309,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18487,16 +18487,16 @@
     </row>
     <row r="310" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="B310" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C310" t="s">
         <v>1</v>
       </c>
       <c r="D310" s="3">
-        <v>12083</v>
+        <v>12095</v>
       </c>
       <c r="F310" s="3" t="str">
         <f>IF(E310="","",IF(E310="DNS",0,IF(E310="DQ",0,IF(E310="DNF",1,IF(AND(ISNUMBER(E310),E310&gt;59),1,_xlfn.XLOOKUP(E310,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18537,16 +18537,16 @@
     </row>
     <row r="311" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="B311" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C311" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D311" s="3">
-        <v>12085</v>
+        <v>834</v>
       </c>
       <c r="F311" s="3" t="str">
         <f>IF(E311="","",IF(E311="DNS",0,IF(E311="DQ",0,IF(E311="DNF",1,IF(AND(ISNUMBER(E311),E311&gt;59),1,_xlfn.XLOOKUP(E311,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18587,16 +18587,16 @@
     </row>
     <row r="312" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="B312" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C312" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D312" s="3">
-        <v>12084</v>
+        <v>836</v>
       </c>
       <c r="F312" s="3" t="str">
         <f>IF(E312="","",IF(E312="DNS",0,IF(E312="DQ",0,IF(E312="DNF",1,IF(AND(ISNUMBER(E312),E312&gt;59),1,_xlfn.XLOOKUP(E312,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18637,16 +18637,16 @@
     </row>
     <row r="313" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B313" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C313" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D313" s="3">
-        <v>12087</v>
+        <v>835</v>
       </c>
       <c r="F313" s="3" t="str">
         <f>IF(E313="","",IF(E313="DNS",0,IF(E313="DQ",0,IF(E313="DNF",1,IF(AND(ISNUMBER(E313),E313&gt;59),1,_xlfn.XLOOKUP(E313,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18687,16 +18687,16 @@
     </row>
     <row r="314" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B314" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C314" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D314" s="3">
-        <v>12093</v>
+        <v>833</v>
       </c>
       <c r="F314" s="3" t="str">
         <f>IF(E314="","",IF(E314="DNS",0,IF(E314="DQ",0,IF(E314="DNF",1,IF(AND(ISNUMBER(E314),E314&gt;59),1,_xlfn.XLOOKUP(E314,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18737,16 +18737,16 @@
     </row>
     <row r="315" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="B315" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C315" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D315" s="3">
-        <v>12090</v>
+        <v>10199</v>
       </c>
       <c r="F315" s="3" t="str">
         <f>IF(E315="","",IF(E315="DNS",0,IF(E315="DQ",0,IF(E315="DNF",1,IF(AND(ISNUMBER(E315),E315&gt;59),1,_xlfn.XLOOKUP(E315,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18787,16 +18787,16 @@
     </row>
     <row r="316" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B316" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C316" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D316" s="3">
-        <v>12094</v>
+        <v>10200</v>
       </c>
       <c r="F316" s="3" t="str">
         <f>IF(E316="","",IF(E316="DNS",0,IF(E316="DQ",0,IF(E316="DNF",1,IF(AND(ISNUMBER(E316),E316&gt;59),1,_xlfn.XLOOKUP(E316,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18837,16 +18837,16 @@
     </row>
     <row r="317" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="B317" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C317" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D317" s="3">
-        <v>12091</v>
+        <v>10193</v>
       </c>
       <c r="F317" s="3" t="str">
         <f>IF(E317="","",IF(E317="DNS",0,IF(E317="DQ",0,IF(E317="DNF",1,IF(AND(ISNUMBER(E317),E317&gt;59),1,_xlfn.XLOOKUP(E317,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18887,16 +18887,16 @@
     </row>
     <row r="318" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="B318" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C318" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D318" s="3">
-        <v>12092</v>
+        <v>10197</v>
       </c>
       <c r="F318" s="3" t="str">
         <f>IF(E318="","",IF(E318="DNS",0,IF(E318="DQ",0,IF(E318="DNF",1,IF(AND(ISNUMBER(E318),E318&gt;59),1,_xlfn.XLOOKUP(E318,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18937,16 +18937,16 @@
     </row>
     <row r="319" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="B319" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C319" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D319" s="3">
-        <v>12088</v>
+        <v>10201</v>
       </c>
       <c r="F319" s="3" t="str">
         <f>IF(E319="","",IF(E319="DNS",0,IF(E319="DQ",0,IF(E319="DNF",1,IF(AND(ISNUMBER(E319),E319&gt;59),1,_xlfn.XLOOKUP(E319,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18987,16 +18987,16 @@
     </row>
     <row r="320" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="B320" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C320" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D320" s="3">
-        <v>12089</v>
+        <v>10195</v>
       </c>
       <c r="F320" s="3" t="str">
         <f>IF(E320="","",IF(E320="DNS",0,IF(E320="DQ",0,IF(E320="DNF",1,IF(AND(ISNUMBER(E320),E320&gt;59),1,_xlfn.XLOOKUP(E320,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19037,16 +19037,16 @@
     </row>
     <row r="321" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B321" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C321" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D321" s="3">
-        <v>12095</v>
+        <v>10196</v>
       </c>
       <c r="F321" s="3" t="str">
         <f>IF(E321="","",IF(E321="DNS",0,IF(E321="DQ",0,IF(E321="DNF",1,IF(AND(ISNUMBER(E321),E321&gt;59),1,_xlfn.XLOOKUP(E321,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19086,73 +19086,67 @@
       </c>
     </row>
     <row r="322" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A322" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B322" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C322" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D322" s="13">
-        <v>12096</v>
-      </c>
-      <c r="E322" s="13"/>
-      <c r="F322" s="13" t="str">
+      <c r="A322" t="s">
+        <v>377</v>
+      </c>
+      <c r="B322" t="s">
+        <v>31</v>
+      </c>
+      <c r="C322" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="3">
+        <v>10194</v>
+      </c>
+      <c r="F322" s="3" t="str">
         <f>IF(E322="","",IF(E322="DNS",0,IF(E322="DQ",0,IF(E322="DNF",1,IF(AND(ISNUMBER(E322),E322&gt;59),1,_xlfn.XLOOKUP(E322,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="G322" s="13"/>
-      <c r="H322" s="13" t="str">
+      <c r="H322" s="3" t="str">
         <f>IF(G322="","",IF(G322="DNS",0,IF(G322="DQ",0,IF(G322="DNF",1,IF(AND(ISNUMBER(G322),G322&gt;59),1,_xlfn.XLOOKUP(G322,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="I322" s="13"/>
-      <c r="J322" s="13" t="str">
+      <c r="J322" s="3" t="str">
         <f>IF(I322="","",IF(I322="DNS",0,IF(I322="DQ",0,IF(I322="DNF",1,IF(AND(ISNUMBER(I322),I322&gt;59),1,_xlfn.XLOOKUP(I322,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="K322" s="13"/>
-      <c r="L322" s="13" t="str">
+      <c r="L322" s="3" t="str">
         <f>IF(K322="","",IF(K322="DNS",0,IF(K322="DQ",0,IF(K322="DNF",1,IF(AND(ISNUMBER(K322),K322&gt;59),1,_xlfn.XLOOKUP(K322,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="M322" s="13"/>
-      <c r="N322" s="13" t="str">
+      <c r="N322" s="3" t="str">
         <f>IF(M322="","",IF(M322="DNS",0,IF(M322="DQ",0,IF(M322="DNF",1,IF(AND(ISNUMBER(M322),M322&gt;59),1,_xlfn.XLOOKUP(M322,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="O322" s="13"/>
-      <c r="P322" s="13" t="str">
+      <c r="P322" s="3" t="str">
         <f>IF(O322="","",IF(O322="DNS",0,IF(O322="DQ",0,IF(O322="DNF",1,IF(AND(ISNUMBER(O322),O322&gt;59),1,_xlfn.XLOOKUP(O322,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="Q322" s="13">
+      <c r="Q322" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
         <v>0</v>
       </c>
-      <c r="R322" s="13">
+      <c r="R322" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
         <v>0</v>
       </c>
-      <c r="S322" s="13">
+      <c r="S322" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
         <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B323" t="s">
         <v>31</v>
       </c>
       <c r="C323" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D323" s="3">
-        <v>12100</v>
+        <v>1042</v>
       </c>
       <c r="F323" s="3" t="str">
         <f>IF(E323="","",IF(E323="DNS",0,IF(E323="DQ",0,IF(E323="DNF",1,IF(AND(ISNUMBER(E323),E323&gt;59),1,_xlfn.XLOOKUP(E323,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19193,16 +19187,16 @@
     </row>
     <row r="324" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="B324" t="s">
         <v>31</v>
       </c>
       <c r="C324" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D324" s="3">
-        <v>12099</v>
+        <v>1043</v>
       </c>
       <c r="F324" s="3" t="str">
         <f>IF(E324="","",IF(E324="DNS",0,IF(E324="DQ",0,IF(E324="DNF",1,IF(AND(ISNUMBER(E324),E324&gt;59),1,_xlfn.XLOOKUP(E324,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19243,16 +19237,16 @@
     </row>
     <row r="325" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="B325" t="s">
         <v>31</v>
       </c>
       <c r="C325" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D325" s="3">
-        <v>12098</v>
+        <v>1041</v>
       </c>
       <c r="F325" s="3" t="str">
         <f>IF(E325="","",IF(E325="DNS",0,IF(E325="DQ",0,IF(E325="DNF",1,IF(AND(ISNUMBER(E325),E325&gt;59),1,_xlfn.XLOOKUP(E325,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19293,16 +19287,16 @@
     </row>
     <row r="326" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="B326" t="s">
         <v>31</v>
       </c>
       <c r="C326" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D326" s="3">
-        <v>12097</v>
+        <v>935</v>
       </c>
       <c r="F326" s="3" t="str">
         <f>IF(E326="","",IF(E326="DNS",0,IF(E326="DQ",0,IF(E326="DNF",1,IF(AND(ISNUMBER(E326),E326&gt;59),1,_xlfn.XLOOKUP(E326,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19342,17 +19336,17 @@
       </c>
     </row>
     <row r="327" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A327" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="B327" s="11" t="s">
+      <c r="A327" t="s">
+        <v>370</v>
+      </c>
+      <c r="B327" t="s">
         <v>31</v>
       </c>
-      <c r="C327" s="11" t="s">
-        <v>1</v>
+      <c r="C327" t="s">
+        <v>6</v>
       </c>
       <c r="D327" s="3">
-        <v>12906</v>
+        <v>933</v>
       </c>
       <c r="F327" s="3" t="str">
         <f>IF(E327="","",IF(E327="DNS",0,IF(E327="DQ",0,IF(E327="DNF",1,IF(AND(ISNUMBER(E327),E327&gt;59),1,_xlfn.XLOOKUP(E327,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19393,16 +19387,16 @@
     </row>
     <row r="328" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="B328" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C328" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D328" s="3">
-        <v>12102</v>
+        <v>931</v>
       </c>
       <c r="F328" s="3" t="str">
         <f>IF(E328="","",IF(E328="DNS",0,IF(E328="DQ",0,IF(E328="DNF",1,IF(AND(ISNUMBER(E328),E328&gt;59),1,_xlfn.XLOOKUP(E328,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19443,16 +19437,16 @@
     </row>
     <row r="329" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="B329" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C329" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D329" s="3">
-        <v>12101</v>
+        <v>932</v>
       </c>
       <c r="F329" s="3" t="str">
         <f>IF(E329="","",IF(E329="DNS",0,IF(E329="DQ",0,IF(E329="DNF",1,IF(AND(ISNUMBER(E329),E329&gt;59),1,_xlfn.XLOOKUP(E329,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19492,73 +19486,67 @@
       </c>
     </row>
     <row r="330" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A330" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B330" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C330" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D330" s="15">
-        <v>1226</v>
-      </c>
-      <c r="E330" s="15"/>
-      <c r="F330" s="15" t="str">
+      <c r="A330" t="s">
+        <v>371</v>
+      </c>
+      <c r="B330" t="s">
+        <v>31</v>
+      </c>
+      <c r="C330" t="s">
+        <v>6</v>
+      </c>
+      <c r="D330" s="3">
+        <v>934</v>
+      </c>
+      <c r="F330" s="3" t="str">
         <f>IF(E330="","",IF(E330="DNS",0,IF(E330="DQ",0,IF(E330="DNF",1,IF(AND(ISNUMBER(E330),E330&gt;59),1,_xlfn.XLOOKUP(E330,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="G330" s="15"/>
-      <c r="H330" s="15" t="str">
+      <c r="H330" s="3" t="str">
         <f>IF(G330="","",IF(G330="DNS",0,IF(G330="DQ",0,IF(G330="DNF",1,IF(AND(ISNUMBER(G330),G330&gt;59),1,_xlfn.XLOOKUP(G330,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="I330" s="15"/>
-      <c r="J330" s="15" t="str">
+      <c r="J330" s="3" t="str">
         <f>IF(I330="","",IF(I330="DNS",0,IF(I330="DQ",0,IF(I330="DNF",1,IF(AND(ISNUMBER(I330),I330&gt;59),1,_xlfn.XLOOKUP(I330,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="K330" s="15"/>
-      <c r="L330" s="15" t="str">
+      <c r="L330" s="3" t="str">
         <f>IF(K330="","",IF(K330="DNS",0,IF(K330="DQ",0,IF(K330="DNF",1,IF(AND(ISNUMBER(K330),K330&gt;59),1,_xlfn.XLOOKUP(K330,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="M330" s="15"/>
-      <c r="N330" s="15" t="str">
+      <c r="N330" s="3" t="str">
         <f>IF(M330="","",IF(M330="DNS",0,IF(M330="DQ",0,IF(M330="DNF",1,IF(AND(ISNUMBER(M330),M330&gt;59),1,_xlfn.XLOOKUP(M330,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="O330" s="15"/>
-      <c r="P330" s="15" t="str">
+      <c r="P330" s="3" t="str">
         <f>IF(O330="","",IF(O330="DNS",0,IF(O330="DQ",0,IF(O330="DNF",1,IF(AND(ISNUMBER(O330),O330&gt;59),1,_xlfn.XLOOKUP(O330,tbl_points[Place],tbl_points[Points],""))))))</f>
         <v/>
       </c>
-      <c r="Q330" s="15">
+      <c r="Q330" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
         <v>0</v>
       </c>
-      <c r="R330" s="15">
+      <c r="R330" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
         <v>0</v>
       </c>
-      <c r="S330" s="15">
+      <c r="S330" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
         <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
-        <v>126</v>
+        <v>391</v>
       </c>
       <c r="B331" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C331" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D331" s="3">
-        <v>1227</v>
+        <v>12100</v>
       </c>
       <c r="F331" s="3" t="str">
         <f>IF(E331="","",IF(E331="DNS",0,IF(E331="DQ",0,IF(E331="DNF",1,IF(AND(ISNUMBER(E331),E331&gt;59),1,_xlfn.XLOOKUP(E331,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19599,16 +19587,16 @@
     </row>
     <row r="332" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>143</v>
+        <v>390</v>
       </c>
       <c r="B332" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C332" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D332" s="3">
-        <v>1233</v>
+        <v>12099</v>
       </c>
       <c r="F332" s="3" t="str">
         <f>IF(E332="","",IF(E332="DNS",0,IF(E332="DQ",0,IF(E332="DNF",1,IF(AND(ISNUMBER(E332),E332&gt;59),1,_xlfn.XLOOKUP(E332,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19649,16 +19637,16 @@
     </row>
     <row r="333" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>141</v>
+        <v>389</v>
       </c>
       <c r="B333" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C333" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D333" s="3">
-        <v>1231</v>
+        <v>12098</v>
       </c>
       <c r="F333" s="3" t="str">
         <f>IF(E333="","",IF(E333="DNS",0,IF(E333="DQ",0,IF(E333="DNF",1,IF(AND(ISNUMBER(E333),E333&gt;59),1,_xlfn.XLOOKUP(E333,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19699,16 +19687,16 @@
     </row>
     <row r="334" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
-        <v>140</v>
+        <v>388</v>
       </c>
       <c r="B334" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C334" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D334" s="3">
-        <v>1230</v>
+        <v>12097</v>
       </c>
       <c r="F334" s="3" t="str">
         <f>IF(E334="","",IF(E334="DNS",0,IF(E334="DQ",0,IF(E334="DNF",1,IF(AND(ISNUMBER(E334),E334&gt;59),1,_xlfn.XLOOKUP(E334,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19748,17 +19736,17 @@
       </c>
     </row>
     <row r="335" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A335" t="s">
-        <v>142</v>
-      </c>
-      <c r="B335" t="s">
-        <v>14</v>
-      </c>
-      <c r="C335" t="s">
-        <v>2</v>
+      <c r="A335" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="B335" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C335" s="17" t="s">
+        <v>1</v>
       </c>
       <c r="D335" s="3">
-        <v>1232</v>
+        <v>12906</v>
       </c>
       <c r="F335" s="3" t="str">
         <f>IF(E335="","",IF(E335="DNS",0,IF(E335="DQ",0,IF(E335="DNF",1,IF(AND(ISNUMBER(E335),E335&gt;59),1,_xlfn.XLOOKUP(E335,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19799,16 +19787,16 @@
     </row>
     <row r="336" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>216</v>
+        <v>387</v>
       </c>
       <c r="B336" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C336" t="s">
         <v>2</v>
       </c>
       <c r="D336" s="3">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="F336" s="3" t="str">
         <f>IF(E336="","",IF(E336="DNS",0,IF(E336="DQ",0,IF(E336="DNF",1,IF(AND(ISNUMBER(E336),E336&gt;59),1,_xlfn.XLOOKUP(E336,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19849,16 +19837,16 @@
     </row>
     <row r="337" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
-        <v>218</v>
+        <v>385</v>
       </c>
       <c r="B337" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C337" t="s">
         <v>2</v>
       </c>
       <c r="D337" s="3">
-        <v>1236</v>
+        <v>1245</v>
       </c>
       <c r="F337" s="3" t="str">
         <f>IF(E337="","",IF(E337="DNS",0,IF(E337="DQ",0,IF(E337="DNF",1,IF(AND(ISNUMBER(E337),E337&gt;59),1,_xlfn.XLOOKUP(E337,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19899,16 +19887,16 @@
     </row>
     <row r="338" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
-        <v>217</v>
+        <v>386</v>
       </c>
       <c r="B338" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C338" t="s">
         <v>2</v>
       </c>
       <c r="D338" s="3">
-        <v>1235</v>
+        <v>1246</v>
       </c>
       <c r="F338" s="3" t="str">
         <f>IF(E338="","",IF(E338="DNS",0,IF(E338="DQ",0,IF(E338="DNF",1,IF(AND(ISNUMBER(E338),E338&gt;59),1,_xlfn.XLOOKUP(E338,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19949,16 +19937,16 @@
     </row>
     <row r="339" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>230</v>
+        <v>392</v>
       </c>
       <c r="B339" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C339" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D339" s="3">
-        <v>1238</v>
+        <v>8084</v>
       </c>
       <c r="F339" s="3" t="str">
         <f>IF(E339="","",IF(E339="DNS",0,IF(E339="DQ",0,IF(E339="DNF",1,IF(AND(ISNUMBER(E339),E339&gt;59),1,_xlfn.XLOOKUP(E339,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19999,16 +19987,16 @@
     </row>
     <row r="340" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>229</v>
+        <v>396</v>
       </c>
       <c r="B340" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C340" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D340" s="3">
-        <v>1237</v>
+        <v>10202</v>
       </c>
       <c r="F340" s="3" t="str">
         <f>IF(E340="","",IF(E340="DNS",0,IF(E340="DQ",0,IF(E340="DNF",1,IF(AND(ISNUMBER(E340),E340&gt;59),1,_xlfn.XLOOKUP(E340,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20049,16 +20037,16 @@
     </row>
     <row r="341" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
-        <v>272</v>
+        <v>397</v>
       </c>
       <c r="B341" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C341" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D341" s="3">
-        <v>1239</v>
+        <v>1044</v>
       </c>
       <c r="F341" s="3" t="str">
         <f>IF(E341="","",IF(E341="DNS",0,IF(E341="DQ",0,IF(E341="DNF",1,IF(AND(ISNUMBER(E341),E341&gt;59),1,_xlfn.XLOOKUP(E341,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20099,16 +20087,16 @@
     </row>
     <row r="342" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>274</v>
+        <v>394</v>
       </c>
       <c r="B342" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C342" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D342" s="3">
-        <v>1241</v>
+        <v>953</v>
       </c>
       <c r="F342" s="3" t="str">
         <f>IF(E342="","",IF(E342="DNS",0,IF(E342="DQ",0,IF(E342="DNF",1,IF(AND(ISNUMBER(E342),E342&gt;59),1,_xlfn.XLOOKUP(E342,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20149,16 +20137,16 @@
     </row>
     <row r="343" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c r="B343" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C343" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D343" s="3">
-        <v>1242</v>
+        <v>952</v>
       </c>
       <c r="F343" s="3" t="str">
         <f>IF(E343="","",IF(E343="DNS",0,IF(E343="DQ",0,IF(E343="DNF",1,IF(AND(ISNUMBER(E343),E343&gt;59),1,_xlfn.XLOOKUP(E343,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20199,16 +20187,16 @@
     </row>
     <row r="344" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>273</v>
+        <v>395</v>
       </c>
       <c r="B344" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C344" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D344" s="3">
-        <v>1240</v>
+        <v>954</v>
       </c>
       <c r="F344" s="3" t="str">
         <f>IF(E344="","",IF(E344="DNS",0,IF(E344="DQ",0,IF(E344="DNF",1,IF(AND(ISNUMBER(E344),E344&gt;59),1,_xlfn.XLOOKUP(E344,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20249,16 +20237,16 @@
     </row>
     <row r="345" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
-        <v>337</v>
+        <v>399</v>
       </c>
       <c r="B345" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C345" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D345" s="3">
-        <v>1243</v>
+        <v>12102</v>
       </c>
       <c r="F345" s="3" t="str">
         <f>IF(E345="","",IF(E345="DNS",0,IF(E345="DQ",0,IF(E345="DNF",1,IF(AND(ISNUMBER(E345),E345&gt;59),1,_xlfn.XLOOKUP(E345,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20299,16 +20287,16 @@
     </row>
     <row r="346" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
-        <v>349</v>
+        <v>398</v>
       </c>
       <c r="B346" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C346" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D346" s="3">
-        <v>1244</v>
+        <v>12101</v>
       </c>
       <c r="F346" s="3" t="str">
         <f>IF(E346="","",IF(E346="DNS",0,IF(E346="DQ",0,IF(E346="DNF",1,IF(AND(ISNUMBER(E346),E346&gt;59),1,_xlfn.XLOOKUP(E346,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20349,16 +20337,16 @@
     </row>
     <row r="347" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B347" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C347" t="s">
         <v>2</v>
       </c>
       <c r="D347" s="3">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F347" s="3" t="str">
         <f>IF(E347="","",IF(E347="DNS",0,IF(E347="DQ",0,IF(E347="DNF",1,IF(AND(ISNUMBER(E347),E347&gt;59),1,_xlfn.XLOOKUP(E347,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20399,16 +20387,16 @@
     </row>
     <row r="348" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="B348" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C348" t="s">
         <v>2</v>
       </c>
       <c r="D348" s="3">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="F348" s="3" t="str">
         <f>IF(E348="","",IF(E348="DNS",0,IF(E348="DQ",0,IF(E348="DNF",1,IF(AND(ISNUMBER(E348),E348&gt;59),1,_xlfn.XLOOKUP(E348,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20447,158 +20435,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A349" t="s">
-        <v>386</v>
-      </c>
-      <c r="B349" t="s">
-        <v>31</v>
-      </c>
-      <c r="C349" t="s">
-        <v>2</v>
-      </c>
-      <c r="D349" s="3">
-        <v>1246</v>
-      </c>
-      <c r="F349" s="3" t="str">
-        <f>IF(E349="","",IF(E349="DNS",0,IF(E349="DQ",0,IF(E349="DNF",1,IF(AND(ISNUMBER(E349),E349&gt;59),1,_xlfn.XLOOKUP(E349,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="H349" s="3" t="str">
-        <f>IF(G349="","",IF(G349="DNS",0,IF(G349="DQ",0,IF(G349="DNF",1,IF(AND(ISNUMBER(G349),G349&gt;59),1,_xlfn.XLOOKUP(G349,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="J349" s="3" t="str">
-        <f>IF(I349="","",IF(I349="DNS",0,IF(I349="DQ",0,IF(I349="DNF",1,IF(AND(ISNUMBER(I349),I349&gt;59),1,_xlfn.XLOOKUP(I349,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="L349" s="3" t="str">
-        <f>IF(K349="","",IF(K349="DNS",0,IF(K349="DQ",0,IF(K349="DNF",1,IF(AND(ISNUMBER(K349),K349&gt;59),1,_xlfn.XLOOKUP(K349,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="N349" s="3" t="str">
-        <f>IF(M349="","",IF(M349="DNS",0,IF(M349="DQ",0,IF(M349="DNF",1,IF(AND(ISNUMBER(M349),M349&gt;59),1,_xlfn.XLOOKUP(M349,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="P349" s="3" t="str">
-        <f>IF(O349="","",IF(O349="DNS",0,IF(O349="DQ",0,IF(O349="DNF",1,IF(AND(ISNUMBER(O349),O349&gt;59),1,_xlfn.XLOOKUP(O349,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="Q349" s="3">
-        <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
-      </c>
-      <c r="R349" s="3">
-        <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
-      </c>
-      <c r="S349" s="3">
-        <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A350" t="s">
-        <v>400</v>
-      </c>
-      <c r="B350" t="s">
-        <v>32</v>
-      </c>
-      <c r="C350" t="s">
-        <v>2</v>
-      </c>
-      <c r="D350" s="3">
-        <v>1248</v>
-      </c>
-      <c r="F350" s="3" t="str">
-        <f>IF(E350="","",IF(E350="DNS",0,IF(E350="DQ",0,IF(E350="DNF",1,IF(AND(ISNUMBER(E350),E350&gt;59),1,_xlfn.XLOOKUP(E350,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="H350" s="3" t="str">
-        <f>IF(G350="","",IF(G350="DNS",0,IF(G350="DQ",0,IF(G350="DNF",1,IF(AND(ISNUMBER(G350),G350&gt;59),1,_xlfn.XLOOKUP(G350,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="J350" s="3" t="str">
-        <f>IF(I350="","",IF(I350="DNS",0,IF(I350="DQ",0,IF(I350="DNF",1,IF(AND(ISNUMBER(I350),I350&gt;59),1,_xlfn.XLOOKUP(I350,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="L350" s="3" t="str">
-        <f>IF(K350="","",IF(K350="DNS",0,IF(K350="DQ",0,IF(K350="DNF",1,IF(AND(ISNUMBER(K350),K350&gt;59),1,_xlfn.XLOOKUP(K350,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="N350" s="3" t="str">
-        <f>IF(M350="","",IF(M350="DNS",0,IF(M350="DQ",0,IF(M350="DNF",1,IF(AND(ISNUMBER(M350),M350&gt;59),1,_xlfn.XLOOKUP(M350,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="P350" s="3" t="str">
-        <f>IF(O350="","",IF(O350="DNS",0,IF(O350="DQ",0,IF(O350="DNF",1,IF(AND(ISNUMBER(O350),O350&gt;59),1,_xlfn.XLOOKUP(O350,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="Q350" s="3">
-        <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
-      </c>
-      <c r="R350" s="3">
-        <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
-      </c>
-      <c r="S350" s="3">
-        <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A351" t="s">
-        <v>401</v>
-      </c>
-      <c r="B351" t="s">
-        <v>32</v>
-      </c>
-      <c r="C351" t="s">
-        <v>2</v>
-      </c>
-      <c r="D351" s="3">
-        <v>1249</v>
-      </c>
-      <c r="F351" s="3" t="str">
-        <f>IF(E351="","",IF(E351="DNS",0,IF(E351="DQ",0,IF(E351="DNF",1,IF(AND(ISNUMBER(E351),E351&gt;59),1,_xlfn.XLOOKUP(E351,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="H351" s="3" t="str">
-        <f>IF(G351="","",IF(G351="DNS",0,IF(G351="DQ",0,IF(G351="DNF",1,IF(AND(ISNUMBER(G351),G351&gt;59),1,_xlfn.XLOOKUP(G351,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="J351" s="3" t="str">
-        <f>IF(I351="","",IF(I351="DNS",0,IF(I351="DQ",0,IF(I351="DNF",1,IF(AND(ISNUMBER(I351),I351&gt;59),1,_xlfn.XLOOKUP(I351,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="L351" s="3" t="str">
-        <f>IF(K351="","",IF(K351="DNS",0,IF(K351="DQ",0,IF(K351="DNF",1,IF(AND(ISNUMBER(K351),K351&gt;59),1,_xlfn.XLOOKUP(K351,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="N351" s="3" t="str">
-        <f>IF(M351="","",IF(M351="DNS",0,IF(M351="DQ",0,IF(M351="DNF",1,IF(AND(ISNUMBER(M351),M351&gt;59),1,_xlfn.XLOOKUP(M351,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="P351" s="3" t="str">
-        <f>IF(O351="","",IF(O351="DNS",0,IF(O351="DQ",0,IF(O351="DNF",1,IF(AND(ISNUMBER(O351),O351&gt;59),1,_xlfn.XLOOKUP(O351,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v/>
-      </c>
-      <c r="Q351" s="3">
-        <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
-      </c>
-      <c r="R351" s="3">
-        <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
-      </c>
-      <c r="S351" s="3">
-        <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D381">
+  <conditionalFormatting sqref="D2:D378">
     <cfRule type="expression" dxfId="15" priority="1">
       <formula>$C2="Bant Boys"</formula>
     </cfRule>
@@ -20636,13 +20474,13 @@
           <x14:formula1>
             <xm:f>helper!$B$2:$B$24</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B351</xm:sqref>
+          <xm:sqref>B2:B348</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D143BE4B-2ABD-4071-9EA1-71E4DA942A1C}">
           <x14:formula1>
             <xm:f>helper!$A$2:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C351</xm:sqref>
+          <xm:sqref>C2:C348</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -20652,7 +20490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB56E0A-EA51-4435-B11C-72027CE87945}">
-  <dimension ref="A1:S99"/>
+  <dimension ref="A1:S98"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
@@ -20729,7 +20567,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" t="str" cm="1">
-        <f t="array" ref="A4:S99">IF($B$1="","",
+        <f t="array" ref="A4:S98">IF($B$1="","",
     _xlfn._xlws.SORT(
         _xlfn._xlws.FILTER(
             tbl_individual[],
@@ -21633,7 +21471,7 @@
         <v>Sr Boys</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>12103</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -25931,16 +25769,16 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A92" t="str">
-        <v>Oliver Radedge</v>
+        <v>Oliver Koch</v>
       </c>
       <c r="B92" t="str">
-        <v>West Van</v>
+        <v>Whistler</v>
       </c>
       <c r="C92" t="str">
         <v>Sr Boys</v>
       </c>
       <c r="D92">
-        <v>12096</v>
+        <v>12100</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -25990,7 +25828,7 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A93" t="str">
-        <v>Oliver Koch</v>
+        <v>Cove White</v>
       </c>
       <c r="B93" t="str">
         <v>Whistler</v>
@@ -25999,7 +25837,7 @@
         <v>Sr Boys</v>
       </c>
       <c r="D93">
-        <v>12100</v>
+        <v>12099</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -26049,7 +25887,7 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A94" t="str">
-        <v>Cove White</v>
+        <v>Kaede Gossman</v>
       </c>
       <c r="B94" t="str">
         <v>Whistler</v>
@@ -26058,7 +25896,7 @@
         <v>Sr Boys</v>
       </c>
       <c r="D94">
-        <v>12099</v>
+        <v>12098</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -26108,7 +25946,7 @@
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A95" t="str">
-        <v>Kaede Gossman</v>
+        <v>Damyen Bouvier</v>
       </c>
       <c r="B95" t="str">
         <v>Whistler</v>
@@ -26117,7 +25955,7 @@
         <v>Sr Boys</v>
       </c>
       <c r="D95">
-        <v>12098</v>
+        <v>12097</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -26167,7 +26005,7 @@
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A96" t="str">
-        <v>Damyen Bouvier</v>
+        <v>Theo Rothdram</v>
       </c>
       <c r="B96" t="str">
         <v>Whistler</v>
@@ -26176,7 +26014,7 @@
         <v>Sr Boys</v>
       </c>
       <c r="D96">
-        <v>12097</v>
+        <v>12906</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -26226,16 +26064,16 @@
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A97" t="str">
-        <v>Theo Rothdram</v>
+        <v>Logan Anderson</v>
       </c>
       <c r="B97" t="str">
-        <v>Whistler</v>
+        <v>Windsor</v>
       </c>
       <c r="C97" t="str">
         <v>Sr Boys</v>
       </c>
       <c r="D97">
-        <v>12906</v>
+        <v>12102</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -26285,7 +26123,7 @@
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A98" t="str">
-        <v>Logan Anderson</v>
+        <v>Sam Fort</v>
       </c>
       <c r="B98" t="str">
         <v>Windsor</v>
@@ -26294,7 +26132,7 @@
         <v>Sr Boys</v>
       </c>
       <c r="D98">
-        <v>12102</v>
+        <v>12101</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -26339,65 +26177,6 @@
         <v>0</v>
       </c>
       <c r="S98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A99" t="str">
-        <v>Sam Fort</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Windsor</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Sr Boys</v>
-      </c>
-      <c r="D99">
-        <v>12101</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99" t="str">
-        <v/>
-      </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-      <c r="H99" t="str">
-        <v/>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99" t="str">
-        <v/>
-      </c>
-      <c r="K99">
-        <v>0</v>
-      </c>
-      <c r="L99" t="str">
-        <v/>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99" t="str">
-        <v/>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99" t="str">
-        <v/>
-      </c>
-      <c r="Q99">
-        <v>0</v>
-      </c>
-      <c r="R99">
-        <v>0</v>
-      </c>
-      <c r="S99">
         <v>0</v>
       </c>
     </row>

--- a/results_2026_master.xlsx
+++ b/results_2026_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19247\Documents\codemathbike\codemathbike_bike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BFDCEDB-1352-44F5-BA39-1F6B49ED6518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{868182DF-9306-4A6D-B30D-3B6CBBE0220C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="-20680" windowWidth="28520" windowHeight="18810" activeTab="2" xr2:uid="{E4CCCC36-747C-4C6A-A938-400850181E6F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{E4CCCC36-747C-4C6A-A938-400850181E6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Rosters - notes" sheetId="11" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="426">
   <si>
     <t>Divisions</t>
   </si>
@@ -1857,10 +1857,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0A7F75BD-58F6-4493-BFAC-CEF3E5A7D6A6}" name="tbl_individual3" displayName="tbl_individual3" ref="A1:E354" totalsRowShown="0" headerRowDxfId="43">
   <autoFilter ref="A1:E354" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}">
@@ -1900,11 +1896,11 @@
   <autoFilter ref="A1:S353" xr:uid="{4732A653-9976-4BC3-B1BB-3377C0BE5451}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Juv Boys"/>
+        <filter val="Bant Boys"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:S350">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A23:S352">
     <sortCondition ref="E1:E353"/>
   </sortState>
   <tableColumns count="19">
@@ -8439,7 +8435,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -8492,7 +8488,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -8545,7 +8541,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -8598,7 +8594,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>159</v>
       </c>
@@ -8651,7 +8647,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -8704,7 +8700,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>291</v>
       </c>
@@ -8757,7 +8753,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>292</v>
       </c>
@@ -8810,7 +8806,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>238</v>
       </c>
@@ -8863,7 +8859,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>250</v>
       </c>
@@ -8916,7 +8912,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -8969,7 +8965,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -9393,25 +9389,25 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>8147</v>
+        <v>837</v>
       </c>
       <c r="E23" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
         <f>IF(E23="","",IF(E23="DNS",0,IF(E23="DQ",0,IF(E23="DNF",1,IF(AND(ISNUMBER(E23),E23&gt;59),1,_xlfn.XLOOKUP(E23,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="H23" s="3" t="str">
         <f>IF(G23="","",IF(G23="DNS",0,IF(G23="DQ",0,IF(G23="DNF",1,IF(AND(ISNUMBER(G23),G23&gt;59),1,_xlfn.XLOOKUP(G23,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9435,15 +9431,15 @@
       </c>
       <c r="Q23" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="R23" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="S23" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>37</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -9552,25 +9548,25 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>8049</v>
+        <v>838</v>
       </c>
       <c r="E26" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3">
         <f>IF(E26="","",IF(E26="DNS",0,IF(E26="DQ",0,IF(E26="DNF",1,IF(AND(ISNUMBER(E26),E26&gt;59),1,_xlfn.XLOOKUP(E26,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="H26" s="3" t="str">
         <f>IF(G26="","",IF(G26="DNS",0,IF(G26="DQ",0,IF(G26="DNF",1,IF(AND(ISNUMBER(G26),G26&gt;59),1,_xlfn.XLOOKUP(G26,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -9594,15 +9590,15 @@
       </c>
       <c r="Q26" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="R26" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="S26" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -10135,25 +10131,25 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="3">
-        <v>8185</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>415</v>
+        <v>8196</v>
+      </c>
+      <c r="E37" s="3">
+        <v>3</v>
       </c>
       <c r="F37" s="3">
         <f>IF(E37="","",IF(E37="DNS",0,IF(E37="DQ",0,IF(E37="DNF",1,IF(AND(ISNUMBER(E37),E37&gt;59),1,_xlfn.XLOOKUP(E37,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H37" s="3" t="str">
         <f>IF(G37="","",IF(G37="DNS",0,IF(G37="DQ",0,IF(G37="DNF",1,IF(AND(ISNUMBER(G37),G37&gt;59),1,_xlfn.XLOOKUP(G37,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10177,36 +10173,36 @@
       </c>
       <c r="Q37" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="R37" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="S37" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="3">
-        <v>8010</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>416</v>
+        <v>8198</v>
+      </c>
+      <c r="E38" s="3">
+        <v>3</v>
       </c>
       <c r="F38" s="3">
         <f>IF(E38="","",IF(E38="DNS",0,IF(E38="DQ",0,IF(E38="DNF",1,IF(AND(ISNUMBER(E38),E38&gt;59),1,_xlfn.XLOOKUP(E38,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H38" s="3" t="str">
         <f>IF(G38="","",IF(G38="DNS",0,IF(G38="DQ",0,IF(G38="DNF",1,IF(AND(ISNUMBER(G38),G38&gt;59),1,_xlfn.XLOOKUP(G38,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10230,36 +10226,36 @@
       </c>
       <c r="Q38" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R38" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S38" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>414</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="3">
-        <v>8086</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>416</v>
+        <v>839</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4</v>
       </c>
       <c r="F39" s="3">
         <f>IF(E39="","",IF(E39="DNS",0,IF(E39="DQ",0,IF(E39="DNF",1,IF(AND(ISNUMBER(E39),E39&gt;59),1,_xlfn.XLOOKUP(E39,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H39" s="3" t="str">
         <f>IF(G39="","",IF(G39="DNS",0,IF(G39="DQ",0,IF(G39="DNF",1,IF(AND(ISNUMBER(G39),G39&gt;59),1,_xlfn.XLOOKUP(G39,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10283,15 +10279,15 @@
       </c>
       <c r="Q39" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R39" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S39" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -10877,25 +10873,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="3">
-        <v>8140</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>416</v>
+        <v>816</v>
+      </c>
+      <c r="E51" s="3">
+        <v>5</v>
       </c>
       <c r="F51" s="3">
         <f>IF(E51="","",IF(E51="DNS",0,IF(E51="DQ",0,IF(E51="DNF",1,IF(AND(ISNUMBER(E51),E51&gt;59),1,_xlfn.XLOOKUP(E51,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H51" s="3" t="str">
         <f>IF(G51="","",IF(G51="DNS",0,IF(G51="DQ",0,IF(G51="DNF",1,IF(AND(ISNUMBER(G51),G51&gt;59),1,_xlfn.XLOOKUP(G51,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10919,36 +10915,36 @@
       </c>
       <c r="Q51" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R51" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S51" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="3">
-        <v>8154</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>416</v>
+        <v>831</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6</v>
       </c>
       <c r="F52" s="3">
         <f>IF(E52="","",IF(E52="DNS",0,IF(E52="DQ",0,IF(E52="DNF",1,IF(AND(ISNUMBER(E52),E52&gt;59),1,_xlfn.XLOOKUP(E52,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H52" s="3" t="str">
         <f>IF(G52="","",IF(G52="DNS",0,IF(G52="DQ",0,IF(G52="DNF",1,IF(AND(ISNUMBER(G52),G52&gt;59),1,_xlfn.XLOOKUP(G52,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -10972,36 +10968,36 @@
       </c>
       <c r="Q52" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="R52" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S52" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>352</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="3">
-        <v>8177</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>416</v>
+        <v>832</v>
+      </c>
+      <c r="E53" s="3">
+        <v>7</v>
       </c>
       <c r="F53" s="3">
         <f>IF(E53="","",IF(E53="DNS",0,IF(E53="DQ",0,IF(E53="DNF",1,IF(AND(ISNUMBER(E53),E53&gt;59),1,_xlfn.XLOOKUP(E53,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H53" s="3" t="str">
         <f>IF(G53="","",IF(G53="DNS",0,IF(G53="DQ",0,IF(G53="DNF",1,IF(AND(ISNUMBER(G53),G53&gt;59),1,_xlfn.XLOOKUP(G53,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11025,36 +11021,36 @@
       </c>
       <c r="Q53" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R53" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S53" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="3">
-        <v>8181</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>416</v>
+        <v>804</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8</v>
       </c>
       <c r="F54" s="3">
         <f>IF(E54="","",IF(E54="DNS",0,IF(E54="DQ",0,IF(E54="DNF",1,IF(AND(ISNUMBER(E54),E54&gt;59),1,_xlfn.XLOOKUP(E54,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H54" s="3" t="str">
         <f>IF(G54="","",IF(G54="DNS",0,IF(G54="DQ",0,IF(G54="DNF",1,IF(AND(ISNUMBER(G54),G54&gt;59),1,_xlfn.XLOOKUP(G54,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11078,36 +11074,36 @@
       </c>
       <c r="Q54" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R54" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S54" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>408</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="3">
-        <v>8186</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>416</v>
+        <v>8009</v>
+      </c>
+      <c r="E55" s="3">
+        <v>9</v>
       </c>
       <c r="F55" s="3">
         <f>IF(E55="","",IF(E55="DNS",0,IF(E55="DQ",0,IF(E55="DNF",1,IF(AND(ISNUMBER(E55),E55&gt;59),1,_xlfn.XLOOKUP(E55,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H55" s="3" t="str">
         <f>IF(G55="","",IF(G55="DNS",0,IF(G55="DQ",0,IF(G55="DNF",1,IF(AND(ISNUMBER(G55),G55&gt;59),1,_xlfn.XLOOKUP(G55,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11131,15 +11127,15 @@
       </c>
       <c r="Q55" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R55" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S55" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -11195,7 +11191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>418</v>
       </c>
@@ -11301,7 +11297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -11354,25 +11350,25 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>103</v>
+        <v>313</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
         <v>7</v>
       </c>
       <c r="D60" s="3">
-        <v>8189</v>
+        <v>824</v>
       </c>
       <c r="E60" s="3">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3">
         <f>IF(E60="","",IF(E60="DNS",0,IF(E60="DQ",0,IF(E60="DNF",1,IF(AND(ISNUMBER(E60),E60&gt;59),1,_xlfn.XLOOKUP(E60,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="H60" s="3" t="str">
         <f>IF(G60="","",IF(G60="DNS",0,IF(G60="DQ",0,IF(G60="DNF",1,IF(AND(ISNUMBER(G60),G60&gt;59),1,_xlfn.XLOOKUP(G60,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11396,15 +11392,15 @@
       </c>
       <c r="Q60" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="R60" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="S60" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -11725,25 +11721,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="3">
-        <v>8190</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>416</v>
+        <v>8197</v>
+      </c>
+      <c r="E67" s="3">
+        <v>11</v>
       </c>
       <c r="F67" s="3">
         <f>IF(E67="","",IF(E67="DNS",0,IF(E67="DQ",0,IF(E67="DNF",1,IF(AND(ISNUMBER(E67),E67&gt;59),1,_xlfn.XLOOKUP(E67,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H67" s="3" t="str">
         <f>IF(G67="","",IF(G67="DNS",0,IF(G67="DQ",0,IF(G67="DNF",1,IF(AND(ISNUMBER(G67),G67&gt;59),1,_xlfn.XLOOKUP(G67,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11767,15 +11763,15 @@
       </c>
       <c r="Q67" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R67" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="S67" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -11831,25 +11827,25 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>113</v>
+        <v>305</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
         <v>7</v>
       </c>
       <c r="D69" s="3">
-        <v>8191</v>
+        <v>823</v>
       </c>
       <c r="E69" s="3">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F69" s="3">
         <f>IF(E69="","",IF(E69="DNS",0,IF(E69="DQ",0,IF(E69="DNF",1,IF(AND(ISNUMBER(E69),E69&gt;59),1,_xlfn.XLOOKUP(E69,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H69" s="3" t="str">
         <f>IF(G69="","",IF(G69="DNS",0,IF(G69="DQ",0,IF(G69="DNF",1,IF(AND(ISNUMBER(G69),G69&gt;59),1,_xlfn.XLOOKUP(G69,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11873,36 +11869,36 @@
       </c>
       <c r="Q69" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="R69" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="S69" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>114</v>
+        <v>314</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
         <v>7</v>
       </c>
       <c r="D70" s="3">
-        <v>8192</v>
+        <v>825</v>
       </c>
       <c r="E70" s="3">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F70" s="3">
         <f>IF(E70="","",IF(E70="DNS",0,IF(E70="DQ",0,IF(E70="DNF",1,IF(AND(ISNUMBER(E70),E70&gt;59),1,_xlfn.XLOOKUP(E70,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H70" s="3" t="str">
         <f>IF(G70="","",IF(G70="DNS",0,IF(G70="DQ",0,IF(G70="DNF",1,IF(AND(ISNUMBER(G70),G70&gt;59),1,_xlfn.XLOOKUP(G70,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -11926,15 +11922,15 @@
       </c>
       <c r="Q70" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="R70" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="S70" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -12467,7 +12463,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>337</v>
       </c>
@@ -12520,7 +12516,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>72</v>
       </c>
@@ -12944,25 +12940,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>122</v>
+        <v>246</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
       </c>
       <c r="D90" s="3">
-        <v>8193</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>416</v>
+        <v>817</v>
+      </c>
+      <c r="E90" s="3">
+        <v>14</v>
       </c>
       <c r="F90" s="3">
         <f>IF(E90="","",IF(E90="DNS",0,IF(E90="DQ",0,IF(E90="DNF",1,IF(AND(ISNUMBER(E90),E90&gt;59),1,_xlfn.XLOOKUP(E90,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H90" s="3" t="str">
         <f>IF(G90="","",IF(G90="DNS",0,IF(G90="DQ",0,IF(G90="DNF",1,IF(AND(ISNUMBER(G90),G90&gt;59),1,_xlfn.XLOOKUP(G90,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -12986,36 +12982,36 @@
       </c>
       <c r="Q90" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="R90" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="S90" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>123</v>
+        <v>356</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
       </c>
       <c r="D91" s="3">
-        <v>8194</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>416</v>
+        <v>833</v>
+      </c>
+      <c r="E91" s="3">
+        <v>15</v>
       </c>
       <c r="F91" s="3">
         <f>IF(E91="","",IF(E91="DNS",0,IF(E91="DQ",0,IF(E91="DNF",1,IF(AND(ISNUMBER(E91),E91&gt;59),1,_xlfn.XLOOKUP(E91,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H91" s="3" t="str">
         <f>IF(G91="","",IF(G91="DNS",0,IF(G91="DQ",0,IF(G91="DNF",1,IF(AND(ISNUMBER(G91),G91&gt;59),1,_xlfn.XLOOKUP(G91,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13039,15 +13035,15 @@
       </c>
       <c r="Q91" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R91" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S91" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -13156,25 +13152,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>140</v>
+        <v>331</v>
       </c>
       <c r="B94" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C94" t="s">
         <v>7</v>
       </c>
       <c r="D94" s="3">
-        <v>8196</v>
+        <v>826</v>
       </c>
       <c r="E94" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F94" s="3">
         <f>IF(E94="","",IF(E94="DNS",0,IF(E94="DQ",0,IF(E94="DNF",1,IF(AND(ISNUMBER(E94),E94&gt;59),1,_xlfn.XLOOKUP(E94,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="H94" s="3" t="str">
         <f>IF(G94="","",IF(G94="DNS",0,IF(G94="DQ",0,IF(G94="DNF",1,IF(AND(ISNUMBER(G94),G94&gt;59),1,_xlfn.XLOOKUP(G94,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13198,15 +13194,15 @@
       </c>
       <c r="Q94" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="R94" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="S94" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>90</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -13315,25 +13311,25 @@
         <v>34</v>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C97" t="s">
         <v>7</v>
       </c>
       <c r="D97" s="3">
-        <v>8195</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>416</v>
+        <v>810</v>
+      </c>
+      <c r="E97" s="3">
+        <v>17</v>
       </c>
       <c r="F97" s="3">
         <f>IF(E97="","",IF(E97="DNS",0,IF(E97="DQ",0,IF(E97="DNF",1,IF(AND(ISNUMBER(E97),E97&gt;59),1,_xlfn.XLOOKUP(E97,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H97" s="3" t="str">
         <f>IF(G97="","",IF(G97="DNS",0,IF(G97="DQ",0,IF(G97="DNF",1,IF(AND(ISNUMBER(G97),G97&gt;59),1,_xlfn.XLOOKUP(G97,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13357,36 +13353,36 @@
       </c>
       <c r="Q97" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R97" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S97" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C98" t="s">
         <v>7</v>
       </c>
       <c r="D98" s="3">
-        <v>8198</v>
+        <v>814</v>
       </c>
       <c r="E98" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F98" s="3">
         <f>IF(E98="","",IF(E98="DNS",0,IF(E98="DQ",0,IF(E98="DNF",1,IF(AND(ISNUMBER(E98),E98&gt;59),1,_xlfn.XLOOKUP(E98,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="H98" s="3" t="str">
         <f>IF(G98="","",IF(G98="DNS",0,IF(G98="DQ",0,IF(G98="DNF",1,IF(AND(ISNUMBER(G98),G98&gt;59),1,_xlfn.XLOOKUP(G98,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13410,15 +13406,15 @@
       </c>
       <c r="Q98" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="R98" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="S98" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>90</v>
+        <v>42</v>
       </c>
     </row>
     <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -13474,25 +13470,25 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>408</v>
+        <v>244</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C100" t="s">
         <v>7</v>
       </c>
       <c r="D100" s="3">
-        <v>8009</v>
+        <v>815</v>
       </c>
       <c r="E100" s="3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F100" s="3">
         <f>IF(E100="","",IF(E100="DNS",0,IF(E100="DQ",0,IF(E100="DNF",1,IF(AND(ISNUMBER(E100),E100&gt;59),1,_xlfn.XLOOKUP(E100,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="H100" s="3" t="str">
         <f>IF(G100="","",IF(G100="DNS",0,IF(G100="DQ",0,IF(G100="DNF",1,IF(AND(ISNUMBER(G100),G100&gt;59),1,_xlfn.XLOOKUP(G100,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13516,36 +13512,36 @@
       </c>
       <c r="Q100" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="R100" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="S100" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>142</v>
+        <v>302</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
         <v>7</v>
       </c>
       <c r="D101" s="3">
-        <v>8197</v>
+        <v>820</v>
       </c>
       <c r="E101" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F101" s="3">
         <f>IF(E101="","",IF(E101="DNS",0,IF(E101="DQ",0,IF(E101="DNF",1,IF(AND(ISNUMBER(E101),E101&gt;59),1,_xlfn.XLOOKUP(E101,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H101" s="3" t="str">
         <f>IF(G101="","",IF(G101="DNS",0,IF(G101="DQ",0,IF(G101="DNF",1,IF(AND(ISNUMBER(G101),G101&gt;59),1,_xlfn.XLOOKUP(G101,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13569,15 +13565,15 @@
       </c>
       <c r="Q101" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="R101" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="S101" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -13633,25 +13629,25 @@
         <v>65</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>145</v>
+        <v>334</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
         <v>7</v>
       </c>
       <c r="D103" s="3">
-        <v>800</v>
+        <v>829</v>
       </c>
       <c r="E103" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F103" s="3">
         <f>IF(E103="","",IF(E103="DNS",0,IF(E103="DQ",0,IF(E103="DNF",1,IF(AND(ISNUMBER(E103),E103&gt;59),1,_xlfn.XLOOKUP(E103,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H103" s="3" t="str">
         <f>IF(G103="","",IF(G103="DNS",0,IF(G103="DQ",0,IF(G103="DNF",1,IF(AND(ISNUMBER(G103),G103&gt;59),1,_xlfn.XLOOKUP(G103,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13675,15 +13671,15 @@
       </c>
       <c r="Q103" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R103" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="S103" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -13898,25 +13894,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
         <v>7</v>
       </c>
       <c r="D108" s="3">
-        <v>801</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>416</v>
+        <v>8191</v>
+      </c>
+      <c r="E108" s="3">
+        <v>22</v>
       </c>
       <c r="F108" s="3">
         <f>IF(E108="","",IF(E108="DNS",0,IF(E108="DQ",0,IF(E108="DNF",1,IF(AND(ISNUMBER(E108),E108&gt;59),1,_xlfn.XLOOKUP(E108,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H108" s="3" t="str">
         <f>IF(G108="","",IF(G108="DNS",0,IF(G108="DQ",0,IF(G108="DNF",1,IF(AND(ISNUMBER(G108),G108&gt;59),1,_xlfn.XLOOKUP(G108,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13940,36 +13936,36 @@
       </c>
       <c r="Q108" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R108" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S108" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C109" t="s">
         <v>7</v>
       </c>
       <c r="D109" s="3">
-        <v>8199</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>416</v>
+        <v>8147</v>
+      </c>
+      <c r="E109" s="3">
+        <v>23</v>
       </c>
       <c r="F109" s="3">
         <f>IF(E109="","",IF(E109="DNS",0,IF(E109="DQ",0,IF(E109="DNF",1,IF(AND(ISNUMBER(E109),E109&gt;59),1,_xlfn.XLOOKUP(E109,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H109" s="3" t="str">
         <f>IF(G109="","",IF(G109="DNS",0,IF(G109="DQ",0,IF(G109="DNF",1,IF(AND(ISNUMBER(G109),G109&gt;59),1,_xlfn.XLOOKUP(G109,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -13993,36 +13989,36 @@
       </c>
       <c r="Q109" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R109" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="S109" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>155</v>
+        <v>303</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C110" t="s">
         <v>7</v>
       </c>
       <c r="D110" s="3">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="E110" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F110" s="3">
         <f>IF(E110="","",IF(E110="DNS",0,IF(E110="DQ",0,IF(E110="DNF",1,IF(AND(ISNUMBER(E110),E110&gt;59),1,_xlfn.XLOOKUP(E110,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="H110" s="3" t="str">
         <f>IF(G110="","",IF(G110="DNS",0,IF(G110="DQ",0,IF(G110="DNF",1,IF(AND(ISNUMBER(G110),G110&gt;59),1,_xlfn.XLOOKUP(G110,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14046,15 +14042,15 @@
       </c>
       <c r="Q110" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="R110" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="S110" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -14110,7 +14106,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>190</v>
       </c>
@@ -14163,7 +14159,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>353</v>
       </c>
@@ -14216,7 +14212,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>354</v>
       </c>
@@ -14269,7 +14265,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>158</v>
       </c>
@@ -14428,25 +14424,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C118" t="s">
         <v>7</v>
       </c>
       <c r="D118" s="3">
-        <v>803</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>416</v>
+        <v>8049</v>
+      </c>
+      <c r="E118" s="3">
+        <v>25</v>
       </c>
       <c r="F118" s="3">
         <f>IF(E118="","",IF(E118="DNS",0,IF(E118="DQ",0,IF(E118="DNF",1,IF(AND(ISNUMBER(E118),E118&gt;59),1,_xlfn.XLOOKUP(E118,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H118" s="3" t="str">
         <f>IF(G118="","",IF(G118="DNS",0,IF(G118="DQ",0,IF(G118="DNF",1,IF(AND(ISNUMBER(G118),G118&gt;59),1,_xlfn.XLOOKUP(G118,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14470,36 +14466,36 @@
       </c>
       <c r="Q118" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R118" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S118" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B119" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C119" t="s">
         <v>7</v>
       </c>
       <c r="D119" s="3">
-        <v>837</v>
+        <v>800</v>
       </c>
       <c r="E119" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F119" s="3">
         <f>IF(E119="","",IF(E119="DNS",0,IF(E119="DQ",0,IF(E119="DNF",1,IF(AND(ISNUMBER(E119),E119&gt;59),1,_xlfn.XLOOKUP(E119,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="H119" s="3" t="str">
         <f>IF(G119="","",IF(G119="DNS",0,IF(G119="DQ",0,IF(G119="DNF",1,IF(AND(ISNUMBER(G119),G119&gt;59),1,_xlfn.XLOOKUP(G119,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14523,36 +14519,36 @@
       </c>
       <c r="Q119" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="R119" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="S119" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="B120" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C120" t="s">
         <v>7</v>
       </c>
       <c r="D120" s="3">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="E120" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F120" s="3">
         <f>IF(E120="","",IF(E120="DNS",0,IF(E120="DQ",0,IF(E120="DNF",1,IF(AND(ISNUMBER(E120),E120&gt;59),1,_xlfn.XLOOKUP(E120,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="H120" s="3" t="str">
         <f>IF(G120="","",IF(G120="DNS",0,IF(G120="DQ",0,IF(G120="DNF",1,IF(AND(ISNUMBER(G120),G120&gt;59),1,_xlfn.XLOOKUP(G120,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14576,36 +14572,36 @@
       </c>
       <c r="Q120" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="R120" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="S120" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>414</v>
+        <v>281</v>
       </c>
       <c r="B121" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C121" t="s">
         <v>7</v>
       </c>
       <c r="D121" s="3">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="E121" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F121" s="3">
         <f>IF(E121="","",IF(E121="DNS",0,IF(E121="DQ",0,IF(E121="DNF",1,IF(AND(ISNUMBER(E121),E121&gt;59),1,_xlfn.XLOOKUP(E121,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="H121" s="3" t="str">
         <f>IF(G121="","",IF(G121="DNS",0,IF(G121="DQ",0,IF(G121="DNF",1,IF(AND(ISNUMBER(G121),G121&gt;59),1,_xlfn.XLOOKUP(G121,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -14629,15 +14625,15 @@
       </c>
       <c r="Q121" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="R121" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="S121" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>85</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -14746,7 +14742,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>318</v>
       </c>
@@ -14799,7 +14795,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>293</v>
       </c>
@@ -14852,7 +14848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>338</v>
       </c>
@@ -14905,7 +14901,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>339</v>
       </c>
@@ -15011,25 +15007,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="B129" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C129" t="s">
         <v>7</v>
       </c>
       <c r="D129" s="3">
-        <v>806</v>
+        <v>8192</v>
       </c>
       <c r="E129" s="3">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F129" s="3">
         <f>IF(E129="","",IF(E129="DNS",0,IF(E129="DQ",0,IF(E129="DNF",1,IF(AND(ISNUMBER(E129),E129&gt;59),1,_xlfn.XLOOKUP(E129,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="H129" s="3" t="str">
         <f>IF(G129="","",IF(G129="DNS",0,IF(G129="DQ",0,IF(G129="DNF",1,IF(AND(ISNUMBER(G129),G129&gt;59),1,_xlfn.XLOOKUP(G129,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15053,15 +15049,15 @@
       </c>
       <c r="Q129" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="R129" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="S129" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -15170,25 +15166,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>173</v>
+        <v>280</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C132" t="s">
         <v>7</v>
       </c>
       <c r="D132" s="3">
-        <v>807</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>416</v>
+        <v>818</v>
+      </c>
+      <c r="E132" s="3">
+        <v>30</v>
       </c>
       <c r="F132" s="3">
         <f>IF(E132="","",IF(E132="DNS",0,IF(E132="DQ",0,IF(E132="DNF",1,IF(AND(ISNUMBER(E132),E132&gt;59),1,_xlfn.XLOOKUP(E132,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H132" s="3" t="str">
         <f>IF(G132="","",IF(G132="DNS",0,IF(G132="DQ",0,IF(G132="DNF",1,IF(AND(ISNUMBER(G132),G132&gt;59),1,_xlfn.XLOOKUP(G132,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15212,36 +15208,36 @@
       </c>
       <c r="Q132" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R132" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S132" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B133" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C133" t="s">
         <v>7</v>
       </c>
       <c r="D133" s="3">
-        <v>808</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>416</v>
+        <v>812</v>
+      </c>
+      <c r="E133" s="3">
+        <v>31</v>
       </c>
       <c r="F133" s="3">
         <f>IF(E133="","",IF(E133="DNS",0,IF(E133="DQ",0,IF(E133="DNF",1,IF(AND(ISNUMBER(E133),E133&gt;59),1,_xlfn.XLOOKUP(E133,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H133" s="3" t="str">
         <f>IF(G133="","",IF(G133="DNS",0,IF(G133="DQ",0,IF(G133="DNF",1,IF(AND(ISNUMBER(G133),G133&gt;59),1,_xlfn.XLOOKUP(G133,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15265,18 +15261,18 @@
       </c>
       <c r="Q133" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R133" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S133" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>189</v>
       </c>
@@ -15806,25 +15802,25 @@
         <v>60</v>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>186</v>
+        <v>359</v>
       </c>
       <c r="B144" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C144" t="s">
         <v>7</v>
       </c>
       <c r="D144" s="3">
-        <v>812</v>
+        <v>836</v>
       </c>
       <c r="E144" s="3">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F144" s="3">
         <f>IF(E144="","",IF(E144="DNS",0,IF(E144="DQ",0,IF(E144="DNF",1,IF(AND(ISNUMBER(E144),E144&gt;59),1,_xlfn.XLOOKUP(E144,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H144" s="3" t="str">
         <f>IF(G144="","",IF(G144="DNS",0,IF(G144="DQ",0,IF(G144="DNF",1,IF(AND(ISNUMBER(G144),G144&gt;59),1,_xlfn.XLOOKUP(G144,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -15848,15 +15844,15 @@
       </c>
       <c r="Q144" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="R144" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="S144" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -16124,25 +16120,25 @@
         <v>95</v>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="B150" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
         <v>7</v>
       </c>
       <c r="D150" s="3">
-        <v>811</v>
+        <v>8189</v>
       </c>
       <c r="E150" s="3">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F150" s="3">
         <f>IF(E150="","",IF(E150="DNS",0,IF(E150="DQ",0,IF(E150="DNF",1,IF(AND(ISNUMBER(E150),E150&gt;59),1,_xlfn.XLOOKUP(E150,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H150" s="3" t="str">
         <f>IF(G150="","",IF(G150="DNS",0,IF(G150="DQ",0,IF(G150="DNF",1,IF(AND(ISNUMBER(G150),G150&gt;59),1,_xlfn.XLOOKUP(G150,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -16166,15 +16162,15 @@
       </c>
       <c r="Q150" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="R150" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S150" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -16230,9 +16226,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B152" t="s">
         <v>20</v>
@@ -16241,7 +16237,7 @@
         <v>7</v>
       </c>
       <c r="D152" s="3">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E152" s="3">
         <v>34</v>
@@ -16283,7 +16279,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>156</v>
       </c>
@@ -16336,7 +16332,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>75</v>
       </c>
@@ -16389,7 +16385,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>74</v>
       </c>
@@ -16442,7 +16438,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>295</v>
       </c>
@@ -17025,25 +17021,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>183</v>
+        <v>332</v>
       </c>
       <c r="B167" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C167" t="s">
         <v>7</v>
       </c>
       <c r="D167" s="3">
-        <v>809</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>416</v>
+        <v>827</v>
+      </c>
+      <c r="E167" s="3">
+        <v>35</v>
       </c>
       <c r="F167" s="3">
         <f>IF(E167="","",IF(E167="DNS",0,IF(E167="DQ",0,IF(E167="DNF",1,IF(AND(ISNUMBER(E167),E167&gt;59),1,_xlfn.XLOOKUP(E167,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H167" s="3" t="str">
         <f>IF(G167="","",IF(G167="DNS",0,IF(G167="DQ",0,IF(G167="DNF",1,IF(AND(ISNUMBER(G167),G167&gt;59),1,_xlfn.XLOOKUP(G167,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -17067,15 +17063,15 @@
       </c>
       <c r="Q167" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R167" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S167" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -18456,25 +18452,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>237</v>
+        <v>333</v>
       </c>
       <c r="B194" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C194" t="s">
         <v>7</v>
       </c>
       <c r="D194" s="3">
-        <v>814</v>
+        <v>828</v>
       </c>
       <c r="E194" s="3">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F194" s="3">
         <f>IF(E194="","",IF(E194="DNS",0,IF(E194="DQ",0,IF(E194="DNF",1,IF(AND(ISNUMBER(E194),E194&gt;59),1,_xlfn.XLOOKUP(E194,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H194" s="3" t="str">
         <f>IF(G194="","",IF(G194="DNS",0,IF(G194="DQ",0,IF(G194="DNF",1,IF(AND(ISNUMBER(G194),G194&gt;59),1,_xlfn.XLOOKUP(G194,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18498,18 +18494,18 @@
       </c>
       <c r="Q194" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="R194" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="S194" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
         <v>124</v>
       </c>
@@ -18615,25 +18611,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>236</v>
+        <v>61</v>
       </c>
       <c r="B197" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C197" t="s">
         <v>7</v>
       </c>
       <c r="D197" s="3">
-        <v>813</v>
+        <v>8185</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F197" s="3">
         <f>IF(E197="","",IF(E197="DNS",0,IF(E197="DQ",0,IF(E197="DNF",1,IF(AND(ISNUMBER(E197),E197&gt;59),1,_xlfn.XLOOKUP(E197,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H197" s="3" t="str">
         <f>IF(G197="","",IF(G197="DNS",0,IF(G197="DQ",0,IF(G197="DNF",1,IF(AND(ISNUMBER(G197),G197&gt;59),1,_xlfn.XLOOKUP(G197,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18657,15 +18653,15 @@
       </c>
       <c r="Q197" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R197" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S197" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -18721,25 +18717,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="B199" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C199" t="s">
         <v>7</v>
       </c>
       <c r="D199" s="3">
-        <v>816</v>
-      </c>
-      <c r="E199" s="3">
-        <v>5</v>
+        <v>8010</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F199" s="3">
         <f>IF(E199="","",IF(E199="DNS",0,IF(E199="DQ",0,IF(E199="DNF",1,IF(AND(ISNUMBER(E199),E199&gt;59),1,_xlfn.XLOOKUP(E199,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H199" s="3" t="str">
         <f>IF(G199="","",IF(G199="DNS",0,IF(G199="DQ",0,IF(G199="DNF",1,IF(AND(ISNUMBER(G199),G199&gt;59),1,_xlfn.XLOOKUP(G199,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -18763,15 +18759,15 @@
       </c>
       <c r="Q199" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R199" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S199" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -19092,25 +19088,25 @@
         <v>49</v>
       </c>
     </row>
-    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>246</v>
+        <v>55</v>
       </c>
       <c r="B206" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C206" t="s">
         <v>7</v>
       </c>
       <c r="D206" s="3">
-        <v>817</v>
-      </c>
-      <c r="E206" s="3">
-        <v>14</v>
+        <v>8086</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F206" s="3">
         <f>IF(E206="","",IF(E206="DNS",0,IF(E206="DQ",0,IF(E206="DNF",1,IF(AND(ISNUMBER(E206),E206&gt;59),1,_xlfn.XLOOKUP(E206,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H206" s="3" t="str">
         <f>IF(G206="","",IF(G206="DNS",0,IF(G206="DQ",0,IF(G206="DNF",1,IF(AND(ISNUMBER(G206),G206&gt;59),1,_xlfn.XLOOKUP(G206,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19134,15 +19130,15 @@
       </c>
       <c r="Q206" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R206" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="S206" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -19198,25 +19194,25 @@
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>244</v>
+        <v>56</v>
       </c>
       <c r="B208" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C208" t="s">
         <v>7</v>
       </c>
       <c r="D208" s="3">
-        <v>815</v>
-      </c>
-      <c r="E208" s="3">
-        <v>19</v>
+        <v>8140</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F208" s="3">
         <f>IF(E208="","",IF(E208="DNS",0,IF(E208="DQ",0,IF(E208="DNF",1,IF(AND(ISNUMBER(E208),E208&gt;59),1,_xlfn.XLOOKUP(E208,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H208" s="3" t="str">
         <f>IF(G208="","",IF(G208="DNS",0,IF(G208="DQ",0,IF(G208="DNF",1,IF(AND(ISNUMBER(G208),G208&gt;59),1,_xlfn.XLOOKUP(G208,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -19240,15 +19236,15 @@
       </c>
       <c r="Q208" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R208" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S208" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -19993,7 +19989,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
         <v>157</v>
       </c>
@@ -20046,7 +20042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
         <v>125</v>
       </c>
@@ -20099,7 +20095,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
         <v>340</v>
       </c>
@@ -20152,7 +20148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
         <v>78</v>
       </c>
@@ -20205,7 +20201,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
         <v>290</v>
       </c>
@@ -20788,25 +20784,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="B238" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C238" t="s">
         <v>7</v>
       </c>
       <c r="D238" s="3">
-        <v>819</v>
-      </c>
-      <c r="E238" s="3">
-        <v>28</v>
+        <v>8154</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F238" s="3">
         <f>IF(E238="","",IF(E238="DNS",0,IF(E238="DQ",0,IF(E238="DNF",1,IF(AND(ISNUMBER(E238),E238&gt;59),1,_xlfn.XLOOKUP(E238,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H238" s="3" t="str">
         <f>IF(G238="","",IF(G238="DNS",0,IF(G238="DQ",0,IF(G238="DNF",1,IF(AND(ISNUMBER(G238),G238&gt;59),1,_xlfn.XLOOKUP(G238,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20830,36 +20826,36 @@
       </c>
       <c r="Q238" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R238" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="S238" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>280</v>
+        <v>59</v>
       </c>
       <c r="B239" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C239" t="s">
         <v>7</v>
       </c>
       <c r="D239" s="3">
-        <v>818</v>
-      </c>
-      <c r="E239" s="3">
-        <v>30</v>
+        <v>8177</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F239" s="3">
         <f>IF(E239="","",IF(E239="DNS",0,IF(E239="DQ",0,IF(E239="DNF",1,IF(AND(ISNUMBER(E239),E239&gt;59),1,_xlfn.XLOOKUP(E239,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H239" s="3" t="str">
         <f>IF(G239="","",IF(G239="DNS",0,IF(G239="DQ",0,IF(G239="DNF",1,IF(AND(ISNUMBER(G239),G239&gt;59),1,_xlfn.XLOOKUP(G239,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -20883,15 +20879,15 @@
       </c>
       <c r="Q239" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R239" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S239" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -21477,7 +21473,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
         <v>307</v>
       </c>
@@ -21530,7 +21526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
         <v>288</v>
       </c>
@@ -21583,7 +21579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
         <v>386</v>
       </c>
@@ -21636,7 +21632,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
         <v>417</v>
       </c>
@@ -21689,7 +21685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
         <v>68</v>
       </c>
@@ -21742,7 +21738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
         <v>76</v>
       </c>
@@ -21795,7 +21791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
         <v>105</v>
       </c>
@@ -21848,7 +21844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
         <v>166</v>
       </c>
@@ -21901,7 +21897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
         <v>167</v>
       </c>
@@ -21954,7 +21950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
         <v>168</v>
       </c>
@@ -22007,7 +22003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
         <v>169</v>
       </c>
@@ -22060,25 +22056,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>305</v>
+        <v>60</v>
       </c>
       <c r="B262" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C262" t="s">
         <v>7</v>
       </c>
       <c r="D262" s="3">
-        <v>823</v>
-      </c>
-      <c r="E262" s="3">
-        <v>12</v>
+        <v>8181</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F262" s="3">
         <f>IF(E262="","",IF(E262="DNS",0,IF(E262="DQ",0,IF(E262="DNF",1,IF(AND(ISNUMBER(E262),E262&gt;59),1,_xlfn.XLOOKUP(E262,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H262" s="3" t="str">
         <f>IF(G262="","",IF(G262="DNS",0,IF(G262="DQ",0,IF(G262="DNF",1,IF(AND(ISNUMBER(G262),G262&gt;59),1,_xlfn.XLOOKUP(G262,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -22102,15 +22098,15 @@
       </c>
       <c r="Q262" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R262" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="S262" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -22166,25 +22162,25 @@
         <v>51</v>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="B264" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C264" t="s">
         <v>7</v>
       </c>
       <c r="D264" s="3">
-        <v>820</v>
-      </c>
-      <c r="E264" s="3">
-        <v>20</v>
+        <v>8186</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F264" s="3">
         <f>IF(E264="","",IF(E264="DNS",0,IF(E264="DQ",0,IF(E264="DNF",1,IF(AND(ISNUMBER(E264),E264&gt;59),1,_xlfn.XLOOKUP(E264,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H264" s="3" t="str">
         <f>IF(G264="","",IF(G264="DNS",0,IF(G264="DQ",0,IF(G264="DNF",1,IF(AND(ISNUMBER(G264),G264&gt;59),1,_xlfn.XLOOKUP(G264,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -22208,36 +22204,36 @@
       </c>
       <c r="Q264" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R264" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S264" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>303</v>
+        <v>104</v>
       </c>
       <c r="B265" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C265" t="s">
         <v>7</v>
       </c>
       <c r="D265" s="3">
-        <v>821</v>
-      </c>
-      <c r="E265" s="3">
-        <v>24</v>
+        <v>8190</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F265" s="3">
         <f>IF(E265="","",IF(E265="DNS",0,IF(E265="DQ",0,IF(E265="DNF",1,IF(AND(ISNUMBER(E265),E265&gt;59),1,_xlfn.XLOOKUP(E265,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H265" s="3" t="str">
         <f>IF(G265="","",IF(G265="DNS",0,IF(G265="DQ",0,IF(G265="DNF",1,IF(AND(ISNUMBER(G265),G265&gt;59),1,_xlfn.XLOOKUP(G265,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -22261,36 +22257,36 @@
       </c>
       <c r="Q265" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R265" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="S265" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>304</v>
+        <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C266" t="s">
         <v>7</v>
       </c>
       <c r="D266" s="3">
-        <v>822</v>
-      </c>
-      <c r="E266" s="3">
-        <v>27</v>
+        <v>8193</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F266" s="3">
         <f>IF(E266="","",IF(E266="DNS",0,IF(E266="DQ",0,IF(E266="DNF",1,IF(AND(ISNUMBER(E266),E266&gt;59),1,_xlfn.XLOOKUP(E266,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H266" s="3" t="str">
         <f>IF(G266="","",IF(G266="DNS",0,IF(G266="DQ",0,IF(G266="DNF",1,IF(AND(ISNUMBER(G266),G266&gt;59),1,_xlfn.XLOOKUP(G266,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -22314,18 +22310,18 @@
       </c>
       <c r="Q266" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R266" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S266" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
         <v>177</v>
       </c>
@@ -22378,7 +22374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
         <v>188</v>
       </c>
@@ -22643,25 +22639,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>313</v>
+        <v>123</v>
       </c>
       <c r="B273" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C273" t="s">
         <v>7</v>
       </c>
       <c r="D273" s="3">
-        <v>824</v>
-      </c>
-      <c r="E273" s="3">
-        <v>10</v>
+        <v>8194</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F273" s="3">
         <f>IF(E273="","",IF(E273="DNS",0,IF(E273="DQ",0,IF(E273="DNF",1,IF(AND(ISNUMBER(E273),E273&gt;59),1,_xlfn.XLOOKUP(E273,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H273" s="3" t="str">
         <f>IF(G273="","",IF(G273="DNS",0,IF(G273="DQ",0,IF(G273="DNF",1,IF(AND(ISNUMBER(G273),G273&gt;59),1,_xlfn.XLOOKUP(G273,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -22685,36 +22681,36 @@
       </c>
       <c r="Q273" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R273" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S273" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>314</v>
+        <v>139</v>
       </c>
       <c r="B274" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C274" t="s">
         <v>7</v>
       </c>
       <c r="D274" s="3">
-        <v>825</v>
-      </c>
-      <c r="E274" s="3">
-        <v>13</v>
+        <v>8195</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F274" s="3">
         <f>IF(E274="","",IF(E274="DNS",0,IF(E274="DQ",0,IF(E274="DNF",1,IF(AND(ISNUMBER(E274),E274&gt;59),1,_xlfn.XLOOKUP(E274,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H274" s="3" t="str">
         <f>IF(G274="","",IF(G274="DNS",0,IF(G274="DQ",0,IF(G274="DNF",1,IF(AND(ISNUMBER(G274),G274&gt;59),1,_xlfn.XLOOKUP(G274,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -22738,15 +22734,15 @@
       </c>
       <c r="Q274" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R274" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S274" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -23120,7 +23116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
         <v>251</v>
       </c>
@@ -23173,7 +23169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
         <v>252</v>
       </c>
@@ -23226,7 +23222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
         <v>253</v>
       </c>
@@ -23279,7 +23275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
         <v>254</v>
       </c>
@@ -23703,25 +23699,25 @@
         <v>39</v>
       </c>
     </row>
-    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
-        <v>331</v>
+        <v>146</v>
       </c>
       <c r="B293" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C293" t="s">
         <v>7</v>
       </c>
       <c r="D293" s="3">
-        <v>826</v>
-      </c>
-      <c r="E293" s="3">
-        <v>16</v>
+        <v>801</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F293" s="3">
         <f>IF(E293="","",IF(E293="DNS",0,IF(E293="DQ",0,IF(E293="DNF",1,IF(AND(ISNUMBER(E293),E293&gt;59),1,_xlfn.XLOOKUP(E293,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H293" s="3" t="str">
         <f>IF(G293="","",IF(G293="DNS",0,IF(G293="DQ",0,IF(G293="DNF",1,IF(AND(ISNUMBER(G293),G293&gt;59),1,_xlfn.XLOOKUP(G293,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -23745,36 +23741,36 @@
       </c>
       <c r="Q293" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R293" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="S293" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>334</v>
+        <v>144</v>
       </c>
       <c r="B294" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C294" t="s">
         <v>7</v>
       </c>
       <c r="D294" s="3">
-        <v>829</v>
-      </c>
-      <c r="E294" s="3">
-        <v>21</v>
+        <v>8199</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F294" s="3">
         <f>IF(E294="","",IF(E294="DNS",0,IF(E294="DQ",0,IF(E294="DNF",1,IF(AND(ISNUMBER(E294),E294&gt;59),1,_xlfn.XLOOKUP(E294,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H294" s="3" t="str">
         <f>IF(G294="","",IF(G294="DNS",0,IF(G294="DQ",0,IF(G294="DNF",1,IF(AND(ISNUMBER(G294),G294&gt;59),1,_xlfn.XLOOKUP(G294,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -23798,15 +23794,15 @@
       </c>
       <c r="Q294" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R294" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S294" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -23915,25 +23911,25 @@
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>332</v>
+        <v>154</v>
       </c>
       <c r="B297" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C297" t="s">
         <v>7</v>
       </c>
       <c r="D297" s="3">
-        <v>827</v>
-      </c>
-      <c r="E297" s="3">
-        <v>35</v>
+        <v>803</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F297" s="3">
         <f>IF(E297="","",IF(E297="DNS",0,IF(E297="DQ",0,IF(E297="DNF",1,IF(AND(ISNUMBER(E297),E297&gt;59),1,_xlfn.XLOOKUP(E297,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H297" s="3" t="str">
         <f>IF(G297="","",IF(G297="DNS",0,IF(G297="DQ",0,IF(G297="DNF",1,IF(AND(ISNUMBER(G297),G297&gt;59),1,_xlfn.XLOOKUP(G297,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -23957,36 +23953,36 @@
       </c>
       <c r="Q297" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R297" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S297" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>333</v>
+        <v>172</v>
       </c>
       <c r="B298" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C298" t="s">
         <v>7</v>
       </c>
       <c r="D298" s="3">
-        <v>828</v>
-      </c>
-      <c r="E298" s="3">
-        <v>36</v>
+        <v>806</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F298" s="3">
         <f>IF(E298="","",IF(E298="DNS",0,IF(E298="DQ",0,IF(E298="DNF",1,IF(AND(ISNUMBER(E298),E298&gt;59),1,_xlfn.XLOOKUP(E298,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H298" s="3" t="str">
         <f>IF(G298="","",IF(G298="DNS",0,IF(G298="DQ",0,IF(G298="DNF",1,IF(AND(ISNUMBER(G298),G298&gt;59),1,_xlfn.XLOOKUP(G298,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -24010,18 +24006,18 @@
       </c>
       <c r="Q298" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R298" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S298" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
         <v>287</v>
       </c>
@@ -24074,7 +24070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
         <v>289</v>
       </c>
@@ -24127,7 +24123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
         <v>294</v>
       </c>
@@ -24180,7 +24176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
         <v>306</v>
       </c>
@@ -24233,7 +24229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
         <v>317</v>
       </c>
@@ -24397,18 +24393,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>335</v>
+        <v>173</v>
       </c>
       <c r="B306" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C306" t="s">
         <v>7</v>
       </c>
       <c r="D306" s="3">
-        <v>830</v>
+        <v>807</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>416</v>
@@ -24662,25 +24658,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
-        <v>351</v>
+        <v>174</v>
       </c>
       <c r="B311" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C311" t="s">
         <v>7</v>
       </c>
       <c r="D311" s="3">
-        <v>831</v>
-      </c>
-      <c r="E311" s="3">
-        <v>6</v>
+        <v>808</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F311" s="3">
         <f>IF(E311="","",IF(E311="DNS",0,IF(E311="DQ",0,IF(E311="DNF",1,IF(AND(ISNUMBER(E311),E311&gt;59),1,_xlfn.XLOOKUP(E311,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H311" s="3" t="str">
         <f>IF(G311="","",IF(G311="DNS",0,IF(G311="DQ",0,IF(G311="DNF",1,IF(AND(ISNUMBER(G311),G311&gt;59),1,_xlfn.XLOOKUP(G311,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -24704,36 +24700,36 @@
       </c>
       <c r="Q311" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R311" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S311" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="B312" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C312" t="s">
         <v>7</v>
       </c>
       <c r="D312" s="3">
-        <v>832</v>
-      </c>
-      <c r="E312" s="3">
-        <v>7</v>
+        <v>811</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F312" s="3">
         <f>IF(E312="","",IF(E312="DNS",0,IF(E312="DQ",0,IF(E312="DNF",1,IF(AND(ISNUMBER(E312),E312&gt;59),1,_xlfn.XLOOKUP(E312,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H312" s="3" t="str">
         <f>IF(G312="","",IF(G312="DNS",0,IF(G312="DQ",0,IF(G312="DNF",1,IF(AND(ISNUMBER(G312),G312&gt;59),1,_xlfn.XLOOKUP(G312,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -24757,18 +24753,18 @@
       </c>
       <c r="Q312" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R312" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="S312" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
         <v>319</v>
       </c>
@@ -24821,7 +24817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
         <v>320</v>
       </c>
@@ -25298,25 +25294,25 @@
         <v>80</v>
       </c>
     </row>
-    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>356</v>
+        <v>236</v>
       </c>
       <c r="B323" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C323" t="s">
         <v>7</v>
       </c>
       <c r="D323" s="3">
-        <v>833</v>
-      </c>
-      <c r="E323" s="3">
-        <v>15</v>
+        <v>813</v>
+      </c>
+      <c r="E323" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F323" s="3">
         <f>IF(E323="","",IF(E323="DNS",0,IF(E323="DQ",0,IF(E323="DNF",1,IF(AND(ISNUMBER(E323),E323&gt;59),1,_xlfn.XLOOKUP(E323,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H323" s="3" t="str">
         <f>IF(G323="","",IF(G323="DNS",0,IF(G323="DQ",0,IF(G323="DNF",1,IF(AND(ISNUMBER(G323),G323&gt;59),1,_xlfn.XLOOKUP(G323,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -25340,36 +25336,36 @@
       </c>
       <c r="Q323" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R323" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S323" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="B324" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C324" t="s">
         <v>7</v>
       </c>
       <c r="D324" s="3">
-        <v>836</v>
-      </c>
-      <c r="E324" s="3">
-        <v>32</v>
+        <v>830</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="F324" s="3">
         <f>IF(E324="","",IF(E324="DNS",0,IF(E324="DQ",0,IF(E324="DNF",1,IF(AND(ISNUMBER(E324),E324&gt;59),1,_xlfn.XLOOKUP(E324,tbl_points[Place],tbl_points[Points],""))))))</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H324" s="3" t="str">
         <f>IF(G324="","",IF(G324="DNS",0,IF(G324="DQ",0,IF(G324="DNF",1,IF(AND(ISNUMBER(G324),G324&gt;59),1,_xlfn.XLOOKUP(G324,tbl_points[Place],tbl_points[Points],""))))))</f>
@@ -25393,15 +25389,15 @@
       </c>
       <c r="Q324" s="3">
         <f>SUM(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R324" s="3">
         <f>MIN(tbl_individual[[#This Row],[R1 Pts]],tbl_individual[[#This Row],[R2 Pts]],tbl_individual[[#This Row],[R3 Pts]],tbl_individual[[#This Row],[R4 Pts]],tbl_individual[[#This Row],[R5 Pts]],tbl_individual[[#This Row],[R6 Pts]])</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S324" s="3">
         <f>tbl_individual[[#This Row],[Total]]</f>
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
@@ -25669,7 +25665,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
         <v>357</v>
       </c>
@@ -26093,7 +26089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
         <v>358</v>
       </c>
@@ -26623,7 +26619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
         <v>336</v>
       </c>
@@ -26676,7 +26672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
         <v>384</v>
       </c>
@@ -26729,7 +26725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
         <v>385</v>
       </c>
@@ -26835,7 +26831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
         <v>383</v>
       </c>
@@ -29411,7 +29407,7 @@
     ""
 )
 )</f>
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D6" s="3" t="str" cm="1">
         <f t="array" ref="D6">_xlfn.LET(
@@ -29580,7 +29576,7 @@
       </c>
       <c r="I6" s="3">
         <f>SUM(tbl_teampoints[[#This Row],[Race 1]]:tbl_teampoints[[#This Row],[Race 6]])</f>
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -39785,16 +39781,16 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
-        <v>Max Remfry</v>
+        <v>Kelyn Horsely</v>
       </c>
       <c r="B23" t="str">
-        <v>Argyle</v>
+        <v>Don Ross</v>
       </c>
       <c r="C23" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D23">
-        <v>8147</v>
+        <v>837</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -39827,16 +39823,16 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
-        <v>Laith Rifaat</v>
+        <v>Elias Newby</v>
       </c>
       <c r="B26" t="str">
-        <v>Argyle</v>
+        <v>Don Ross</v>
       </c>
       <c r="C26" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D26">
-        <v>8049</v>
+        <v>838</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -39981,44 +39977,44 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
-        <v>Owen Purdy</v>
+        <v>Alexander Moran</v>
       </c>
       <c r="B37" t="str">
-        <v>Argyle</v>
+        <v>Chatelech</v>
       </c>
       <c r="C37" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D37">
-        <v>8185</v>
+        <v>8196</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
-        <v>Ryan Pasha</v>
+        <v>Asher Lissett</v>
       </c>
       <c r="B38" t="str">
-        <v>Argyle</v>
+        <v>Coast Mtn</v>
       </c>
       <c r="C38" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D38">
-        <v>8010</v>
+        <v>8198</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
-        <v>Dylan MacDondald</v>
+        <v>Tristan Clark</v>
       </c>
       <c r="B39" t="str">
-        <v>Argyle</v>
+        <v>Don Ross</v>
       </c>
       <c r="C39" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D39">
-        <v>8086</v>
+        <v>839</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -40177,72 +40173,72 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
-        <v>Lucas Cullingworth</v>
+        <v>Dash Nicoll</v>
       </c>
       <c r="B51" t="str">
-        <v>Argyle</v>
+        <v>Pemberton</v>
       </c>
       <c r="C51" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D51">
-        <v>8140</v>
+        <v>816</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
-        <v>Riley Buxton</v>
+        <v>Hayden Bristow</v>
       </c>
       <c r="B52" t="str">
-        <v>Argyle</v>
+        <v>West Van</v>
       </c>
       <c r="C52" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D52">
-        <v>8154</v>
+        <v>831</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
-        <v>Rowen Doerr</v>
+        <v>Trent Bristow</v>
       </c>
       <c r="B53" t="str">
-        <v>Argyle</v>
+        <v>West Van</v>
       </c>
       <c r="C53" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D53">
-        <v>8177</v>
+        <v>832</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
-        <v>Ronin Stewart</v>
+        <v>Slater McDougall</v>
       </c>
       <c r="B54" t="str">
-        <v>Argyle</v>
+        <v>Collingwood</v>
       </c>
       <c r="C54" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D54">
-        <v>8181</v>
+        <v>804</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
-        <v>Nico Scott</v>
+        <v>Callum Paul</v>
       </c>
       <c r="B55" t="str">
-        <v>Argyle</v>
+        <v>Coast Mtn</v>
       </c>
       <c r="C55" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D55">
-        <v>8186</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -40303,16 +40299,16 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
-        <v>Aiden Bucci</v>
+        <v>Teo Damici</v>
       </c>
       <c r="B60" t="str">
-        <v>Brockton</v>
+        <v>STA</v>
       </c>
       <c r="C60" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D60">
-        <v>8189</v>
+        <v>824</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -40401,16 +40397,16 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67" t="str">
-        <v>Henry Sparrow</v>
+        <v>Andrew Simpson</v>
       </c>
       <c r="B67" t="str">
-        <v>Brockton</v>
+        <v>Coast Mtn</v>
       </c>
       <c r="C67" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D67">
-        <v>8190</v>
+        <v>8197</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -40429,30 +40425,30 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69" t="str">
-        <v>Austin Bandic</v>
+        <v>Andrew Wenzlaff</v>
       </c>
       <c r="B69" t="str">
-        <v>Burnaby Mtn</v>
+        <v>St. Georges</v>
       </c>
       <c r="C69" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D69">
-        <v>8191</v>
+        <v>823</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70" t="str">
-        <v>Yara Raouf Malayeri</v>
+        <v>Rory Sykes</v>
       </c>
       <c r="B70" t="str">
-        <v>Burnaby Mtn</v>
+        <v>STA</v>
       </c>
       <c r="C70" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D70">
-        <v>8192</v>
+        <v>825</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -40726,30 +40722,30 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A90" t="str">
-        <v>James Kwong</v>
+        <v>Micah Treadway</v>
       </c>
       <c r="B90" t="str">
-        <v>Carson</v>
+        <v>Pemberton</v>
       </c>
       <c r="C90" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D90">
-        <v>8193</v>
+        <v>817</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A91" t="str">
-        <v>Bryce Weatherly</v>
+        <v>Luke McGowan</v>
       </c>
       <c r="B91" t="str">
-        <v>Carson</v>
+        <v>Whistler</v>
       </c>
       <c r="C91" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D91">
-        <v>8194</v>
+        <v>833</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.4">
@@ -40782,16 +40778,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A94" t="str">
-        <v>Alexander Moran</v>
+        <v>William Kolper</v>
       </c>
       <c r="B94" t="str">
-        <v>Chatelech</v>
+        <v>Sutherland</v>
       </c>
       <c r="C94" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D94">
-        <v>8196</v>
+        <v>826</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.4">
@@ -40824,30 +40820,30 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97" t="str">
-        <v>Jack Walton</v>
+        <v>Felix Carr</v>
       </c>
       <c r="B97" t="str">
-        <v>Chatelech</v>
+        <v>Handsworth</v>
       </c>
       <c r="C97" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D97">
-        <v>8195</v>
+        <v>810</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98" t="str">
-        <v>Asher Lissett</v>
+        <v>Lennart Schilling</v>
       </c>
       <c r="B98" t="str">
-        <v>Coast Mtn</v>
+        <v>Mulgrave</v>
       </c>
       <c r="C98" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D98">
-        <v>8198</v>
+        <v>814</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -40866,30 +40862,30 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100" t="str">
-        <v>Callum Paul</v>
+        <v>Ryan Kearnes</v>
       </c>
       <c r="B100" t="str">
-        <v>Coast Mtn</v>
+        <v>Pemberton</v>
       </c>
       <c r="C100" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D100">
-        <v>8009</v>
+        <v>815</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101" t="str">
-        <v>Andrew Simpson</v>
+        <v>Tristan Cole</v>
       </c>
       <c r="B101" t="str">
-        <v>Coast Mtn</v>
+        <v>St. Georges</v>
       </c>
       <c r="C101" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D101">
-        <v>8197</v>
+        <v>820</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -40908,16 +40904,16 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103" t="str">
-        <v>Jackson Jones</v>
+        <v>Seth Andru</v>
       </c>
       <c r="B103" t="str">
-        <v>Coast Mtn</v>
+        <v>Sutherland</v>
       </c>
       <c r="C103" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D103">
-        <v>800</v>
+        <v>829</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -40978,44 +40974,44 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108" t="str">
-        <v>Cole Fraser</v>
+        <v>Austin Bandic</v>
       </c>
       <c r="B108" t="str">
-        <v>Coast Mtn</v>
+        <v>Burnaby Mtn</v>
       </c>
       <c r="C108" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D108">
-        <v>801</v>
+        <v>8191</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109" t="str">
-        <v>Weston Morum</v>
+        <v>Max Remfry</v>
       </c>
       <c r="B109" t="str">
-        <v>Coast Mtn</v>
+        <v>Argyle</v>
       </c>
       <c r="C109" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D109">
-        <v>8199</v>
+        <v>8147</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A110" t="str">
-        <v>Slater McDougall</v>
+        <v>Alasdair Robertson</v>
       </c>
       <c r="B110" t="str">
-        <v>Collingwood</v>
+        <v>St. Georges</v>
       </c>
       <c r="C110" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D110">
-        <v>804</v>
+        <v>821</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -41118,58 +41114,58 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A118" t="str">
-        <v>Jack Burt</v>
+        <v>Laith Rifaat</v>
       </c>
       <c r="B118" t="str">
-        <v>Collingwood</v>
+        <v>Argyle</v>
       </c>
       <c r="C118" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D118">
-        <v>803</v>
+        <v>8049</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A119" t="str">
-        <v>Kelyn Horsely</v>
+        <v>Jackson Jones</v>
       </c>
       <c r="B119" t="str">
-        <v>Don Ross</v>
+        <v>Coast Mtn</v>
       </c>
       <c r="C119" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D119">
-        <v>837</v>
+        <v>800</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A120" t="str">
-        <v>Elias Newby</v>
+        <v>David Shilletto</v>
       </c>
       <c r="B120" t="str">
-        <v>Don Ross</v>
+        <v>St. Georges</v>
       </c>
       <c r="C120" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D120">
-        <v>838</v>
+        <v>822</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A121" t="str">
-        <v>Tristan Clark</v>
+        <v>Augusten Worsfold</v>
       </c>
       <c r="B121" t="str">
-        <v>Don Ross</v>
+        <v>Rockridge</v>
       </c>
       <c r="C121" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D121">
-        <v>839</v>
+        <v>819</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -41272,16 +41268,16 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A129" t="str">
-        <v>Jivcko Elvir Sheilds</v>
+        <v>Yara Raouf Malayeri</v>
       </c>
       <c r="B129" t="str">
-        <v>Elphinstone</v>
+        <v>Burnaby Mtn</v>
       </c>
       <c r="C129" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D129">
-        <v>806</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.4">
@@ -41314,16 +41310,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A132" t="str">
-        <v>Sean Weber</v>
+        <v>Lucas Solis</v>
       </c>
       <c r="B132" t="str">
-        <v>Elphinstone</v>
+        <v>Rockridge</v>
       </c>
       <c r="C132" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D132">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>412</v>
@@ -41331,16 +41327,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A133" t="str">
-        <v>Arthur Scale</v>
+        <v>Remy Zurbuchen</v>
       </c>
       <c r="B133" t="str">
-        <v>Elphinstone</v>
+        <v>Handsworth</v>
       </c>
       <c r="C133" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D133">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>412</v>
@@ -41500,16 +41496,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A144" t="str">
-        <v>Remy Zurbuchen</v>
+        <v>Anton Anghellescu</v>
       </c>
       <c r="B144" t="str">
-        <v>Handsworth</v>
+        <v>Whistler</v>
       </c>
       <c r="C144" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D144">
-        <v>812</v>
+        <v>836</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -41584,16 +41580,16 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A150" t="str">
-        <v>William Lucas</v>
+        <v>Aiden Bucci</v>
       </c>
       <c r="B150" t="str">
-        <v>Handsworth</v>
+        <v>Brockton</v>
       </c>
       <c r="C150" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D150">
-        <v>811</v>
+        <v>8189</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -41612,7 +41608,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A152" t="str">
-        <v>Felix Carr</v>
+        <v>Marcelo Alcocer Tremari</v>
       </c>
       <c r="B152" t="str">
         <v>Handsworth</v>
@@ -41621,7 +41617,7 @@
         <v>Bant Boys</v>
       </c>
       <c r="D152">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -41822,16 +41818,16 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A167" t="str">
-        <v>Marcelo Alcocer Tremari</v>
+        <v>Erik Moore</v>
       </c>
       <c r="B167" t="str">
-        <v>Handsworth</v>
+        <v>Sutherland</v>
       </c>
       <c r="C167" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D167">
-        <v>809</v>
+        <v>827</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -42200,16 +42196,16 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A194" t="str">
-        <v>Lennart Schilling</v>
+        <v>Kaelan Percival</v>
       </c>
       <c r="B194" t="str">
-        <v>Mulgrave</v>
+        <v>Sutherland</v>
       </c>
       <c r="C194" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D194">
-        <v>814</v>
+        <v>828</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -42242,16 +42238,16 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A197" t="str">
-        <v>Jeronimo Gomez</v>
+        <v>Owen Purdy</v>
       </c>
       <c r="B197" t="str">
-        <v>Mulgrave</v>
+        <v>Argyle</v>
       </c>
       <c r="C197" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D197">
-        <v>813</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -42270,16 +42266,16 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A199" t="str">
-        <v>Dash Nicoll</v>
+        <v>Ryan Pasha</v>
       </c>
       <c r="B199" t="str">
-        <v>Pemberton</v>
+        <v>Argyle</v>
       </c>
       <c r="C199" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D199">
-        <v>816</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -42368,16 +42364,16 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A206" t="str">
-        <v>Micah Treadway</v>
+        <v>Dylan MacDondald</v>
       </c>
       <c r="B206" t="str">
-        <v>Pemberton</v>
+        <v>Argyle</v>
       </c>
       <c r="C206" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D206">
-        <v>817</v>
+        <v>8086</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -42396,16 +42392,16 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A208" t="str">
-        <v>Ryan Kearnes</v>
+        <v>Lucas Cullingworth</v>
       </c>
       <c r="B208" t="str">
-        <v>Pemberton</v>
+        <v>Argyle</v>
       </c>
       <c r="C208" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D208">
-        <v>815</v>
+        <v>8140</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -42816,30 +42812,30 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A238" t="str">
-        <v>Augusten Worsfold</v>
+        <v>Riley Buxton</v>
       </c>
       <c r="B238" t="str">
-        <v>Rockridge</v>
+        <v>Argyle</v>
       </c>
       <c r="C238" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D238">
-        <v>819</v>
+        <v>8154</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A239" t="str">
-        <v>Lucas Solis</v>
+        <v>Rowen Doerr</v>
       </c>
       <c r="B239" t="str">
-        <v>Rockridge</v>
+        <v>Argyle</v>
       </c>
       <c r="C239" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D239">
-        <v>818</v>
+        <v>8177</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -43164,16 +43160,16 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A262" t="str">
-        <v>Andrew Wenzlaff</v>
+        <v>Ronin Stewart</v>
       </c>
       <c r="B262" t="str">
-        <v>St. Georges</v>
+        <v>Argyle</v>
       </c>
       <c r="C262" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D262">
-        <v>823</v>
+        <v>8181</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>407</v>
@@ -43198,16 +43194,16 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A264" t="str">
-        <v>Tristan Cole</v>
+        <v>Nico Scott</v>
       </c>
       <c r="B264" t="str">
-        <v>St. Georges</v>
+        <v>Argyle</v>
       </c>
       <c r="C264" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D264">
-        <v>820</v>
+        <v>8186</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>407</v>
@@ -43215,16 +43211,16 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A265" t="str">
-        <v>Alasdair Robertson</v>
+        <v>Henry Sparrow</v>
       </c>
       <c r="B265" t="str">
-        <v>St. Georges</v>
+        <v>Brockton</v>
       </c>
       <c r="C265" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D265">
-        <v>821</v>
+        <v>8190</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>407</v>
@@ -43232,16 +43228,16 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A266" t="str">
-        <v>David Shilletto</v>
+        <v>James Kwong</v>
       </c>
       <c r="B266" t="str">
-        <v>St. Georges</v>
+        <v>Carson</v>
       </c>
       <c r="C266" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D266">
-        <v>822</v>
+        <v>8193</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>407</v>
@@ -43339,30 +43335,30 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A273" t="str">
-        <v>Teo Damici</v>
+        <v>Bryce Weatherly</v>
       </c>
       <c r="B273" t="str">
-        <v>STA</v>
+        <v>Carson</v>
       </c>
       <c r="C273" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D273">
-        <v>824</v>
+        <v>8194</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A274" t="str">
-        <v>Rory Sykes</v>
+        <v>Jack Walton</v>
       </c>
       <c r="B274" t="str">
-        <v>STA</v>
+        <v>Chatelech</v>
       </c>
       <c r="C274" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D274">
-        <v>825</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -43625,30 +43621,30 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A293" t="str">
-        <v>William Kolper</v>
+        <v>Cole Fraser</v>
       </c>
       <c r="B293" t="str">
-        <v>Sutherland</v>
+        <v>Coast Mtn</v>
       </c>
       <c r="C293" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D293">
-        <v>826</v>
+        <v>801</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A294" t="str">
-        <v>Seth Andru</v>
+        <v>Weston Morum</v>
       </c>
       <c r="B294" t="str">
-        <v>Sutherland</v>
+        <v>Coast Mtn</v>
       </c>
       <c r="C294" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D294">
-        <v>829</v>
+        <v>8199</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.4">
@@ -43681,30 +43677,30 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A297" t="str">
-        <v>Erik Moore</v>
+        <v>Jack Burt</v>
       </c>
       <c r="B297" t="str">
-        <v>Sutherland</v>
+        <v>Collingwood</v>
       </c>
       <c r="C297" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D297">
-        <v>827</v>
+        <v>803</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A298" t="str">
-        <v>Kaelan Percival</v>
+        <v>Jivcko Elvir Sheilds</v>
       </c>
       <c r="B298" t="str">
-        <v>Sutherland</v>
+        <v>Elphinstone</v>
       </c>
       <c r="C298" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D298">
-        <v>828</v>
+        <v>806</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.4">
@@ -43807,16 +43803,16 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A306" t="str">
-        <v>Greyson Klein</v>
+        <v>Sean Weber</v>
       </c>
       <c r="B306" t="str">
-        <v>Sutherland</v>
+        <v>Elphinstone</v>
       </c>
       <c r="C306" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D306">
-        <v>830</v>
+        <v>807</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.4">
@@ -43877,30 +43873,30 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A311" t="str">
-        <v>Hayden Bristow</v>
+        <v>Arthur Scale</v>
       </c>
       <c r="B311" t="str">
-        <v>West Van</v>
+        <v>Elphinstone</v>
       </c>
       <c r="C311" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D311">
-        <v>831</v>
+        <v>808</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A312" t="str">
-        <v>Trent Bristow</v>
+        <v>William Lucas</v>
       </c>
       <c r="B312" t="str">
-        <v>West Van</v>
+        <v>Handsworth</v>
       </c>
       <c r="C312" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D312">
-        <v>832</v>
+        <v>811</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.4">
@@ -44045,30 +44041,30 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A323" t="str">
-        <v>Luke McGowan</v>
+        <v>Jeronimo Gomez</v>
       </c>
       <c r="B323" t="str">
-        <v>Whistler</v>
+        <v>Mulgrave</v>
       </c>
       <c r="C323" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D323">
-        <v>833</v>
+        <v>813</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A324" t="str">
-        <v>Anton Anghellescu</v>
+        <v>Greyson Klein</v>
       </c>
       <c r="B324" t="str">
-        <v>Whistler</v>
+        <v>Sutherland</v>
       </c>
       <c r="C324" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D324">
-        <v>836</v>
+        <v>830</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.4">
@@ -44579,16 +44575,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <v>Andrew Wenzlaff</v>
+        <v>Ronin Stewart</v>
       </c>
       <c r="B6" t="str">
-        <v>St. Georges</v>
+        <v>Argyle</v>
       </c>
       <c r="C6" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D6">
-        <v>823</v>
+        <v>8181</v>
       </c>
       <c r="E6" s="3" t="str">
         <v>yes</v>
@@ -44613,16 +44609,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <v>Tristan Cole</v>
+        <v>Nico Scott</v>
       </c>
       <c r="B8" t="str">
-        <v>St. Georges</v>
+        <v>Argyle</v>
       </c>
       <c r="C8" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D8">
-        <v>820</v>
+        <v>8186</v>
       </c>
       <c r="E8" s="3" t="str">
         <v>yes</v>
@@ -44630,16 +44626,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <v>Alasdair Robertson</v>
+        <v>Henry Sparrow</v>
       </c>
       <c r="B9" t="str">
-        <v>St. Georges</v>
+        <v>Brockton</v>
       </c>
       <c r="C9" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D9">
-        <v>821</v>
+        <v>8190</v>
       </c>
       <c r="E9" s="3" t="str">
         <v>yes</v>
@@ -44647,16 +44643,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
-        <v>David Shilletto</v>
+        <v>James Kwong</v>
       </c>
       <c r="B10" t="str">
-        <v>St. Georges</v>
+        <v>Carson</v>
       </c>
       <c r="C10" t="str">
         <v>Bant Boys</v>
       </c>
       <c r="D10">
-        <v>822</v>
+        <v>8193</v>
       </c>
       <c r="E10" s="3" t="str">
         <v>yes</v>
